--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B6F80A-CEF5-4F6A-9D40-13DA59B6C7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DD5895-2F2E-4058-B90E-ECBEB22A1300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="13380" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="61">
   <si>
     <t>Epic</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Story Point</t>
   </si>
   <si>
-    <t>Show inline errors</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -193,1745 +190,6 @@
     <t>Frontend Dev</t>
   </si>
   <si>
-    <t>Sign Up</t>
-  </si>
-  <si>
-    <t>1. Submit form data
-2. Submit ID image
-3. Submit selfie image</t>
-  </si>
-  <si>
-    <t>Sign In</t>
-  </si>
-  <si>
-    <t>Post-landing Navigation</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = UNAUTHENTICATED and entryIntent = LIST/RENT/NULL
-1. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">SignIn </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = UNAUTHENTICATED, pressing Rent a Bike or List a Bike button navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SignIn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> page</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Pressing </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink
-1. Navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ExploreMaps</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout (MANUAL/e2e TESTING)
-2. Activates </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab (MANUAL/e2e TESTING)</t>
-    </r>
-  </si>
-  <si>
-    <t>Explore</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED or UNAUTHENTICATED:
-1. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ExploreMaps</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout
-2. Activate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab (guest access)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, tapping on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tabs should navigate the user to the respective screens</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = UNAUTHENTICATED, if user presses any other tab
-1. Block navigation for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Profile
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">2. Store tab pressing intent of user in context </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tabIntent</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = RIDES, BIKES, PROFILE and share globally
-3. navigate the user to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SignIn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen render
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bottomNavTabs render with Explore tab active (MANUAL/e2e TESTING)</t>
-    </r>
-  </si>
-  <si>
-    <t>All tab icons press call mockFunction()</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing Rent a Bike button:
-1. Navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">RenterE-BikeFilter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen
-2. Activates </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing List a Bike button:
-1. Navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">OwnerE-BikeListing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen
-2. Activates </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED and entryIntent = RENT:
-1. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">RenterE-BikeFilter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen
-2. Show "Welcome Username" as heading of the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen
-3. Show "Book an E-Bike" sub-heading under heading
-3. Activate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED and entryIntent = LIST:
-1. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">OwnerE-BikeBooking </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen
-2. Show "Welcome Username" as heading of the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerE-BikeListing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen
-3. Show "Your E-Bikes" as subheading under heading
-4. Activate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If user's authStatus = UNAUTHENTICATED
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">tabs are not pressable (MANUAL/e2e TESTING)
-2. user is navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SignIn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen (MANUAL/e2e TESTING)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If user's authStatus = UNAUTHENTICATED
-Routing logic works with tabs mapped to correct screens:
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - RenterE-BikeFilter
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -  OwnerE-BikeListing
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - ExploreMaps</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Profile
-(MANUAL/e2e TESTING)</t>
-    </r>
-  </si>
-  <si>
-    <t>After successful login (if user's authStatus = AUTHENTICATED) redirect to the intended tab, based on tabIntent</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout
-2. Full Name input
-3. Birth date picker - calendar control
-4. Email input
-5. Terms &amp; Conditions checkbox
-6. Disable Continue button until checkbox checked</t>
-    </r>
-  </si>
-  <si>
-    <t>Client-side validations:
-1. Age &gt; 16 years
-2. Prevent using same email to signup twice</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Create T&amp;C screen layout
-2. Render scrollable content
-3. Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button
-4. Navigate back to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen upon pressing OK button</t>
-    </r>
-  </si>
-  <si>
-    <t>1. Validate image against ID ~ 80%</t>
-  </si>
-  <si>
-    <t>1. Validate image is without hats or glasses
-2. Validate image clarity (no blur or shake)</t>
-  </si>
-  <si>
-    <t>1. Show loading state
-2. Handle backend validation errors (existing email)
-3. Display field entry errors</t>
-  </si>
-  <si>
-    <t>1. Detect entryIntent (RENT/LIST)
-2. Detect tabIntent (RIDES/BIKES/PROFILE)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Renter should be navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout
-2. Show "Welcome Username" as heading of the RenterE-BikeFilter screen
-3. Show "Book an E-Bike" sub-heading under heading
-4. Activate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Lister/Owner should be navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerE-BikeBooking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen
-2. Show "Welcome Username" as heading of the OwnerE-BikeListing screen
-3. Show "Your E-Bikes" as subheading under heading
-4. Activate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. T&amp;C checkbox pressing calls a mockFunction()
-2. Govt. ID &amp; Selfie buttons pressing calls a mockFunction()
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Continue </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pressing calls a mockFunction()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sign Up screen renders
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Full Name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> input field is visible
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date of Birth</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> input field and calendar control is visible
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Email</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> input is visible
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Create Password</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> input is visible
-5. I accept the T&amp;C </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkbox</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is visible
-6. Upload Government ID &amp; Selfie buttons are visible
-7. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Continue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button is visible
-8. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink is visible</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Add ID upload button
-2. Integrate camera
-3. Preview uploaded ID
-4. Handle upload failure
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Retake</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> buttons
-6. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button closes the camera and navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Retake</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button reopens the camera</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Add selfie capture button
-2. Open camera
-3. Capture selfie image
-4. Preview selfie
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Retake</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> buttons
-6.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button closes the camera and navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Retake</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button reopens the camera
-7. Handle upload failure</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. T&amp;C screen navigation and reverse navigation to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen via </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button works
-2. Camera open, close, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Retake</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigations work
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen
-(MANUAL/e2e TESTING)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Auto-login user upon successful sign up
-2. Do not let the user to continue until all details are filled and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">T&amp;C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>is checked</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. ID and Selfie matching accuracy ~ 80% (MANUAL/e2e TESTING)
-2. Sign up attempt with duplicate email does NOT work
-3. Sign up attempt with password length less than 6 characters does NOT work
-4. Sign up attempt without checking in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">T&amp;C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkbox does not work</t>
-    </r>
-  </si>
-  <si>
-    <t>KYC</t>
-  </si>
-  <si>
     <t>Days</t>
   </si>
   <si>
@@ -2375,9 +633,6 @@
     </r>
   </si>
   <si>
-    <t>You do not have an active booking for these dates!</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">1. Design the cards for </t>
     </r>
@@ -3081,6 +1336,183 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">1.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onClick navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-SelectedBike'sOwnerDetails s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">creen
+2.  </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Learn More</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink onClick navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingInsuranceDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+3. Disable onClick of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button until checkbox is not checked
+4. If checked, onClick </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterBookedE-BikesList </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Create </t>
     </r>
     <r>
@@ -3279,7 +1711,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> hyperlink
-5. A chcekbox with "Purchase mandatory </t>
+5. A checkbox with "Purchase mandatory </t>
     </r>
     <r>
       <rPr>
@@ -3313,183 +1745,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>Book</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1.  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Owner's Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> onClick navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBooking-SelectedBike'sOwnerDetails s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">creen
-2.  </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Learn More</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Insurance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink onClick navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingInsuranceDetails</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen
-3. Disable onClick of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button until checkbox is not checked
-4. If checked, onClick </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">RenterBookedE-BikesList </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen</t>
     </r>
   </si>
 </sst>
@@ -3497,7 +1752,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3546,13 +1801,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -3856,6 +2104,78 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3864,78 +2184,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5237,7 +3485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
@@ -5259,7 +3507,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -5271,7 +3519,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>3</v>
@@ -5286,11 +3534,11 @@
         <v>30</v>
       </c>
       <c r="J1" s="5">
-        <f>SUM(J2:J70)</f>
+        <f>SUM(J2:J72)</f>
         <v>102</v>
       </c>
       <c r="K1" s="5">
-        <f>SUM(K2:K70)</f>
+        <f>SUM(K2:K72)</f>
         <v>16</v>
       </c>
       <c r="L1" s="5" t="s">
@@ -5308,18 +3556,18 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C2" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="str" cm="1">
@@ -5330,7 +3578,7 @@
         <f>I2</f>
         <v/>
       </c>
-      <c r="K2" s="65">
+      <c r="K2" s="44">
         <v>16</v>
       </c>
       <c r="L2" s="6" t="s">
@@ -5346,18 +3594,18 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C3" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="str" cm="1">
@@ -5365,10 +3613,10 @@
         <v/>
       </c>
       <c r="J3" s="9" t="str">
-        <f t="shared" ref="J3:J58" si="0">I3</f>
+        <f t="shared" ref="J3:J60" si="0">I3</f>
         <v/>
       </c>
-      <c r="K3" s="66"/>
+      <c r="K3" s="45"/>
       <c r="L3" s="6" t="s">
         <v>27</v>
       </c>
@@ -5382,18 +3630,18 @@
         <v>14</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C4" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6" t="str" cm="1">
@@ -5404,7 +3652,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K4" s="66"/>
+      <c r="K4" s="45"/>
       <c r="L4" s="6" t="s">
         <v>27</v>
       </c>
@@ -5418,18 +3666,18 @@
         <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C5" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6" t="str" cm="1">
@@ -5440,7 +3688,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K5" s="66"/>
+      <c r="K5" s="45"/>
       <c r="L5" s="6" t="s">
         <v>27</v>
       </c>
@@ -5454,18 +3702,18 @@
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C6" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6" t="str" cm="1">
@@ -5476,7 +3724,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K6" s="66"/>
+      <c r="K6" s="45"/>
       <c r="L6" s="6" t="s">
         <v>27</v>
       </c>
@@ -5488,18 +3736,18 @@
         <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C7" s="6">
         <v>1.1000000000000001</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="str" cm="1">
@@ -5510,7 +3758,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K7" s="66"/>
+      <c r="K7" s="45"/>
       <c r="L7" s="6" t="s">
         <v>27</v>
       </c>
@@ -5522,25 +3770,25 @@
         <v>18</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C8" s="9">
         <v>3.1</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="6" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5550,7 +3798,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K8" s="66"/>
+      <c r="K8" s="45"/>
       <c r="L8" s="9" t="s">
         <v>27</v>
       </c>
@@ -5562,25 +3810,25 @@
     <row r="9" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C9" s="9">
         <v>3.1</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="6" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5590,7 +3838,7 @@
         <f>I9</f>
         <v>2</v>
       </c>
-      <c r="K9" s="66"/>
+      <c r="K9" s="45"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
@@ -5598,25 +3846,25 @@
     <row r="10" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C10" s="9">
         <v>3.1</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="6" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5626,7 +3874,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K10" s="66"/>
+      <c r="K10" s="45"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
@@ -5634,25 +3882,25 @@
     <row r="11" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C11" s="9">
         <v>3.1</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="6" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5662,7 +3910,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K11" s="67"/>
+      <c r="K11" s="46"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
@@ -5672,19 +3920,19 @@
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="6" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5702,25 +3950,25 @@
     <row r="13" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C13" s="9">
         <v>3.1</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I13" s="6" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5740,18 +3988,18 @@
         <v>20</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C14" s="11">
         <v>3.2</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11" t="str" cm="1">
@@ -5762,7 +4010,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K14" s="68"/>
+      <c r="K14" s="47"/>
       <c r="L14" s="11" t="s">
         <v>27</v>
       </c>
@@ -5776,18 +4024,18 @@
         <v>21</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C15" s="11">
         <v>3.2</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11" t="str" cm="1">
@@ -5798,7 +4046,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K15" s="69"/>
+      <c r="K15" s="48"/>
       <c r="L15" s="11" t="s">
         <v>27</v>
       </c>
@@ -5812,18 +4060,18 @@
         <v>22</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C16" s="11">
         <v>3.2</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11" t="str" cm="1">
@@ -5834,7 +4082,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K16" s="69"/>
+      <c r="K16" s="48"/>
       <c r="L16" s="11" t="s">
         <v>27</v>
       </c>
@@ -5848,18 +4096,18 @@
         <v>23</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C17" s="11">
         <v>3.2</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="11" t="str" cm="1">
@@ -5870,7 +4118,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K17" s="69"/>
+      <c r="K17" s="48"/>
       <c r="L17" s="11" t="s">
         <v>27</v>
       </c>
@@ -5884,18 +4132,18 @@
         <v>24</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C18" s="11">
         <v>3.2</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11" t="str" cm="1">
@@ -5906,7 +4154,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K18" s="69"/>
+      <c r="K18" s="48"/>
       <c r="L18" s="11" t="s">
         <v>27</v>
       </c>
@@ -5920,18 +4168,18 @@
         <v>25</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C19" s="11">
         <v>3.2</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="11" t="str" cm="1">
@@ -5942,7 +4190,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K19" s="69"/>
+      <c r="K19" s="48"/>
       <c r="L19" s="11" t="s">
         <v>27</v>
       </c>
@@ -5956,18 +4204,18 @@
         <v>26</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C20" s="11">
         <v>3.2</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11" t="str" cm="1">
@@ -5978,7 +4226,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K20" s="69"/>
+      <c r="K20" s="48"/>
       <c r="L20" s="11" t="s">
         <v>27</v>
       </c>
@@ -5992,18 +4240,18 @@
         <v>29</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C21" s="11">
         <v>3.2</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21" s="15"/>
       <c r="G21" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11" t="str" cm="1">
@@ -6014,7 +4262,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K21" s="69"/>
+      <c r="K21" s="48"/>
       <c r="L21" s="11" t="s">
         <v>27</v>
       </c>
@@ -6028,25 +4276,25 @@
         <v>32</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C22" s="12">
         <v>3.2</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I22" s="12" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6056,7 +4304,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K22" s="70"/>
+      <c r="K22" s="49"/>
       <c r="L22" s="12" t="s">
         <v>27</v>
       </c>
@@ -6068,25 +4316,25 @@
     <row r="23" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="12" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C23" s="12">
         <v>3.2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I23" s="12" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6104,11 +4352,13 @@
     <row r="24" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="C24" s="12">
+        <v>3.3</v>
+      </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="13" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
@@ -6120,117 +4370,69 @@
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="17">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="17">
         <v>33</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B27" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="17">
-        <v>1.3</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="18"/>
-      <c r="G25" s="17" t="s">
+      <c r="C27" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I25" s="17" cm="1">
-        <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H27" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="17" cm="1">
+        <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J27" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K25" s="62"/>
-      <c r="L25" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
-        <v>34</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="17">
-        <v>1.3</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" s="17" cm="1">
-        <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J26" s="17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K26" s="63"/>
-      <c r="L26" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
-        <v>36</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="17">
-        <v>1.3</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="17" cm="1">
-        <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J27" s="17">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K27" s="63"/>
+      <c r="K27" s="59"/>
       <c r="L27" s="17" t="s">
         <v>27</v>
       </c>
@@ -6241,26 +4443,20 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="17">
-        <v>1.3</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>42</v>
-      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I28" s="17" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6270,7 +4466,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K28" s="63"/>
+      <c r="K28" s="60"/>
       <c r="L28" s="17" t="s">
         <v>27</v>
       </c>
@@ -6281,26 +4477,20 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="17">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="17">
-        <v>1.3</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>42</v>
-      </c>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="17" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6310,7 +4500,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K29" s="63"/>
+      <c r="K29" s="60"/>
       <c r="L29" s="17" t="s">
         <v>27</v>
       </c>
@@ -6320,97 +4510,101 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="19">
+      <c r="A30" s="17">
+        <v>38</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="17" cm="1">
+        <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K30" s="60"/>
+      <c r="L30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="17">
+        <v>39</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="17" cm="1">
+        <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J31" s="17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K31" s="60"/>
+      <c r="L31" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="19">
         <v>40</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B32" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="53" t="s">
+      <c r="C32" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="I30" s="53" cm="1">
-        <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H32" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="50" cm="1">
+        <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J30" s="53">
+      <c r="J32" s="50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K30" s="63"/>
-      <c r="L30" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="19">
-        <v>41</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="19">
-        <v>43</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="63"/>
+      <c r="K32" s="60"/>
       <c r="L32" s="19" t="s">
         <v>27</v>
       </c>
@@ -6421,26 +4615,20 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>44</v>
-      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="20"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="63"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="60"/>
       <c r="L33" s="19" t="s">
         <v>27</v>
       </c>
@@ -6451,26 +4639,20 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>44</v>
-      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
       <c r="F34" s="20"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="63"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="60"/>
       <c r="L34" s="19" t="s">
         <v>27</v>
       </c>
@@ -6481,26 +4663,20 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>44</v>
-      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
       <c r="F35" s="20"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="63"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="60"/>
       <c r="L35" s="19" t="s">
         <v>27</v>
       </c>
@@ -6511,26 +4687,20 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>44</v>
-      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
       <c r="F36" s="20"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="54"/>
-      <c r="K36" s="63"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="60"/>
       <c r="L36" s="19" t="s">
         <v>27</v>
       </c>
@@ -6541,28 +4711,20 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="19">
-        <v>1.3</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="64"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="60"/>
       <c r="L37" s="19" t="s">
         <v>27</v>
       </c>
@@ -6571,98 +4733,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="19">
+        <v>47</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="19">
+        <v>48</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="21">
         <v>49</v>
       </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21">
-        <v>1.4</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="21" t="s">
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="H38" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="50" cm="1">
-        <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H40" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="62" cm="1">
+        <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J38" s="50">
+      <c r="J40" s="62">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K38" s="50"/>
-      <c r="L38" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="21">
-        <v>50</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21">
-        <v>1.4</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="21">
-        <v>51</v>
-      </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21">
-        <v>1.4</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
+      <c r="K40" s="62"/>
       <c r="L40" s="21" t="s">
         <v>27</v>
       </c>
@@ -6671,28 +4813,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="21">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B41" s="21"/>
-      <c r="C41" s="21">
-        <v>1.4</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="51"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
       <c r="L41" s="21" t="s">
         <v>27</v>
       </c>
@@ -6701,98 +4835,74 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A42" s="23">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="21">
+        <v>51</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
+      <c r="K42" s="63"/>
+      <c r="L42" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M42" s="21"/>
+      <c r="N42" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="21">
+        <v>52</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="63"/>
+      <c r="L43" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="23">
         <v>53</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23">
-        <v>1.4</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42" s="44" t="s">
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="H42" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42" s="44" cm="1">
-        <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H44" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="68" cm="1">
+        <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J42" s="44">
+      <c r="J44" s="68">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K42" s="51"/>
-      <c r="L42" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A43" s="23">
-        <v>54</v>
-      </c>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23">
-        <v>1.4</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="51"/>
-      <c r="L43" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M43" s="23"/>
-      <c r="N43" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="23">
-        <v>55</v>
-      </c>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23">
-        <v>1.4</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="51"/>
+      <c r="K44" s="63"/>
       <c r="L44" s="23" t="s">
         <v>27</v>
       </c>
@@ -6801,30 +4911,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="23">
-        <v>56</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="23">
-        <v>1.4</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F45" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="52"/>
+        <v>54</v>
+      </c>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="63"/>
       <c r="L45" s="23" t="s">
         <v>27</v>
       </c>
@@ -6833,98 +4933,76 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="28">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="23">
+        <v>55</v>
+      </c>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="63"/>
+      <c r="L46" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M46" s="23"/>
+      <c r="N46" s="23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="23">
+        <v>56</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="64"/>
+      <c r="L47" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M47" s="23"/>
+      <c r="N47" s="23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="28">
         <v>57</v>
       </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="D46" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="28" t="s">
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G46" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="H46" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="I46" s="47" cm="1">
-        <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H48" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" s="65" cm="1">
+        <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J46" s="47">
+      <c r="J48" s="65">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K46" s="47"/>
-      <c r="L46" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="28">
-        <v>58</v>
-      </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
-      <c r="L47" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M47" s="28"/>
-      <c r="N47" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="28">
-        <v>59</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="D48" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="K48" s="65"/>
       <c r="L48" s="28" t="s">
         <v>27</v>
       </c>
@@ -6933,28 +5011,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="28">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B49" s="28"/>
-      <c r="C49" s="28">
-        <v>1.5</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E49" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="49"/>
-      <c r="K49" s="48"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+      <c r="K49" s="66"/>
       <c r="L49" s="28" t="s">
         <v>27</v>
       </c>
@@ -6963,240 +5033,168 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A50" s="26">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="28">
+        <v>59</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="66"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="28">
+        <v>60</v>
+      </c>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="67"/>
+      <c r="H51" s="67"/>
+      <c r="I51" s="67"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="66"/>
+      <c r="L51" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="26">
         <v>61</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B52" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="26">
-        <v>1.5</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F50" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G50" s="26" t="s">
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="H50" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I50" s="26" cm="1">
-        <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H52" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="26" cm="1">
+        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J50" s="26">
+      <c r="J52" s="26">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K50" s="48"/>
-      <c r="L50" s="26" t="s">
+      <c r="K52" s="66"/>
+      <c r="L52" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="M50" s="26"/>
-      <c r="N50" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="26">
+      <c r="M52" s="26"/>
+      <c r="N52" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="26">
         <v>62</v>
       </c>
-      <c r="B51" s="26" t="s">
+      <c r="B53" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="26">
-        <v>1.5</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F51" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G51" s="26" t="s">
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="H51" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="26" cm="1">
-        <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H53" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" s="26" cm="1">
+        <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J51" s="26">
+      <c r="J53" s="26">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K51" s="48"/>
-      <c r="L51" s="26" t="s">
+      <c r="K53" s="66"/>
+      <c r="L53" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="M51" s="26"/>
-      <c r="N51" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="26">
+      <c r="M53" s="26"/>
+      <c r="N53" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="26">
         <v>63</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B54" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="26">
-        <v>1.5</v>
-      </c>
-      <c r="D52" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E52" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F52" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G52" s="26" t="s">
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="H52" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="26" cm="1">
-        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H54" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="26" cm="1">
+        <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J52" s="26">
+      <c r="J54" s="26">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K52" s="49"/>
-      <c r="L52" s="26" t="s">
+      <c r="K54" s="67"/>
+      <c r="L54" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="M52" s="26"/>
-      <c r="N52" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" s="16" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="30">
+      <c r="M54" s="26"/>
+      <c r="N54" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="30">
         <v>64</v>
-      </c>
-      <c r="B53" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="30">
-        <v>1.6</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="G53" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H53" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="I53" s="30" cm="1">
-        <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J53" s="30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K53" s="56"/>
-      <c r="L53" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M53" s="30"/>
-      <c r="N53" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="30">
-        <v>65</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="30">
-        <v>1.6</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G54" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H54" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="I54" s="30" cm="1">
-        <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J54" s="30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K54" s="57"/>
-      <c r="L54" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="30">
-        <v>66</v>
       </c>
       <c r="B55" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C55" s="30">
-        <v>1.6</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" s="30" t="s">
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F55" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="G55" s="30" t="s">
-        <v>43</v>
-      </c>
       <c r="H55" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I55" s="30" cm="1">
         <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7206,7 +5204,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K55" s="57"/>
+      <c r="K55" s="53"/>
       <c r="L55" s="30" t="s">
         <v>27</v>
       </c>
@@ -7215,576 +5213,464 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="33">
+    <row r="56" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="30">
+        <v>65</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H56" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="I56" s="30" cm="1">
+        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J56" s="30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K56" s="54"/>
+      <c r="L56" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M56" s="30"/>
+      <c r="N56" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="30">
+        <v>66</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="30" cm="1">
+        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J57" s="30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K57" s="54"/>
+      <c r="L57" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="33">
         <v>68</v>
       </c>
-      <c r="B56" s="33" t="s">
+      <c r="B58" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D56" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E56" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="G56" s="33" t="s">
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H56" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="I56" s="33" cm="1">
-        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H58" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I58" s="33" cm="1">
+        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J58" s="33">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K56" s="57"/>
-      <c r="L56" s="33" t="s">
+      <c r="K58" s="54"/>
+      <c r="L58" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M56" s="33"/>
-      <c r="N56" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="33">
+      <c r="M58" s="33"/>
+      <c r="N58" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="33">
         <v>69</v>
       </c>
-      <c r="B57" s="33" t="s">
+      <c r="B59" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D57" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F57" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G57" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="H57" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="I57" s="33" cm="1">
-        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I59" s="33" cm="1">
+        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J59" s="33">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K57" s="57"/>
-      <c r="L57" s="33" t="s">
+      <c r="K59" s="54"/>
+      <c r="L59" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M57" s="33"/>
-      <c r="N57" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="33">
+      <c r="M59" s="33"/>
+      <c r="N59" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="33">
         <v>70</v>
       </c>
-      <c r="B58" s="33" t="s">
+      <c r="B60" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D58" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E58" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="G58" s="33" t="s">
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H58" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58" s="33" cm="1">
-        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H60" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I60" s="33" cm="1">
+        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J58" s="33">
+      <c r="J60" s="33">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K58" s="57"/>
-      <c r="L58" s="33" t="s">
+      <c r="K60" s="54"/>
+      <c r="L60" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M58" s="33"/>
-      <c r="N58" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33">
+      <c r="M60" s="33"/>
+      <c r="N60" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="33">
         <v>71</v>
       </c>
-      <c r="B59" s="33" t="s">
+      <c r="B61" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D59" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="G59" s="33" t="s">
+      <c r="C61" s="33"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="33"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H59" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" s="33" cm="1">
-        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H61" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="33" cm="1">
+        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J59" s="33">
-        <f t="shared" ref="J59:J75" si="1">I59</f>
+      <c r="J61" s="33">
+        <f t="shared" ref="J61:J77" si="1">I61</f>
         <v>2</v>
       </c>
-      <c r="K59" s="57"/>
-      <c r="L59" s="33" t="s">
+      <c r="K61" s="54"/>
+      <c r="L61" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M59" s="33"/>
-      <c r="N59" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="33">
+      <c r="M61" s="33"/>
+      <c r="N61" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="33">
         <v>76</v>
       </c>
-      <c r="B60" s="33" t="s">
+      <c r="B62" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D60" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E60" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F60" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="G60" s="33" t="s">
+      <c r="C62" s="33"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H60" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="I60" s="33" cm="1">
-        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H62" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="I62" s="33" cm="1">
+        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J62" s="33">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K60" s="57"/>
-      <c r="L60" s="33" t="s">
+      <c r="K62" s="54"/>
+      <c r="L62" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M60" s="33"/>
-      <c r="N60" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="33">
+      <c r="M62" s="33"/>
+      <c r="N62" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="33">
         <v>77</v>
       </c>
-      <c r="B61" s="33" t="s">
+      <c r="B63" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D61" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="G61" s="33" t="s">
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H61" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="I61" s="33" cm="1">
-        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H63" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" s="33" cm="1">
+        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J61" s="33">
+      <c r="J63" s="33">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K61" s="57"/>
-      <c r="L61" s="33" t="s">
+      <c r="K63" s="54"/>
+      <c r="L63" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M61" s="33"/>
-      <c r="N61" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="33">
+      <c r="M63" s="33"/>
+      <c r="N63" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="33">
         <v>78</v>
       </c>
-      <c r="B62" s="33" t="s">
+      <c r="B64" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D62" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E62" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F62" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="G62" s="33" t="s">
+      <c r="C64" s="33"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H62" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="I62" s="33" cm="1">
-        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H64" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I64" s="33" cm="1">
+        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J64" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K62" s="57"/>
-      <c r="L62" s="33" t="s">
+      <c r="K64" s="54"/>
+      <c r="L64" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M62" s="33"/>
-      <c r="N62" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="33">
+      <c r="M64" s="33"/>
+      <c r="N64" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="33">
         <v>79</v>
       </c>
-      <c r="B63" s="33" t="s">
+      <c r="B65" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C63" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D63" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E63" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F63" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="G63" s="33" t="s">
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H63" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="I63" s="33" cm="1">
-        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H65" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I65" s="33" cm="1">
+        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J65" s="33">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K63" s="57"/>
-      <c r="L63" s="33" t="s">
+      <c r="K65" s="54"/>
+      <c r="L65" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M63" s="33"/>
-      <c r="N63" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33">
+      <c r="M65" s="33"/>
+      <c r="N65" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="33">
         <v>80</v>
       </c>
-      <c r="B64" s="33" t="s">
+      <c r="B66" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D64" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E64" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="G64" s="33" t="s">
+      <c r="C66" s="33"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H64" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="I64" s="33" cm="1">
-        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H66" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" s="33" cm="1">
+        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J64" s="33">
+      <c r="J66" s="33">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K64" s="57"/>
-      <c r="L64" s="33" t="s">
+      <c r="K66" s="54"/>
+      <c r="L66" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M64" s="33"/>
-      <c r="N64" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33">
+      <c r="M66" s="33"/>
+      <c r="N66" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="33">
         <v>81</v>
       </c>
-      <c r="B65" s="33" t="s">
+      <c r="B67" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="33">
-        <v>1.6</v>
-      </c>
-      <c r="D65" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="E65" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F65" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G65" s="33" t="s">
+      <c r="C67" s="33"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="33"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H65" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I65" s="33" cm="1">
-        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H67" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="33" cm="1">
+        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J67" s="33">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K65" s="58"/>
-      <c r="L65" s="33" t="s">
+      <c r="K67" s="55"/>
+      <c r="L67" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="M65" s="33"/>
-      <c r="N65" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="30">
+      <c r="M67" s="33"/>
+      <c r="N67" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="30">
         <v>67</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B68" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="37">
-        <v>1.7</v>
-      </c>
-      <c r="D66" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="E66" s="37" t="s">
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="F66" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="I66" s="37" cm="1">
-        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H68" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="I68" s="37" cm="1">
+        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J66" s="37">
-        <f>I66</f>
+      <c r="J68" s="37">
+        <f>I68</f>
         <v>1</v>
       </c>
-      <c r="K66" s="59"/>
-      <c r="L66" s="37" t="s">
+      <c r="K68" s="56"/>
+      <c r="L68" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M66" s="37"/>
-      <c r="N66" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="33">
-        <v>72</v>
-      </c>
-      <c r="B67" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="35">
-        <v>1.7</v>
-      </c>
-      <c r="D67" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E67" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="F67" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="G67" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="I67" s="35" cm="1">
-        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J67" s="35">
-        <f>I67</f>
-        <v>8</v>
-      </c>
-      <c r="K67" s="60"/>
-      <c r="L67" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M67" s="35"/>
-      <c r="N67" s="35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="33">
-        <v>73</v>
-      </c>
-      <c r="B68" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="35">
-        <v>1.7</v>
-      </c>
-      <c r="D68" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E68" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="G68" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="I68" s="35" cm="1">
-        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J68" s="35">
-        <f>I68</f>
-        <v>5</v>
-      </c>
-      <c r="K68" s="60"/>
-      <c r="L68" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M68" s="35"/>
-      <c r="N68" s="35" t="s">
+      <c r="M68" s="37"/>
+      <c r="N68" s="37" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="33">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B69" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="35">
-        <v>1.7</v>
-      </c>
-      <c r="D69" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E69" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="F69" s="36" t="s">
-        <v>68</v>
-      </c>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="36"/>
       <c r="G69" s="35" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H69" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I69" s="35" cm="1">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7794,7 +5680,7 @@
         <f>I69</f>
         <v>8</v>
       </c>
-      <c r="K69" s="60"/>
+      <c r="K69" s="57"/>
       <c r="L69" s="35" t="s">
         <v>27</v>
       </c>
@@ -7803,28 +5689,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="33">
-        <v>75</v>
-      </c>
-      <c r="B70" s="33"/>
-      <c r="C70" s="35">
-        <v>1.7</v>
-      </c>
-      <c r="D70" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E70" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="F70" s="36" t="s">
-        <v>69</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B70" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="36"/>
       <c r="G70" s="35" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H70" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I70" s="35" cm="1">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7834,7 +5714,7 @@
         <f>I70</f>
         <v>5</v>
       </c>
-      <c r="K70" s="61"/>
+      <c r="K70" s="57"/>
       <c r="L70" s="35" t="s">
         <v>27</v>
       </c>
@@ -7844,60 +5724,74 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
-        <v>82</v>
-      </c>
-      <c r="B71" s="2" t="s">
+      <c r="A71" s="33">
+        <v>74</v>
+      </c>
+      <c r="B71" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2" t="str" cm="1">
+      <c r="C71" s="35"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="35"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="H71" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="I71" s="35" cm="1">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K71" s="32"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="J71" s="35">
+        <f>I71</f>
+        <v>8</v>
+      </c>
+      <c r="K71" s="57"/>
+      <c r="L71" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="M71" s="35"/>
+      <c r="N71" s="35" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>83</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2" t="str" cm="1">
+      <c r="A72" s="33">
+        <v>75</v>
+      </c>
+      <c r="B72" s="33"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="I72" s="35" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J72" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K72" s="32"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="J72" s="35">
+        <f>I72</f>
+        <v>5</v>
+      </c>
+      <c r="K72" s="58"/>
+      <c r="L72" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="M72" s="35"/>
+      <c r="N72" s="35" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>7</v>
@@ -7923,7 +5817,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>7</v>
@@ -7949,7 +5843,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>7</v>
@@ -7973,29 +5867,81 @@
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
     </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>85</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2" t="str" cm="1">
+        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K76" s="32"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>86</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2" t="str" cm="1">
+        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K77" s="32"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="J30:J37"/>
-    <mergeCell ref="K53:K65"/>
-    <mergeCell ref="K66:K70"/>
-    <mergeCell ref="K25:K37"/>
-    <mergeCell ref="K38:K45"/>
-    <mergeCell ref="K46:K52"/>
-    <mergeCell ref="J42:J45"/>
-    <mergeCell ref="G46:G49"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="I46:I49"/>
-    <mergeCell ref="J46:J49"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="I42:I45"/>
-    <mergeCell ref="H38:H41"/>
-    <mergeCell ref="I38:I41"/>
-    <mergeCell ref="G38:G41"/>
-    <mergeCell ref="J38:J41"/>
-    <mergeCell ref="G30:G37"/>
-    <mergeCell ref="H30:H37"/>
-    <mergeCell ref="I30:I37"/>
+    <mergeCell ref="H40:H43"/>
+    <mergeCell ref="I40:I43"/>
+    <mergeCell ref="G40:G43"/>
+    <mergeCell ref="J40:J43"/>
+    <mergeCell ref="G32:G39"/>
+    <mergeCell ref="H32:H39"/>
+    <mergeCell ref="I32:I39"/>
+    <mergeCell ref="G48:G51"/>
+    <mergeCell ref="H48:H51"/>
+    <mergeCell ref="I48:I51"/>
+    <mergeCell ref="J48:J51"/>
+    <mergeCell ref="G44:G47"/>
+    <mergeCell ref="H44:H47"/>
+    <mergeCell ref="I44:I47"/>
+    <mergeCell ref="J32:J39"/>
+    <mergeCell ref="K55:K67"/>
+    <mergeCell ref="K68:K72"/>
+    <mergeCell ref="K27:K39"/>
+    <mergeCell ref="K40:K47"/>
+    <mergeCell ref="K48:K54"/>
+    <mergeCell ref="J44:J47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8015,16 +5961,16 @@
   <sheetData>
     <row r="1" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -8247,7 +6193,7 @@
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">

--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DD5895-2F2E-4058-B90E-ECBEB22A1300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D841FD3A-1A1E-4B56-AB28-FE0AD603FB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-72" yWindow="0" windowWidth="11928" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="92">
   <si>
     <t>Epic</t>
   </si>
@@ -79,9 +79,6 @@
     <t>Blocker / Notes</t>
   </si>
   <si>
-    <t>Auth</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
     <t>Scope</t>
   </si>
   <si>
-    <t>Task #</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -209,336 +203,6 @@
   </si>
   <si>
     <t>Marketplace-Renting</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen component/layout:
-1. Heading: "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Welcome username</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"
-2. Subheading: "B</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ook an E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>From</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> DatePicker and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>To</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> DatePicker
-4. Price Range (per week)
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Category</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> box with dropdown for bike types
-6. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup Location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Location Picker
-7. Style </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Continue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button as primary
-8. Style </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Visit My Bookings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button as secondary
-9. Navigate from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBooking-BikeDetails</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Continue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button press
-10. Navigate from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedBikesList</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Visit My Bookings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button press</t>
-    </r>
   </si>
   <si>
     <r>
@@ -830,58 +494,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. Accept filter values from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen
-2. Fetch / mock list of available e-bikes
-3. Apply filters to e-bike dataset
-4. Sort matching bikes in ascending order of price
-5. Identify cheapest bike from filtered results
-6. If no results, show message: “</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No E-Bikes found! Consider increasing your budget.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>”</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">1. Create </t>
     </r>
     <r>
@@ -1254,81 +866,6 @@
       </rPr>
       <t xml:space="preserve">button to the highlighted bike
 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Render remaining bikes as list of clickable cards, under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Similar E-Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> subheading
-2. Ensure list order: cheapest → costliest
-3. Ensure scrollable list behavior
-4. Handle loading state (skeleton)
-5. Detect no-results condition
-6. If no more filtered matching bikes to show in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Similar E-Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> list:
-- Display: "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Increase your budget to discover more amazing E-Bikes!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"
-- Disable scroll of the list view</t>
     </r>
   </si>
   <si>
@@ -1747,12 +1284,2560 @@
       <t>Book</t>
     </r>
   </si>
+  <si>
+    <t>RenterE-BikeBooking-SelectedBike'sOwnerDetails</t>
+  </si>
+  <si>
+    <t>RenterE-BikeBookingInsuranceDetails</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen component/layout, create:
+1. Heading: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Welcome username</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+2. Subheading: "B</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ook an E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+3. Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Date picker with validation (cannot select past dates) &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Date picker with validation (&gt;= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Date).
+4. Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price Range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> slider (per week) with min/max labels.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> box with dropdown for bike types (enum)
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup Location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Location Picker
+7. Persist filter state locally while navigating.
+8. Style </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Continue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button as primary
+9. Style </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Visit My Bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button as secondary
+10. Navigate from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-BikeDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Continue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button press
+11. Navigate from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Visit My Bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button press</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Accept filter values (dates, price, category, location) from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+2. Fetch / mock list of available e-bikes
+3. Apply filters to e-bike dataset
+4. Sort matching bikes in ascending order of weekly price
+5. Identify cheapest bike from filtered results
+6. If no results, show message: “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No E-Bikes found! Consider increasing your budget.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-SelectedBike'sOwnerDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen component/layout:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1. Fetch and render the selected E-Bike's  owner's name as heading
+2. Render owner's image as avatar
+3. Render a text field for the user to type something </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;=200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> characters
+4. Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bikes Listed: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">section that displays the number of bikes listed by owner
+5. Rating and no. of ratings
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Community Activities</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink navigates to the owner's community </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">activities
+7. Render an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button that navigates back to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+TO BE JUST AN EMPTY SCREEN WITH THE Ok BUTTON UNTIL FINALIZED</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingInsuranceDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen component/layout:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1. Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as heading
+2. Render the whole insurance document inside a scrollable iist component.
+3. Render an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button that navigates back to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>Backend Dev</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /api/users/{ownerId}/public-profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Logic: Query user table for public fields only.
+2. Output: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>avatarUrl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bikesListedCount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (aggregate query), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>communityProfileUrl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /api/content/insurance-policy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint:
+1. Logic: Fetch the current active insurance policy text/HTML from a CMS or config file (allows updating policy without app store releases).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Create</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> GET /api/bikes/search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Input (Query Params): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>startDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>endDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>maxPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e-bike type), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (lat/long or cityId).
+2. Logic:
+- Filter bikes by availability (exclude bikes booked during startDate to endDate).
+- Filter by price range and category.
+- Sorting: Implement strict SQL sorting: ORDER BY price ASC.
+3. Output: List of Bike objects (thumbnail, name, price, rating).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /api/bikes/{id} Endpoint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Logic: Fetch full details for a specific bike.
+2. Output: Detailed JSON including specifications, full image URLs, and nested owner summary object.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RenterBookedBikesList </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If the Purchase mandatory insurance checkbox is checked, pressing Book button navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen. If not, alert: Purchase the insurance to continue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Render e-bikes filtered by the date entered in list of clickable cards with E-bike </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Circular thumbnail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the E-Bike, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date Range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, E-bike </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the cards</t>
+    </r>
+  </si>
+  <si>
+    <t>Render "You do not have an active booking for these dates!" instead of the list of scrollable cards, if no results found</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Input: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bikeId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renterId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>startDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>endDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>insuranceAccepted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (boolean).
+2. Logic:
+- Race Condition Check: Verify bike is still available for dates (lock row).
+- Validation: Ensure insuranceAccepted is true.
+- Transaction: Create Booking record with status CONFIRMED.
+3.Output: bookingId, status.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /api/bookings/my-bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Logic: Fetch all bookings for the authenticated renter.
+2. Sorting: Sort by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>startDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> descending (newest/upcoming first).
+3. Output: List of bookings with attached Bike metadata.</t>
+    </r>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>RenterBookedBikesList</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Render heading: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Welcome John</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+2. Render sub-heading: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Your Bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+3. Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Date picker with validation (cannot select past dates) &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Date picker with validation (&gt;= From Date).
+4. Render the user's e-bikes in a list of clickable cards
+5. Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book an E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button
+6. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book an E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen onPress of listed cards, showing the details of respective e-bike</t>
+    </r>
+  </si>
+  <si>
+    <t>RenterBookedE-BikeOptions</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Render the booked E-Bike's 
+- enlarged image as the card's background image (occupying 100% of the card)
+- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, E-bike </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of booking (From-To) of the cheapest e-bike under the card
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeCancellationOption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <t>RenterBookedE-BikeCancellationOption</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeCancellationOption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Render the booked E-Bike's 
+- enlarged image as the card's background image (occupying 100% of the card)
+- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
+2. Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancellation Charge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return Amount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (price - cancellation charge)
+3. Cancellation policy in a scrollable content with a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Read more </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">hyperlink
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Confirm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> secondary button
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Do Not Cancel, Go Back </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>primary button</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Confirm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button onPress initiates cancellation (no function for now, (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alert("Cancellation Confirmed")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Do Not Cancel, Go Back</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button onPress navigates back to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /api/bookings/{id}/cancellation-quote</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint:
+1. Logic: Calculate refund based on policy:
+- If &gt;24h before: 100% refund.
+- If &lt;24h before: X% penalty.
+- If Mid-ride (User Story 3.13): Calculate pro-rated usage + penalty.
+2. Output: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>refundAmount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cancellationFee</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>totalPaid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings/{id}/cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Input: reason (optional).
+2. Logic: Update status to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CANCELLED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, trigger Refund Service.</t>
+    </r>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings/{id}/issues</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Type: Multipart/Form-Data.
+2. Input: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>imageFile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Pre-ride vs Mid-ride).
+3. Logic: Upload image to storage (S3/Cloudinary), save URL, create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> record linked to booking.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings/{id}/start-ride</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Logic: Validate booking is today. Update status to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Start "Ride Timer" (if applicable).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Create</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> POST /api/incidents</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Type: Multipart/Form-Data.
+2. Logic: High-priority alert. Store incident report, trigger email/SMS to Support Team.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings/{id}/return-completion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Type: Multipart/Form-Data.
+2. Input:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returnImage, rating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (1-5), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reviewComment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. Logic:
+- Upload return proof image.
+- Update booking status to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>COMPLETED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- Update Bike Owner's aggregate rating.
+- Trigger "Successfully Returned!" notification to Owner.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1810,6 +3895,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1977,12 +4084,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2104,49 +4208,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2155,7 +4217,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2183,6 +4251,60 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3485,2463 +5607,2482 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="80.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="11.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="80.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="4">
+        <f>SUM(I2:I45)</f>
+        <v>42</v>
+      </c>
+      <c r="J1" s="4">
+        <f>SUM(J2:J45)</f>
+        <v>16</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="str" cm="1">
+        <f t="array" ref="H2">_xlfn.SWITCH(G2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I2" s="8" t="str">
+        <f>H2</f>
+        <v/>
+      </c>
+      <c r="J2" s="67">
+        <v>16</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="5">
-        <f>SUM(J2:J72)</f>
-        <v>102</v>
-      </c>
-      <c r="K1" s="5">
-        <f>SUM(K2:K72)</f>
-        <v>16</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6" t="str" cm="1">
-        <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="E3" s="6"/>
+      <c r="F3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="str" cm="1">
+        <f t="array" ref="H3">_xlfn.SWITCH(G3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J2" s="9" t="str">
-        <f>I2</f>
+      <c r="I3" s="8" t="str">
+        <f t="shared" ref="I3:I39" si="0">H3</f>
         <v/>
       </c>
-      <c r="K2" s="44">
-        <v>16</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
-        <v>13</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="str" cm="1">
-        <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="J3" s="41"/>
+      <c r="K3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="str" cm="1">
+        <f t="array" ref="H4">_xlfn.SWITCH(G4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J3" s="9" t="str">
-        <f t="shared" ref="J3:J60" si="0">I3</f>
-        <v/>
-      </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>14</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="str" cm="1">
-        <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="9" t="str">
+      <c r="I4" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K4" s="45"/>
-      <c r="L4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>15</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6" t="str" cm="1">
-        <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="J4" s="41"/>
+      <c r="K4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="str" cm="1">
+        <f t="array" ref="H5">_xlfn.SWITCH(G5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J5" s="9" t="str">
+      <c r="I5" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K5" s="45"/>
-      <c r="L5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="str" cm="1">
-        <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="J5" s="41"/>
+      <c r="K5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="str" cm="1">
+        <f t="array" ref="H6">_xlfn.SWITCH(G6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J6" s="9" t="str">
+      <c r="I6" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K6" s="45"/>
-      <c r="L6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6" t="str" cm="1">
-        <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="J6" s="41"/>
+      <c r="K6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+    </row>
+    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="str" cm="1">
+        <f t="array" ref="H7">_xlfn.SWITCH(G7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J7" s="9" t="str">
+      <c r="I7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K7" s="45"/>
-      <c r="L7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
-        <v>18</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="9">
+      <c r="J7" s="41"/>
+      <c r="K7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+    </row>
+    <row r="8" spans="1:13" ht="216" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="8">
         <v>3.1</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>48</v>
+      <c r="C8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="6" cm="1">
-        <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>58</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="5" cm="1">
+        <f t="array" ref="H8">_xlfn.SWITCH(G8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J8" s="9">
+      <c r="I8" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9" t="s">
+      <c r="J8" s="41"/>
+      <c r="K8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="9">
+      <c r="G9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="5" cm="1">
+        <f t="array" ref="H9">_xlfn.SWITCH(G9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I9" s="8">
+        <f>H9</f>
+        <v>2</v>
+      </c>
+      <c r="J9" s="41"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="8">
         <v>3.1</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="6" cm="1">
-        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="5" cm="1">
+        <f t="array" ref="H10">_xlfn.SWITCH(G10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J9" s="9">
-        <f>I9</f>
-        <v>2</v>
-      </c>
-      <c r="K9" s="45"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="6" cm="1">
-        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J10" s="9">
+      <c r="I10" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K10" s="45"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="9">
+      <c r="J10" s="41"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="8">
         <v>3.1</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>49</v>
+      <c r="C11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="6" cm="1">
-        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>52</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="5" cm="1">
+        <f t="array" ref="H11">_xlfn.SWITCH(G11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J11" s="9">
+      <c r="I11" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K11" s="46"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-    </row>
-    <row r="12" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
-        <v>49</v>
+      <c r="J11" s="68"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="6" cm="1">
-        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>50</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="5" cm="1">
+        <f t="array" ref="H12">_xlfn.SWITCH(G12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J12" s="9">
+      <c r="I12" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K12" s="42"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>43</v>
-      </c>
+      <c r="J12" s="41"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="13"/>
       <c r="F13" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="6" cm="1">
-        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J13" s="9">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K13" s="42"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="11">
-        <v>20</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="11">
-        <v>3.2</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11" t="str" cm="1">
-        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>40</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10" t="str" cm="1">
+        <f t="array" ref="H13">_xlfn.SWITCH(G13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J14" s="11" t="str">
+      <c r="I13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K14" s="47"/>
-      <c r="L14" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <v>21</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="11">
+      <c r="J13" s="69"/>
+      <c r="K13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="10">
         <v>3.2</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11" t="str" cm="1">
-        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="str" cm="1">
+        <f t="array" ref="H14">_xlfn.SWITCH(G14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J15" s="11" t="str">
+      <c r="I14" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="11">
-        <v>22</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="11">
+      <c r="J14" s="42"/>
+      <c r="K14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="10">
         <v>3.2</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11" t="str" cm="1">
-        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10" t="str" cm="1">
+        <f t="array" ref="H15">_xlfn.SWITCH(G15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J16" s="11" t="str">
+      <c r="I15" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K16" s="48"/>
-      <c r="L16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
-        <v>23</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="11">
+      <c r="J15" s="42"/>
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="10">
         <v>3.2</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11" t="str" cm="1">
-        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10" t="str" cm="1">
+        <f t="array" ref="H16">_xlfn.SWITCH(G16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J17" s="11" t="str">
+      <c r="I16" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
-        <v>24</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="11">
+      <c r="J16" s="42"/>
+      <c r="K16" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="10">
         <v>3.2</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11" t="str" cm="1">
-        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="str" cm="1">
+        <f t="array" ref="H17">_xlfn.SWITCH(G17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J18" s="11" t="str">
+      <c r="I17" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K18" s="48"/>
-      <c r="L18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="11">
-        <v>25</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="11">
+      <c r="J17" s="42"/>
+      <c r="K17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="10">
         <v>3.2</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11" t="str" cm="1">
-        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10" t="str" cm="1">
+        <f t="array" ref="H18">_xlfn.SWITCH(G18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J19" s="11" t="str">
+      <c r="I18" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K19" s="48"/>
-      <c r="L19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="11">
+      <c r="J18" s="42"/>
+      <c r="K18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="11">
+      <c r="L18" s="10"/>
+      <c r="M18" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="10">
         <v>3.2</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11" t="str" cm="1">
-        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10" t="str" cm="1">
+        <f t="array" ref="H19">_xlfn.SWITCH(G19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J20" s="11" t="str">
+      <c r="I19" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K20" s="48"/>
-      <c r="L20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
-        <v>29</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="11">
+      <c r="J19" s="42"/>
+      <c r="K19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="10">
         <v>3.2</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11" t="str" cm="1">
-        <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10" t="str" cm="1">
+        <f t="array" ref="H20">_xlfn.SWITCH(G20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J21" s="11" t="str">
+      <c r="I20" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="K21" s="48"/>
-      <c r="L21" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11" t="s">
+      <c r="J20" s="42"/>
+      <c r="K20" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12">
-        <v>32</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" s="12" cm="1">
-        <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="G21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="11" cm="1">
+        <f t="array" ref="H21">_xlfn.SWITCH(G21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J22" s="12">
+      <c r="I21" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K22" s="49"/>
-      <c r="L22" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12" t="s">
+      <c r="J21" s="70"/>
+      <c r="K21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I23" s="12" cm="1">
-        <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="G22" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="11" cm="1">
+        <f t="array" ref="H22">_xlfn.SWITCH(G22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J23" s="12">
+      <c r="I22" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K23" s="43"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12">
-        <v>3.3</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12">
-        <v>3.4</v>
-      </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12">
-        <v>3.4</v>
-      </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
-        <v>33</v>
-      </c>
-      <c r="B27" s="17" t="s">
+      <c r="J22" s="42"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="17">
-        <v>3.5</v>
-      </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="17" cm="1">
-        <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J27" s="17">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K27" s="59"/>
-      <c r="L27" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17" t="s">
+    </row>
+    <row r="23" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
-        <v>34</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I28" s="17" cm="1">
-        <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="G23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="11" cm="1">
+        <f t="array" ref="H23">_xlfn.SWITCH(G23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J28" s="17">
+      <c r="I23" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K28" s="60"/>
-      <c r="L28" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="17">
-        <v>36</v>
-      </c>
-      <c r="B29" s="17" t="s">
+      <c r="J23" s="64"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="17" cm="1">
-        <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+    </row>
+    <row r="24" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="31"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="31" cm="1">
+        <f t="array" ref="H24">_xlfn.SWITCH(G24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J29" s="17">
+      <c r="I24" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K29" s="60"/>
-      <c r="L29" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="17">
-        <v>38</v>
-      </c>
-      <c r="B30" s="17" t="s">
+      <c r="J24" s="66"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" s="17" cm="1">
-        <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+    </row>
+    <row r="25" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="31"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="31" cm="1">
+        <f t="array" ref="H25">_xlfn.SWITCH(G25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J30" s="17">
+      <c r="I25" s="31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K30" s="60"/>
-      <c r="L30" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17" t="s">
+      <c r="J25" s="66"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="17">
+      <c r="G26" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="16" cm="1">
+        <f t="array" ref="H26">_xlfn.SWITCH(G26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I26" s="16">
+        <f>H26</f>
+        <v>3</v>
+      </c>
+      <c r="J26" s="44"/>
+      <c r="K26" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="E27" s="17"/>
+      <c r="F27" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="16" cm="1">
+        <f t="array" ref="H27">_xlfn.SWITCH(G27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I27" s="16">
+        <f>H27</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="45"/>
+      <c r="K27" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="17" cm="1">
-        <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+    </row>
+    <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="16" cm="1">
+        <f t="array" ref="H28">_xlfn.SWITCH(G28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J31" s="17">
+      <c r="I28" s="16">
+        <f>H28</f>
+        <v>2</v>
+      </c>
+      <c r="J28" s="45"/>
+      <c r="K28" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" s="16" cm="1">
+        <f t="array" ref="H29">_xlfn.SWITCH(G29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I29" s="16">
+        <f>H29</f>
+        <v>1</v>
+      </c>
+      <c r="J29" s="45"/>
+      <c r="K29" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="16" cm="1">
+        <f t="array" ref="H30">_xlfn.SWITCH(G30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I30" s="16">
+        <f>H30</f>
+        <v>2</v>
+      </c>
+      <c r="J30" s="45"/>
+      <c r="K30" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="18">
+        <v>3.3</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18" t="str" cm="1">
+        <f t="array" ref="H31">_xlfn.SWITCH(G31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="18"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A32" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="18">
+        <v>3.4</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18" t="str" cm="1">
+        <f t="array" ref="H32">_xlfn.SWITCH(G32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="18"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="15" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="31"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="15" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="31"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="65" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="66"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="49" cm="1">
+        <f t="array" ref="H35">_xlfn.SWITCH(G35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I35" s="49">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K31" s="60"/>
-      <c r="L31" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="19">
-        <v>40</v>
-      </c>
-      <c r="B32" s="19" t="s">
+      <c r="J35" s="49"/>
+      <c r="K35" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="19">
-        <v>3.5</v>
-      </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="50" cm="1">
-        <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J32" s="50">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K32" s="60"/>
-      <c r="L32" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="19">
-        <v>41</v>
-      </c>
-      <c r="B33" s="19" t="s">
+    </row>
+    <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="60"/>
-      <c r="L33" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="19">
-        <v>43</v>
-      </c>
-      <c r="B34" s="19" t="s">
+    </row>
+    <row r="37" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="21"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="51"/>
-      <c r="K34" s="60"/>
-      <c r="L34" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="19">
-        <v>44</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="60"/>
-      <c r="L35" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="19">
-        <v>45</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="60"/>
-      <c r="L36" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="19">
-        <v>46</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="60"/>
-      <c r="L37" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="19">
-        <v>47</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="20"/>
+    </row>
+    <row r="38" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="51"/>
       <c r="G38" s="51"/>
       <c r="H38" s="51"/>
       <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="60"/>
-      <c r="L38" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19" t="s">
+      <c r="J38" s="50"/>
+      <c r="K38" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="22">
+        <v>3.5</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="55" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="19">
+      <c r="G39" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="55" cm="1">
+        <f t="array" ref="H39">_xlfn.SWITCH(G39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I39" s="55">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="J39" s="50"/>
+      <c r="K39" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B40" s="22">
+        <v>3.5</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="21">
-        <v>49</v>
-      </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="62" t="s">
+    </row>
+    <row r="41" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="22">
+        <v>3.6</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="22">
+        <v>3.7</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22">
+        <v>3.8</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
+    </row>
+    <row r="44" spans="1:13" s="15" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H44" s="22" cm="1">
+        <f t="array" ref="H44">_xlfn.SWITCH(G44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I44" s="22">
+        <f t="shared" ref="I44:I47" si="1">H44</f>
+        <v>2</v>
+      </c>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="15" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H45" s="22" cm="1">
+        <f t="array" ref="H45">_xlfn.SWITCH(G45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I45" s="22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
+      <c r="M45" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="28"/>
+      <c r="F46" s="72" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="I40" s="62" cm="1">
-        <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J40" s="62">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K40" s="62"/>
-      <c r="L40" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="21">
-        <v>50</v>
-      </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="63"/>
-      <c r="J41" s="63"/>
-      <c r="K41" s="63"/>
-      <c r="L41" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M41" s="21"/>
-      <c r="N41" s="21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="21">
-        <v>51</v>
-      </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="63"/>
-      <c r="H42" s="63"/>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
-      <c r="K42" s="63"/>
-      <c r="L42" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M42" s="21"/>
-      <c r="N42" s="21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="21">
-        <v>52</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="64"/>
-      <c r="J43" s="64"/>
-      <c r="K43" s="63"/>
-      <c r="L43" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M43" s="21"/>
-      <c r="N43" s="21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="23">
-        <v>53</v>
-      </c>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="68" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="68" cm="1">
-        <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H46" s="72" cm="1">
+        <f t="array" ref="H46">_xlfn.SWITCH(G46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J44" s="68">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K44" s="63"/>
-      <c r="L44" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M44" s="23"/>
-      <c r="N44" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="23">
-        <v>54</v>
-      </c>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="69"/>
-      <c r="K45" s="63"/>
-      <c r="L45" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="23">
-        <v>55</v>
-      </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="63"/>
-      <c r="L46" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="23">
-        <v>56</v>
-      </c>
-      <c r="B47" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70"/>
-      <c r="K47" s="64"/>
-      <c r="L47" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="28">
-        <v>57</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="H48" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" s="65" cm="1">
-        <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J48" s="65">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K48" s="65"/>
-      <c r="L48" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M48" s="28"/>
-      <c r="N48" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="28">
-        <v>58</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="66"/>
-      <c r="H49" s="66"/>
-      <c r="I49" s="66"/>
-      <c r="J49" s="66"/>
-      <c r="K49" s="66"/>
-      <c r="L49" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="28">
-        <v>59</v>
-      </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="66"/>
-      <c r="H50" s="66"/>
-      <c r="I50" s="66"/>
-      <c r="J50" s="66"/>
-      <c r="K50" s="66"/>
-      <c r="L50" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M50" s="28"/>
-      <c r="N50" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="28">
-        <v>60</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="67"/>
-      <c r="H51" s="67"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="67"/>
-      <c r="K51" s="66"/>
-      <c r="L51" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="26">
-        <v>61</v>
-      </c>
-      <c r="B52" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="H52" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="26" cm="1">
-        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J52" s="26">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K52" s="66"/>
-      <c r="L52" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="M52" s="26"/>
-      <c r="N52" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="26">
-        <v>62</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" s="26" cm="1">
-        <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J53" s="26">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K53" s="66"/>
-      <c r="L53" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="M53" s="26"/>
-      <c r="N53" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="26">
-        <v>63</v>
-      </c>
-      <c r="B54" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="H54" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="26" cm="1">
-        <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J54" s="26">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K54" s="67"/>
-      <c r="L54" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="M54" s="26"/>
-      <c r="N54" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="30">
-        <v>64</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="I55" s="30" cm="1">
-        <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J55" s="30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K55" s="53"/>
-      <c r="L55" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="30">
-        <v>65</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="H56" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="I56" s="30" cm="1">
-        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J56" s="30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K56" s="54"/>
-      <c r="L56" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M56" s="30"/>
-      <c r="N56" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="30">
-        <v>66</v>
-      </c>
-      <c r="B57" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="I57" s="30" cm="1">
-        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J57" s="30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K57" s="54"/>
-      <c r="L57" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M57" s="30"/>
-      <c r="N57" s="30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="33">
-        <v>68</v>
-      </c>
-      <c r="B58" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H58" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I58" s="33" cm="1">
-        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J58" s="33">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K58" s="54"/>
-      <c r="L58" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M58" s="33"/>
-      <c r="N58" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="33">
-        <v>69</v>
-      </c>
-      <c r="B59" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="H59" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" s="33" cm="1">
-        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J59" s="33">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K59" s="54"/>
-      <c r="L59" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M59" s="33"/>
-      <c r="N59" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="33">
-        <v>70</v>
-      </c>
-      <c r="B60" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H60" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="I60" s="33" cm="1">
-        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J60" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K60" s="54"/>
-      <c r="L60" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M60" s="33"/>
-      <c r="N60" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="33">
-        <v>71</v>
-      </c>
-      <c r="B61" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H61" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="33" cm="1">
-        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J61" s="33">
-        <f t="shared" ref="J61:J77" si="1">I61</f>
-        <v>2</v>
-      </c>
-      <c r="K61" s="54"/>
-      <c r="L61" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M61" s="33"/>
-      <c r="N61" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="33">
-        <v>76</v>
-      </c>
-      <c r="B62" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H62" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="I62" s="33" cm="1">
-        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J62" s="33">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K62" s="54"/>
-      <c r="L62" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M62" s="33"/>
-      <c r="N62" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="33">
-        <v>77</v>
-      </c>
-      <c r="B63" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H63" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I63" s="33" cm="1">
-        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J63" s="33">
+      <c r="I46" s="72">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K63" s="54"/>
-      <c r="L63" s="33" t="s">
+      <c r="J46" s="52">
+        <v>11</v>
+      </c>
+      <c r="K46" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="L46" s="27"/>
+      <c r="M46" s="27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" s="28"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="28"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="28"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="25">
+        <v>3.9</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" s="25" cm="1">
+        <f t="array" ref="H50">_xlfn.SWITCH(G50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I50" s="25">
+        <f t="shared" ref="I50:I68" si="2">H50</f>
+        <v>3</v>
+      </c>
+      <c r="J50" s="53"/>
+      <c r="K50" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="25">
+        <v>3.9</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="H51" s="25" cm="1">
+        <f t="array" ref="H51">_xlfn.SWITCH(G51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I51" s="25">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J51" s="53"/>
+      <c r="K51" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="25">
+        <v>3.9</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H52" s="25" cm="1">
+        <f t="array" ref="H52">_xlfn.SWITCH(G52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I52" s="25">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J52" s="54"/>
+      <c r="K52" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="L52" s="25"/>
+      <c r="M52" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="25">
+        <v>3.9</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H53" s="25" cm="1">
+        <f t="array" ref="H53">_xlfn.SWITCH(G53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I53" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J53" s="47"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="25"/>
+    </row>
+    <row r="54" spans="1:13" s="15" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="31"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H54" s="31" cm="1">
+        <f t="array" ref="H54">_xlfn.SWITCH(G54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I54" s="31">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J54" s="66"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+    </row>
+    <row r="55" spans="1:13" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="31"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="F55" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55" s="31" cm="1">
+        <f t="array" ref="H55">_xlfn.SWITCH(G55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I55" s="31">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J55" s="66"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+    </row>
+    <row r="56" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="30"/>
+      <c r="F56" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H56" s="29" cm="1">
+        <f t="array" ref="H56">_xlfn.SWITCH(G56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I56" s="29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J56" s="58">
         <v>27</v>
       </c>
-      <c r="M63" s="33"/>
-      <c r="N63" s="33" t="s">
+      <c r="K56" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="L56" s="29"/>
+      <c r="M56" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E57" s="30"/>
+      <c r="F57" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G57" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H57" s="29" cm="1">
+        <f t="array" ref="H57">_xlfn.SWITCH(G57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I57" s="29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J57" s="59"/>
+      <c r="K57" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E58" s="30"/>
+      <c r="F58" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G58" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H58" s="29" cm="1">
+        <f t="array" ref="H58">_xlfn.SWITCH(G58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I58" s="29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J58" s="59"/>
+      <c r="K58" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="33"/>
+      <c r="F59" s="32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="33">
-        <v>78</v>
-      </c>
-      <c r="B64" s="33" t="s">
+      <c r="G59" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" s="32" cm="1">
+        <f t="array" ref="H59">_xlfn.SWITCH(G59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I59" s="32">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J59" s="59"/>
+      <c r="K59" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="33"/>
+      <c r="F60" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" s="32" cm="1">
+        <f t="array" ref="H60">_xlfn.SWITCH(G60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I60" s="32">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J60" s="59"/>
+      <c r="K60" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="33"/>
+      <c r="F61" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H61" s="32" cm="1">
+        <f t="array" ref="H61">_xlfn.SWITCH(G61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I61" s="32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J61" s="59"/>
+      <c r="K61" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
+    </row>
+    <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="33"/>
+      <c r="F62" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62" s="32" cm="1">
+        <f t="array" ref="H62">_xlfn.SWITCH(G62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I62" s="32">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J62" s="59"/>
+      <c r="K62" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L62" s="32"/>
+      <c r="M62" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="33"/>
+      <c r="F63" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G63" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H63" s="32" cm="1">
+        <f t="array" ref="H63">_xlfn.SWITCH(G63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I63" s="32">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J63" s="59"/>
+      <c r="K63" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L63" s="32"/>
+      <c r="M63" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32" t="s">
+        <v>41</v>
+      </c>
       <c r="E64" s="33"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H64" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="I64" s="33" cm="1">
-        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="F64" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H64" s="32" cm="1">
+        <f t="array" ref="H64">_xlfn.SWITCH(G64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I64" s="32">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J64" s="59"/>
+      <c r="K64" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" s="32"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" s="33"/>
+      <c r="F65" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H65" s="32" cm="1">
+        <f t="array" ref="H65">_xlfn.SWITCH(G65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J64" s="33">
-        <f t="shared" si="1"/>
+      <c r="I65" s="32">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K64" s="54"/>
-      <c r="L64" s="33" t="s">
+      <c r="J65" s="59"/>
+      <c r="K65" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L65" s="32"/>
+      <c r="M65" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66" s="33"/>
+      <c r="F66" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H66" s="32" cm="1">
+        <f t="array" ref="H66">_xlfn.SWITCH(G66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I66" s="32">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J66" s="59"/>
+      <c r="K66" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L66" s="32"/>
+      <c r="M66" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="33"/>
+      <c r="F67" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H67" s="32" cm="1">
+        <f t="array" ref="H67">_xlfn.SWITCH(G67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I67" s="32">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J67" s="59"/>
+      <c r="K67" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="33"/>
+      <c r="F68" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G68" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H68" s="32" cm="1">
+        <f t="array" ref="H68">_xlfn.SWITCH(G68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I68" s="32">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J68" s="60"/>
+      <c r="K68" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="L68" s="32"/>
+      <c r="M68" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A69" s="31"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E69" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="66"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
+    </row>
+    <row r="70" spans="1:13" s="15" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="31"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E70" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="66"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+    </row>
+    <row r="71" spans="1:13" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="31"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="31"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="66"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="31"/>
+      <c r="M71" s="31"/>
+    </row>
+    <row r="72" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E72" s="37"/>
+      <c r="F72" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="G72" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H72" s="36" cm="1">
+        <f t="array" ref="H72">_xlfn.SWITCH(G72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I72" s="36">
+        <f>H72</f>
+        <v>1</v>
+      </c>
+      <c r="J72" s="61">
         <v>27</v>
       </c>
-      <c r="M64" s="33"/>
-      <c r="N64" s="33" t="s">
+      <c r="K72" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="L72" s="36"/>
+      <c r="M72" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" s="35"/>
+      <c r="F73" s="34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="33">
-        <v>79</v>
-      </c>
-      <c r="B65" s="33" t="s">
+      <c r="G73" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73" s="34" cm="1">
+        <f t="array" ref="H73">_xlfn.SWITCH(G73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I73" s="34">
+        <f>H73</f>
+        <v>8</v>
+      </c>
+      <c r="J73" s="62"/>
+      <c r="K73" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="L73" s="34"/>
+      <c r="M73" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H65" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="I65" s="33" cm="1">
-        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J65" s="33">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K65" s="54"/>
-      <c r="L65" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M65" s="33"/>
-      <c r="N65" s="33" t="s">
+    </row>
+    <row r="74" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B74" s="34"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" s="35"/>
+      <c r="F74" s="34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="33">
-        <v>80</v>
-      </c>
-      <c r="B66" s="33" t="s">
+      <c r="G74" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H74" s="34" cm="1">
+        <f t="array" ref="H74">_xlfn.SWITCH(G74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I74" s="34">
+        <f>H74</f>
+        <v>5</v>
+      </c>
+      <c r="J74" s="62"/>
+      <c r="K74" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="L74" s="34"/>
+      <c r="M74" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H66" s="33" t="s">
+    </row>
+    <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" s="35"/>
+      <c r="F75" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="I66" s="33" cm="1">
-        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J66" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K66" s="54"/>
-      <c r="L66" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M66" s="33"/>
-      <c r="N66" s="33" t="s">
+      <c r="H75" s="34" cm="1">
+        <f t="array" ref="H75">_xlfn.SWITCH(G75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="33">
-        <v>81</v>
-      </c>
-      <c r="B67" s="33" t="s">
+      <c r="I75" s="34">
+        <f>H75</f>
+        <v>8</v>
+      </c>
+      <c r="J75" s="62"/>
+      <c r="K75" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="34"/>
+      <c r="M75" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H67" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="33" cm="1">
-        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J67" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="K67" s="55"/>
-      <c r="L67" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="M67" s="33"/>
-      <c r="N67" s="33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="30">
-        <v>67</v>
-      </c>
-      <c r="B68" s="30" t="s">
+    </row>
+    <row r="76" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="34"/>
+      <c r="C76" s="34"/>
+      <c r="D76" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="35"/>
+      <c r="F76" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H76" s="34" cm="1">
+        <f t="array" ref="H76">_xlfn.SWITCH(G76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I76" s="34">
+        <f>H76</f>
+        <v>5</v>
+      </c>
+      <c r="J76" s="63"/>
+      <c r="K76" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="34"/>
+      <c r="M76" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="I68" s="37" cm="1">
-        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J68" s="37">
-        <f>I68</f>
-        <v>1</v>
-      </c>
-      <c r="K68" s="56"/>
-      <c r="L68" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="M68" s="37"/>
-      <c r="N68" s="37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="33">
-        <v>72</v>
-      </c>
-      <c r="B69" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H69" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="I69" s="35" cm="1">
-        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J69" s="35">
-        <f>I69</f>
-        <v>8</v>
-      </c>
-      <c r="K69" s="57"/>
-      <c r="L69" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M69" s="35"/>
-      <c r="N69" s="35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="33">
-        <v>73</v>
-      </c>
-      <c r="B70" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H70" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="I70" s="35" cm="1">
-        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J70" s="35">
-        <f>I70</f>
-        <v>5</v>
-      </c>
-      <c r="K70" s="57"/>
-      <c r="L70" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M70" s="35"/>
-      <c r="N70" s="35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="33">
-        <v>74</v>
-      </c>
-      <c r="B71" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="35"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="H71" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="I71" s="35" cm="1">
-        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J71" s="35">
-        <f>I71</f>
-        <v>8</v>
-      </c>
-      <c r="K71" s="57"/>
-      <c r="L71" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M71" s="35"/>
-      <c r="N71" s="35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="33">
-        <v>75</v>
-      </c>
-      <c r="B72" s="33"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="36"/>
-      <c r="G72" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="H72" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="I72" s="35" cm="1">
-        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J72" s="35">
-        <f>I72</f>
-        <v>5</v>
-      </c>
-      <c r="K72" s="58"/>
-      <c r="L72" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="M72" s="35"/>
-      <c r="N72" s="35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
-        <v>82</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2" t="str" cm="1">
-        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J73" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K73" s="32"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
-        <v>83</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2" t="str" cm="1">
-        <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J74" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K74" s="32"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
-        <v>84</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2" t="str" cm="1">
-        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K75" s="32"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
-        <v>85</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2" t="str" cm="1">
-        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J76" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K76" s="32"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
-        <v>86</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2" t="str" cm="1">
-        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="32" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K77" s="32"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
+    </row>
+    <row r="77" spans="1:13" s="15" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="31"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="31"/>
+      <c r="J77" s="31"/>
+      <c r="K77" s="31"/>
+      <c r="L77" s="31"/>
+      <c r="M77" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="H40:H43"/>
-    <mergeCell ref="I40:I43"/>
-    <mergeCell ref="G40:G43"/>
-    <mergeCell ref="J40:J43"/>
-    <mergeCell ref="G32:G39"/>
-    <mergeCell ref="H32:H39"/>
-    <mergeCell ref="I32:I39"/>
-    <mergeCell ref="G48:G51"/>
-    <mergeCell ref="H48:H51"/>
-    <mergeCell ref="I48:I51"/>
-    <mergeCell ref="J48:J51"/>
-    <mergeCell ref="G44:G47"/>
-    <mergeCell ref="H44:H47"/>
-    <mergeCell ref="I44:I47"/>
-    <mergeCell ref="J32:J39"/>
-    <mergeCell ref="K55:K67"/>
-    <mergeCell ref="K68:K72"/>
-    <mergeCell ref="K27:K39"/>
-    <mergeCell ref="K40:K47"/>
-    <mergeCell ref="K48:K54"/>
-    <mergeCell ref="J44:J47"/>
+  <mergeCells count="12">
+    <mergeCell ref="J56:J68"/>
+    <mergeCell ref="J72:J76"/>
+    <mergeCell ref="J35:J42"/>
+    <mergeCell ref="J46:J52"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="G39:G42"/>
+    <mergeCell ref="H39:H42"/>
+    <mergeCell ref="I39:I42"/>
+    <mergeCell ref="G35:G38"/>
+    <mergeCell ref="H35:H38"/>
+    <mergeCell ref="F35:F38"/>
+    <mergeCell ref="I35:I38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5953,31 +8094,31 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B2" s="39">
         <v>156</v>
       </c>
       <c r="C2" s="1">
@@ -5988,147 +8129,147 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="41">
+      <c r="B3" s="40">
         <f>156-SUM(D$3:D3)</f>
         <v>156</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>156-A3*15.6</f>
         <v>140.4</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="41">
+      <c r="B4" s="40">
         <f>156-SUM(D$3:D4)</f>
         <v>156</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f t="shared" ref="C4:C12" si="0">156-A4*15.6</f>
         <v>124.8</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="K4" s="39"/>
+      <c r="K4" s="38"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="40">
         <f>156-SUM(D$3:D5)</f>
         <v>156</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>109.2</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="40">
         <f>156-SUM(D$3:D6)</f>
         <v>156</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>93.6</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="40">
         <f>156-SUM(D$3:D7)</f>
         <v>148</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="40">
         <f>156-SUM(D$3:D8)</f>
         <v>148</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>62.400000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9" s="40">
         <f>156-SUM(D$3:D9)</f>
         <v>148</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>46.8</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="40">
         <f>156-SUM(D$3:D10)</f>
         <v>148</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f t="shared" si="0"/>
         <v>31.200000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="40">
         <f>156-SUM(D$3:D11)</f>
         <v>148</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f t="shared" si="0"/>
         <v>15.599999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="40">
         <f>156-SUM(D$3:D12)</f>
         <v>148</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6146,32 +8287,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6185,65 +8326,65 @@
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13.44140625" style="1"/>
-    <col min="3" max="16384" width="13.44140625" style="3"/>
+    <col min="3" max="16384" width="13.44140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D841FD3A-1A1E-4B56-AB28-FE0AD603FB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4DE37A-B949-4D64-82A2-EC62EBDD79E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-72" yWindow="0" windowWidth="11928" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="109">
   <si>
     <t>Epic</t>
   </si>
@@ -2919,237 +2919,6 @@
     <t>RenterBookedE-BikeOptions</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedE-BikeOptions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout:
-1. Render the booked E-Bike's 
-- enlarged image as the card's background image (occupying 100% of the card)
-- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, E-bike </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date range</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of booking (From-To) of the cheapest e-bike under the card
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Owner's Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> clickable hyperlink
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Insurance Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> clickable hyperlink
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel Booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> clickable hyperlink</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedE-BikeCancellationOption</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen onPress of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel Booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink</t>
-    </r>
-  </si>
-  <si>
     <t>RenterBookedE-BikeCancellationOption</t>
   </si>
   <si>
@@ -3832,12 +3601,1713 @@
 - Trigger "Successfully Returned!" notification to Owner.</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeCancellationOption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cancel Booking </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Render the booked E-Bike's 
+- enlarged image as the card's background image (occupying 100% of the card)
+- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, E-bike </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of booking (From-To) of the cheapest e-bike under the card
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+6. Fetch the booking start date and lock away </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option on the date
+- Render a checkbox, followed by "I confirm all </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e-bike features</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are working fine" text with hyperlink
+- Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accept E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeFeaturestoCheck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Add on/off toggles for all the feature options
+2. Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Raise Issue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">primary button
+3. Add logic to block operation of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Raise Issue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button until at least 1 (or more than 1) toggles are turned off
+4. If &gt;=1 toggles are turned off, onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Raise Issue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterBookedE-BikeRaiseIssue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterBookedE-BikeOptions </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen:
+1. Add logic for blocking navigation of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accept E-Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button until the "I confirm all </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e-bike features</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are working fine" checkbox is checked.
+2. If checked, onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accept E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button changes the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeCurrentBooking </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen:
+- Render "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Report an Incident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with current booking" hyperlink + text, under "I confirm all </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e-bike features</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are working fine"
+- Change </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Accept E-Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Return E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button
+3. onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e-bike features</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeFeaturestoCheck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>TBD IF "RenterE-BikeCurrentBooking" screen should be a standalone screen or a different state after renter accepts the booked e-bike on the " RenterBookedE-BikeOptions" screen itself</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeRaiseIssue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Add heading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upload an image of the issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> camera upload
+3. Add subheading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Describe the Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Add a TextField that accepts long paragraphs
+4. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issuse + Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> secondary button
+5. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ignore Issue, Go Back </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>primary button</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBookingReportIncident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Add heading:R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>report Incident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upload an image of the incident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> camera upload
+3. Add subheading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Incident Category
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- Add a dropdown field for selecting from given incident enum: (Theft, Flat Tyre,...., Others)
+4. Add subheading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Incident Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Add a TextField that accepts long paragraphs
+6. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Report</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button
+7. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dial 000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> secondary button
+8. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Make an Insurance Claim </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">secondary button
+- onpress navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeCurrentBookingClaimInsurance </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBookingClaimInsurance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Add heading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Claim Insurance
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Claim Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as a scrollable content…</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Read more</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink
+3. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Initiate Claim </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>primary button</t>
+    </r>
+  </si>
+  <si>
+    <t>RenterBookedE-BikeFeaturestoCheck</t>
+  </si>
+  <si>
+    <t>RenterBookedE-BikeRaiseIssue</t>
+  </si>
+  <si>
+    <t>RenterE-BikeCurrentBooking</t>
+  </si>
+  <si>
+    <t>RenterE-BikeCurrentBookingReportIncident</t>
+  </si>
+  <si>
+    <t>RenterE-BikeCurrentBookingClaimInsurance</t>
+  </si>
+  <si>
+    <t>RenterE-BikeReturn</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen:
+1. onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Report an Incident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBookingReportIncident</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+2. onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBookingClaimInsurance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeReturn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen:
+1. Add heading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upload an image at return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> camera upload
+3. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rate your experience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section
+- Pressable 5 stars (only </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Colors.primary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> outlines) for rating submission
+- Add logic to show 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Colors.primary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> filled stars, if 5th star is pressed. 4 filled stars if 4 are pressed...and so on.
+4. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Leave a comment </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">section
+-  Add a TextField that accepts long paragraphs
+5. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Return </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>primary button
+- onPress returns the bike (sends backend signal)</t>
+    </r>
+  </si>
+  <si>
+    <t>RenterE-BikeReturn (PREMATURE)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen:
+1. onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeReturn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, if currentDate == bookingEndDate
+2. if currentDate !== bookingEndDate, onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button renders a modal on the same screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>modal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> window component:
+- Add message for user: You are about to return the E-Bike before your booking ends, there won't be any refunds!
+- Add two pressable options in the modal window: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Keep Riding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as primary, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return Anyway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as secondary
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return Anyway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onPress navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeReturn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Keep Riding </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onPress closes the modal without doing anything</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3917,6 +5387,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4084,7 +5560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4226,51 +5702,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4306,6 +5737,54 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5607,7 +7086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="1" customWidth="1"/>
@@ -5693,7 +7172,7 @@
         <f>H2</f>
         <v/>
       </c>
-      <c r="J2" s="67">
+      <c r="J2" s="52">
         <v>16</v>
       </c>
       <c r="K2" s="5" t="s">
@@ -6008,7 +7487,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J11" s="68"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8" t="s">
@@ -6072,7 +7551,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J13" s="69"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="10" t="s">
         <v>26</v>
       </c>
@@ -6342,7 +7821,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J21" s="70"/>
+      <c r="J21" s="55"/>
       <c r="K21" s="11" t="s">
         <v>26</v>
       </c>
@@ -6418,7 +7897,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J23" s="64"/>
+      <c r="J23" s="49"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11" t="s">
@@ -6432,7 +7911,7 @@
       <c r="D24" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="50" t="s">
         <v>65</v>
       </c>
       <c r="F24" s="31" t="s">
@@ -6449,7 +7928,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J24" s="66"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="31"/>
       <c r="L24" s="31"/>
       <c r="M24" s="31" t="s">
@@ -6463,7 +7942,7 @@
       <c r="D25" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="65" t="s">
+      <c r="E25" s="50" t="s">
         <v>66</v>
       </c>
       <c r="F25" s="31" t="s">
@@ -6480,7 +7959,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J25" s="66"/>
+      <c r="J25" s="51"/>
       <c r="K25" s="31"/>
       <c r="L25" s="31"/>
       <c r="M25" s="31" t="s">
@@ -6723,7 +8202,7 @@
       <c r="D33" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E33" s="65" t="s">
+      <c r="E33" s="50" t="s">
         <v>63</v>
       </c>
       <c r="F33" s="31" t="s">
@@ -6732,7 +8211,7 @@
       <c r="G33" s="31"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
-      <c r="J33" s="66"/>
+      <c r="J33" s="51"/>
       <c r="K33" s="31"/>
       <c r="L33" s="31"/>
       <c r="M33" s="31" t="s">
@@ -6746,7 +8225,7 @@
       <c r="D34" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="65" t="s">
+      <c r="E34" s="50" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="31" t="s">
@@ -6755,7 +8234,7 @@
       <c r="G34" s="31"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
-      <c r="J34" s="66"/>
+      <c r="J34" s="51"/>
       <c r="K34" s="31"/>
       <c r="L34" s="31"/>
       <c r="M34" s="31" t="s">
@@ -6772,21 +8251,21 @@
         <v>39</v>
       </c>
       <c r="E35" s="21"/>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="49" t="s">
+      <c r="G35" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="H35" s="49" cm="1">
+      <c r="H35" s="64" cm="1">
         <f t="array" ref="H35">_xlfn.SWITCH(G35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="I35" s="49">
+      <c r="I35" s="64">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J35" s="49"/>
+      <c r="J35" s="64"/>
       <c r="K35" s="20" t="s">
         <v>26</v>
       </c>
@@ -6805,11 +8284,11 @@
         <v>39</v>
       </c>
       <c r="E36" s="21"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
       <c r="K36" s="20" t="s">
         <v>26</v>
       </c>
@@ -6828,11 +8307,11 @@
         <v>39</v>
       </c>
       <c r="E37" s="21"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
       <c r="K37" s="20" t="s">
         <v>26</v>
       </c>
@@ -6851,11 +8330,11 @@
         <v>39</v>
       </c>
       <c r="E38" s="21"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="50"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="65"/>
       <c r="K38" s="20" t="s">
         <v>26</v>
       </c>
@@ -6880,21 +8359,21 @@
       <c r="E39" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="F39" s="55" t="s">
+      <c r="F39" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="G39" s="55" t="s">
+      <c r="G39" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="55" cm="1">
+      <c r="H39" s="70" cm="1">
         <f t="array" ref="H39">_xlfn.SWITCH(G39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="I39" s="55">
+      <c r="I39" s="70">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J39" s="50"/>
+      <c r="J39" s="65"/>
       <c r="K39" s="22" t="s">
         <v>26</v>
       </c>
@@ -6919,11 +8398,11 @@
       <c r="E40" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="50"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="65"/>
       <c r="K40" s="22" t="s">
         <v>26</v>
       </c>
@@ -6948,11 +8427,11 @@
       <c r="E41" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="50"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="65"/>
       <c r="K41" s="22" t="s">
         <v>26</v>
       </c>
@@ -6977,11 +8456,11 @@
       <c r="E42" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="51"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="66"/>
       <c r="K42" s="22" t="s">
         <v>26</v>
       </c>
@@ -7022,7 +8501,7 @@
       <c r="D44" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="71" t="s">
+      <c r="E44" s="56" t="s">
         <v>71</v>
       </c>
       <c r="F44" s="31" t="s">
@@ -7036,7 +8515,7 @@
         <v>2</v>
       </c>
       <c r="I44" s="22">
-        <f t="shared" ref="I44:I47" si="1">H44</f>
+        <f t="shared" ref="I44:I46" si="1">H44</f>
         <v>2</v>
       </c>
       <c r="J44" s="31"/>
@@ -7055,7 +8534,7 @@
       <c r="D45" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="71" t="s">
+      <c r="E45" s="56" t="s">
         <v>72</v>
       </c>
       <c r="F45" s="31" t="s">
@@ -7089,21 +8568,21 @@
         <v>39</v>
       </c>
       <c r="E46" s="28"/>
-      <c r="F46" s="72" t="s">
+      <c r="F46" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="G46" s="72" t="s">
+      <c r="G46" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="H46" s="72" cm="1">
+      <c r="H46" s="57" cm="1">
         <f t="array" ref="H46">_xlfn.SWITCH(G46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="I46" s="72">
+      <c r="I46" s="57">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J46" s="52">
+      <c r="J46" s="67">
         <v>11</v>
       </c>
       <c r="K46" s="27" t="s">
@@ -7124,11 +8603,11 @@
         <v>39</v>
       </c>
       <c r="E47" s="28"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="53"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="68"/>
       <c r="K47" s="27" t="s">
         <v>73</v>
       </c>
@@ -7147,11 +8626,11 @@
         <v>39</v>
       </c>
       <c r="E48" s="28"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="53"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="58"/>
+      <c r="J48" s="68"/>
       <c r="K48" s="27" t="s">
         <v>73</v>
       </c>
@@ -7170,11 +8649,11 @@
         <v>39</v>
       </c>
       <c r="E49" s="28"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="74"/>
-      <c r="I49" s="74"/>
-      <c r="J49" s="53"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="68"/>
       <c r="K49" s="27" t="s">
         <v>73</v>
       </c>
@@ -7183,7 +8662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
         <v>48</v>
       </c>
@@ -7197,23 +8676,23 @@
         <v>41</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F50" s="25" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H50" s="25" cm="1">
         <f t="array" ref="H50">_xlfn.SWITCH(G50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I50" s="25">
-        <f t="shared" ref="I50:I68" si="2">H50</f>
-        <v>3</v>
-      </c>
-      <c r="J50" s="53"/>
+        <f t="shared" ref="I50:I65" si="2">H50</f>
+        <v>5</v>
+      </c>
+      <c r="J50" s="68"/>
       <c r="K50" s="25" t="s">
         <v>74</v>
       </c>
@@ -7230,13 +8709,13 @@
         <v>3.9</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>41</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F51" s="25" t="s">
         <v>8</v>
@@ -7252,7 +8731,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J51" s="53"/>
+      <c r="J51" s="68"/>
       <c r="K51" s="25" t="s">
         <v>74</v>
       </c>
@@ -7269,13 +8748,13 @@
         <v>3.9</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D52" s="25" t="s">
         <v>41</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F52" s="25" t="s">
         <v>8</v>
@@ -7291,7 +8770,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J52" s="54"/>
+      <c r="J52" s="69"/>
       <c r="K52" s="25" t="s">
         <v>74</v>
       </c>
@@ -7308,13 +8787,13 @@
         <v>3.9</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D53" s="25" t="s">
         <v>41</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F53" s="25" t="s">
         <v>8</v>
@@ -7342,8 +8821,8 @@
       <c r="D54" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E54" s="65" t="s">
-        <v>85</v>
+      <c r="E54" s="50" t="s">
+        <v>83</v>
       </c>
       <c r="F54" s="31" t="s">
         <v>33</v>
@@ -7359,7 +8838,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J54" s="66"/>
+      <c r="J54" s="51"/>
       <c r="K54" s="31"/>
       <c r="L54" s="31"/>
       <c r="M54" s="31"/>
@@ -7371,8 +8850,8 @@
       <c r="D55" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E55" s="65" t="s">
-        <v>86</v>
+      <c r="E55" s="50" t="s">
+        <v>84</v>
       </c>
       <c r="F55" s="31" t="s">
         <v>33</v>
@@ -7388,7 +8867,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J55" s="66"/>
+      <c r="J55" s="51"/>
       <c r="K55" s="31"/>
       <c r="L55" s="31"/>
       <c r="M55" s="31"/>
@@ -7417,7 +8896,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J56" s="58">
+      <c r="J56" s="74">
         <v>27</v>
       </c>
       <c r="K56" s="29" t="s">
@@ -7452,7 +8931,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J57" s="59"/>
+      <c r="J57" s="75"/>
       <c r="K57" s="29" t="s">
         <v>73</v>
       </c>
@@ -7485,7 +8964,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J58" s="59"/>
+      <c r="J58" s="75"/>
       <c r="K58" s="29" t="s">
         <v>73</v>
       </c>
@@ -7494,33 +8973,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A59" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B59" s="75" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="32"/>
+      <c r="B59" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>79</v>
+      </c>
       <c r="D59" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="33"/>
+      <c r="E59" s="33" t="s">
+        <v>93</v>
+      </c>
       <c r="F59" s="32" t="s">
         <v>8</v>
       </c>
       <c r="G59" s="32" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H59" s="32" cm="1">
         <f t="array" ref="H59">_xlfn.SWITCH(G59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59" s="32">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="J59" s="59"/>
+        <v>1</v>
+      </c>
+      <c r="J59" s="75"/>
       <c r="K59" s="32" t="s">
         <v>74</v>
       </c>
@@ -7529,16 +9012,22 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
+      <c r="B60" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>98</v>
+      </c>
       <c r="D60" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="33"/>
+      <c r="E60" s="33" t="s">
+        <v>92</v>
+      </c>
       <c r="F60" s="32" t="s">
         <v>34</v>
       </c>
@@ -7553,7 +9042,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J60" s="59"/>
+      <c r="J60" s="75"/>
       <c r="K60" s="32" t="s">
         <v>74</v>
       </c>
@@ -7562,16 +9051,22 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
+      <c r="B61" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>99</v>
+      </c>
       <c r="D61" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="33"/>
+      <c r="E61" s="33" t="s">
+        <v>95</v>
+      </c>
       <c r="F61" s="32" t="s">
         <v>8</v>
       </c>
@@ -7586,7 +9081,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J61" s="59"/>
+      <c r="J61" s="75"/>
       <c r="K61" s="32" t="s">
         <v>26</v>
       </c>
@@ -7595,49 +9090,55 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="32" t="s">
+    <row r="62" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32" t="s">
+      <c r="B62" s="34">
+        <v>3.11</v>
+      </c>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E62" s="33"/>
-      <c r="F62" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="G62" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H62" s="32" cm="1">
+      <c r="E62" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="34" t="str" cm="1">
         <f t="array" ref="H62">_xlfn.SWITCH(G62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I62" s="32">
+        <v/>
+      </c>
+      <c r="I62" s="34" t="str">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J62" s="59"/>
-      <c r="K62" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="L62" s="32"/>
-      <c r="M62" s="32" t="s">
+        <v/>
+      </c>
+      <c r="J62" s="76"/>
+      <c r="K62" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="34"/>
+      <c r="M62" s="34" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
+      <c r="B63" s="32">
+        <v>3.11</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>100</v>
+      </c>
       <c r="D63" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="E63" s="33"/>
+      <c r="E63" s="33" t="s">
+        <v>104</v>
+      </c>
       <c r="F63" s="32" t="s">
         <v>8</v>
       </c>
@@ -7652,7 +9153,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J63" s="59"/>
+      <c r="J63" s="75"/>
       <c r="K63" s="32" t="s">
         <v>74</v>
       </c>
@@ -7661,16 +9162,22 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A64" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B64" s="32"/>
-      <c r="C64" s="32"/>
+      <c r="B64" s="32">
+        <v>3.11</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>101</v>
+      </c>
       <c r="D64" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="E64" s="33"/>
+      <c r="E64" s="33" t="s">
+        <v>96</v>
+      </c>
       <c r="F64" s="32" t="s">
         <v>8</v>
       </c>
@@ -7685,7 +9192,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J64" s="59"/>
+      <c r="J64" s="75"/>
       <c r="K64" s="32" t="s">
         <v>74</v>
       </c>
@@ -7694,16 +9201,22 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B65" s="32"/>
-      <c r="C65" s="32"/>
+      <c r="B65" s="32">
+        <v>3.11</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>102</v>
+      </c>
       <c r="D65" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="33"/>
+      <c r="E65" s="33" t="s">
+        <v>97</v>
+      </c>
       <c r="F65" s="32" t="s">
         <v>8</v>
       </c>
@@ -7718,7 +9231,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J65" s="59"/>
+      <c r="J65" s="75"/>
       <c r="K65" s="32" t="s">
         <v>74</v>
       </c>
@@ -7727,194 +9240,212 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="32" t="s">
+    <row r="66" spans="1:13" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A66" s="31"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E66" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="51"/>
+      <c r="K66" s="31"/>
+      <c r="L66" s="31"/>
+      <c r="M66" s="31"/>
+    </row>
+    <row r="67" spans="1:13" s="15" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="31"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E67" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="51"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+    </row>
+    <row r="68" spans="1:13" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="31"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E68" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="31"/>
+      <c r="I68" s="31"/>
+      <c r="J68" s="51"/>
+      <c r="K68" s="31"/>
+      <c r="L68" s="31"/>
+      <c r="M68" s="31"/>
+    </row>
+    <row r="69" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B66" s="32"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32" t="s">
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" s="37"/>
+      <c r="F69" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="G69" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H69" s="36" cm="1">
+        <f t="array" ref="H69">_xlfn.SWITCH(G69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I69" s="36">
+        <f>H69</f>
+        <v>1</v>
+      </c>
+      <c r="J69" s="61">
+        <v>27</v>
+      </c>
+      <c r="K69" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="L69" s="36"/>
+      <c r="M69" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A70" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="34">
+        <v>3.12</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D70" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E66" s="33"/>
-      <c r="F66" s="32" t="s">
+      <c r="E70" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F70" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="G66" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="H66" s="32" cm="1">
-        <f t="array" ref="H66">_xlfn.SWITCH(G66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I66" s="32">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="J66" s="59"/>
-      <c r="K66" s="32" t="s">
+      <c r="G70" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" s="34" cm="1">
+        <f t="array" ref="H70">_xlfn.SWITCH(G70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I70" s="34">
+        <f>H70</f>
+        <v>8</v>
+      </c>
+      <c r="J70" s="62"/>
+      <c r="K70" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="L66" s="32"/>
-      <c r="M66" s="32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="32" t="s">
+      <c r="L70" s="34"/>
+      <c r="M70" s="34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B67" s="32"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="32" t="s">
+      <c r="B71" s="34">
+        <v>3.12</v>
+      </c>
+      <c r="C71" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D71" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E67" s="33"/>
-      <c r="F67" s="32" t="s">
+      <c r="E71" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="F71" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H67" s="32" cm="1">
-        <f t="array" ref="H67">_xlfn.SWITCH(G67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I67" s="32">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="J67" s="59"/>
-      <c r="K67" s="32" t="s">
+      <c r="G71" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H71" s="34" cm="1">
+        <f t="array" ref="H71">_xlfn.SWITCH(G71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I71" s="34">
+        <f>H71</f>
+        <v>5</v>
+      </c>
+      <c r="J71" s="62"/>
+      <c r="K71" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="L67" s="32"/>
-      <c r="M67" s="32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="32" t="s">
+      <c r="L71" s="34"/>
+      <c r="M71" s="34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B68" s="32"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32" t="s">
+      <c r="B72" s="34">
+        <v>3.13</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E68" s="33"/>
-      <c r="F68" s="32" t="s">
+      <c r="E72" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="F72" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G72" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H72" s="34" cm="1">
+        <f t="array" ref="H72">_xlfn.SWITCH(G72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="G68" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H68" s="32" cm="1">
-        <f t="array" ref="H68">_xlfn.SWITCH(G68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I68" s="32">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J68" s="60"/>
-      <c r="K68" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="L68" s="32"/>
-      <c r="M68" s="32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A69" s="31"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E69" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="66"/>
-      <c r="K69" s="31"/>
-      <c r="L69" s="31"/>
-      <c r="M69" s="31"/>
-    </row>
-    <row r="70" spans="1:13" s="15" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="31"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E70" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="66"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-    </row>
-    <row r="71" spans="1:13" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="31"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E71" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="66"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
-      <c r="M71" s="31"/>
-    </row>
-    <row r="72" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B72" s="36"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E72" s="37"/>
-      <c r="F72" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G72" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="H72" s="36" cm="1">
-        <f t="array" ref="H72">_xlfn.SWITCH(G72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I72" s="36">
+      <c r="I72" s="34">
         <f>H72</f>
-        <v>1</v>
-      </c>
-      <c r="J72" s="61">
-        <v>27</v>
-      </c>
-      <c r="K72" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="L72" s="36"/>
-      <c r="M72" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="62"/>
+      <c r="K72" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="34"/>
+      <c r="M72" s="34" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7929,150 +9460,50 @@
       </c>
       <c r="E73" s="35"/>
       <c r="F73" s="34" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="G73" s="34" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H73" s="34" cm="1">
         <f t="array" ref="H73">_xlfn.SWITCH(G73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I73" s="34">
         <f>H73</f>
-        <v>8</v>
-      </c>
-      <c r="J73" s="62"/>
+        <v>5</v>
+      </c>
+      <c r="J73" s="63"/>
       <c r="K73" s="34" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L73" s="34"/>
       <c r="M73" s="34" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B74" s="34"/>
-      <c r="C74" s="34"/>
-      <c r="D74" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E74" s="35"/>
-      <c r="F74" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="G74" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H74" s="34" cm="1">
-        <f t="array" ref="H74">_xlfn.SWITCH(G74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="I74" s="34">
-        <f>H74</f>
-        <v>5</v>
-      </c>
-      <c r="J74" s="62"/>
-      <c r="K74" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="L74" s="34"/>
-      <c r="M74" s="34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B75" s="34"/>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E75" s="35"/>
-      <c r="F75" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="G75" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H75" s="34" cm="1">
-        <f t="array" ref="H75">_xlfn.SWITCH(G75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="I75" s="34">
-        <f>H75</f>
-        <v>8</v>
-      </c>
-      <c r="J75" s="62"/>
-      <c r="K75" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="34"/>
-      <c r="M75" s="34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B76" s="34"/>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E76" s="35"/>
-      <c r="F76" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="G76" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H76" s="34" cm="1">
-        <f t="array" ref="H76">_xlfn.SWITCH(G76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="I76" s="34">
-        <f>H76</f>
-        <v>5</v>
-      </c>
-      <c r="J76" s="63"/>
-      <c r="K76" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="L76" s="34"/>
-      <c r="M76" s="34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" s="15" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="31"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31" t="s">
+    <row r="74" spans="1:13" s="15" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="31"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="E77" s="65" t="s">
-        <v>91</v>
-      </c>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="31"/>
-      <c r="K77" s="31"/>
-      <c r="L77" s="31"/>
-      <c r="M77" s="31"/>
+      <c r="E74" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
+      <c r="J74" s="31"/>
+      <c r="K74" s="31"/>
+      <c r="L74" s="31"/>
+      <c r="M74" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="J56:J68"/>
-    <mergeCell ref="J72:J76"/>
+  <mergeCells count="11">
+    <mergeCell ref="J69:J73"/>
     <mergeCell ref="J35:J42"/>
     <mergeCell ref="J46:J52"/>
     <mergeCell ref="F39:F42"/>
@@ -8084,6 +9515,7 @@
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="I35:I38"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4DE37A-B949-4D64-82A2-EC62EBDD79E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AC7448-03C9-47E6-9DFD-833849AF4A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="106">
   <si>
     <t>Epic</t>
   </si>
@@ -2541,131 +2541,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>POST /api/bookings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Endpoint
-1. Input: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bikeId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>renterId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>startDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>endDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>insuranceAccepted</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (boolean).
-2. Logic:
-- Race Condition Check: Verify bike is still available for dates (lock row).
-- Validation: Ensure insuranceAccepted is true.
-- Transaction: Create Booking record with status CONFIRMED.
-3.Output: bookingId, status.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>GET /api/bookings/my-bookings</t>
     </r>
     <r>
@@ -2699,15 +2574,6 @@
       <t xml:space="preserve"> descending (newest/upcoming first).
 3. Output: List of bookings with attached Bike metadata.</t>
     </r>
-  </si>
-  <si>
-    <t>WIP</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>RenterBookedBikesList</t>
@@ -3329,195 +3195,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>POST /api/bookings/{id}/issues</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Endpoint
-1. Type: Multipart/Form-Data.
-2. Input: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>imageFile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Pre-ride vs Mid-ride).
-3. Logic: Upload image to storage (S3/Cloudinary), save URL, create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Issue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> record linked to booking.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>POST /api/bookings/{id}/start-ride</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Endpoint
-1. Logic: Validate booking is today. Update status to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ACTIVE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Start "Ride Timer" (if applicable).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Create</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> POST /api/incidents</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Endpoint
-1. Type: Multipart/Form-Data.
-2. Logic: High-priority alert. Store incident report, trigger email/SMS to Support Team.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>POST /api/bookings/{id}/return-completion</t>
     </r>
     <r>
@@ -5300,6 +4977,434 @@
         <scheme val="minor"/>
       </rPr>
       <t>onPress closes the modal without doing anything</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings/{id}/start-ride</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Logic: Validate booking is today. Update status from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CONFIRMED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ACTIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- Trigger the "Ride Timer" or timestamp for insurance coverage start.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings/{id}/issues</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint (PRE-RIDE)
+1. Type: Multipart/Form-Data (Image + Text).
+2. Input: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>imageFile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Pre-ride vs Mid-ride).
+3. Logic: Upload image to storage (S3/Cloudinary), save URL, create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> record linked to booking.
+4. Mark booking as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CANCELLED_WITH_ISSUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+Trigger refund (full refund since it's an issue, not a user cancellation).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /api/bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Input: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bikeId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renterId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>startDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>endDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>insuranceAccepted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (boolean).
+2. Logic:
+- Race Condition Check: Verify bike is still available for dates (lock row).
+- Validation: Ensure insuranceAccepted is true.
+- Transaction: Create Booking record with status </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONFIRMED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3.Output: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bookingId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Create</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> POST /api/incidents</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint (MID-RIDE)
+1. Type: Multipart/Form-Data.
+2. Logic: High-priority alert. Store incident report, trigger email/SMS to Support Team/admin.
+- Link to active </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bookingId</t>
     </r>
   </si>
 </sst>
@@ -5560,7 +5665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5738,13 +5843,22 @@
     <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5773,18 +5887,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7086,7 +7188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="1" customWidth="1"/>
@@ -7311,7 +7413,9 @@
         <v>26</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -7342,7 +7446,9 @@
         <v>26</v>
       </c>
       <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
@@ -7414,7 +7520,9 @@
         <v>2</v>
       </c>
       <c r="J9" s="41"/>
-      <c r="K9" s="8"/>
+      <c r="K9" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="L9" s="8"/>
       <c r="M9" s="8" t="s">
         <v>7</v>
@@ -7451,7 +7559,9 @@
         <v>2</v>
       </c>
       <c r="J10" s="41"/>
-      <c r="K10" s="8"/>
+      <c r="K10" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8" t="s">
         <v>7</v>
@@ -7488,7 +7598,9 @@
         <v>2</v>
       </c>
       <c r="J11" s="53"/>
-      <c r="K11" s="8"/>
+      <c r="K11" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8" t="s">
         <v>7</v>
@@ -7521,7 +7633,9 @@
         <v>2</v>
       </c>
       <c r="J12" s="41"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8" t="s">
         <v>7</v>
@@ -7861,7 +7975,9 @@
         <v>1</v>
       </c>
       <c r="J22" s="42"/>
-      <c r="K22" s="11"/>
+      <c r="K22" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="L22" s="11"/>
       <c r="M22" s="11" t="s">
         <v>7</v>
@@ -7898,7 +8014,9 @@
         <v>1</v>
       </c>
       <c r="J23" s="49"/>
-      <c r="K23" s="11"/>
+      <c r="K23" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="L23" s="11"/>
       <c r="M23" s="11" t="s">
         <v>7</v>
@@ -7929,7 +8047,9 @@
         <v>2</v>
       </c>
       <c r="J24" s="51"/>
-      <c r="K24" s="31"/>
+      <c r="K24" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L24" s="31"/>
       <c r="M24" s="31" t="s">
         <v>7</v>
@@ -7960,7 +8080,9 @@
         <v>1</v>
       </c>
       <c r="J25" s="51"/>
-      <c r="K25" s="31"/>
+      <c r="K25" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L25" s="31"/>
       <c r="M25" s="31" t="s">
         <v>7</v>
@@ -8159,7 +8281,9 @@
       </c>
       <c r="I31" s="18"/>
       <c r="J31" s="43"/>
-      <c r="K31" s="18"/>
+      <c r="K31" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="L31" s="18"/>
       <c r="M31" s="18" t="s">
         <v>7</v>
@@ -8189,7 +8313,9 @@
       </c>
       <c r="I32" s="18"/>
       <c r="J32" s="43"/>
-      <c r="K32" s="18"/>
+      <c r="K32" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="L32" s="18"/>
       <c r="M32" s="18" t="s">
         <v>7</v>
@@ -8212,7 +8338,9 @@
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="J33" s="51"/>
-      <c r="K33" s="31"/>
+      <c r="K33" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L33" s="31"/>
       <c r="M33" s="31" t="s">
         <v>7</v>
@@ -8235,7 +8363,9 @@
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="J34" s="51"/>
-      <c r="K34" s="31"/>
+      <c r="K34" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L34" s="31"/>
       <c r="M34" s="31" t="s">
         <v>7</v>
@@ -8251,21 +8381,21 @@
         <v>39</v>
       </c>
       <c r="E35" s="21"/>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="H35" s="64" cm="1">
+      <c r="H35" s="67" cm="1">
         <f t="array" ref="H35">_xlfn.SWITCH(G35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="I35" s="64">
+      <c r="I35" s="67">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J35" s="64"/>
+      <c r="J35" s="67"/>
       <c r="K35" s="20" t="s">
         <v>26</v>
       </c>
@@ -8284,11 +8414,11 @@
         <v>39</v>
       </c>
       <c r="E36" s="21"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="65"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="68"/>
+      <c r="J36" s="68"/>
       <c r="K36" s="20" t="s">
         <v>26</v>
       </c>
@@ -8307,11 +8437,11 @@
         <v>39</v>
       </c>
       <c r="E37" s="21"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="65"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="68"/>
       <c r="K37" s="20" t="s">
         <v>26</v>
       </c>
@@ -8330,11 +8460,11 @@
         <v>39</v>
       </c>
       <c r="E38" s="21"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="65"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="68"/>
       <c r="K38" s="20" t="s">
         <v>26</v>
       </c>
@@ -8351,7 +8481,7 @@
         <v>3.5</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D39" s="22" t="s">
         <v>41</v>
@@ -8359,21 +8489,21 @@
       <c r="E39" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="F39" s="70" t="s">
+      <c r="F39" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="G39" s="70" t="s">
+      <c r="G39" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="70" cm="1">
+      <c r="H39" s="73" cm="1">
         <f t="array" ref="H39">_xlfn.SWITCH(G39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="I39" s="70">
+      <c r="I39" s="73">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J39" s="65"/>
+      <c r="J39" s="68"/>
       <c r="K39" s="22" t="s">
         <v>26</v>
       </c>
@@ -8390,19 +8520,19 @@
         <v>3.5</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D40" s="22" t="s">
         <v>41</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="65"/>
+        <v>73</v>
+      </c>
+      <c r="F40" s="74"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="68"/>
       <c r="K40" s="22" t="s">
         <v>26</v>
       </c>
@@ -8419,7 +8549,7 @@
         <v>3.6</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>41</v>
@@ -8427,11 +8557,11 @@
       <c r="E41" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="65"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="74"/>
+      <c r="I41" s="74"/>
+      <c r="J41" s="68"/>
       <c r="K41" s="22" t="s">
         <v>26</v>
       </c>
@@ -8448,7 +8578,7 @@
         <v>3.7</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D42" s="22" t="s">
         <v>41</v>
@@ -8456,11 +8586,11 @@
       <c r="E42" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="72"/>
-      <c r="J42" s="66"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="75"/>
+      <c r="J42" s="69"/>
       <c r="K42" s="22" t="s">
         <v>26</v>
       </c>
@@ -8475,22 +8605,26 @@
         <v>3.8</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>41</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F43" s="48"/>
       <c r="G43" s="48"/>
       <c r="H43" s="48"/>
       <c r="I43" s="48"/>
       <c r="J43" s="46"/>
-      <c r="K43" s="22"/>
+      <c r="K43" s="22" t="s">
+        <v>26</v>
+      </c>
       <c r="L43" s="22"/>
-      <c r="M43" s="22"/>
+      <c r="M43" s="22" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="44" spans="1:13" s="15" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A44" s="31" t="s">
@@ -8502,7 +8636,7 @@
         <v>62</v>
       </c>
       <c r="E44" s="56" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="F44" s="31" t="s">
         <v>33</v>
@@ -8519,7 +8653,9 @@
         <v>2</v>
       </c>
       <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
+      <c r="K44" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L44" s="31"/>
       <c r="M44" s="31" t="s">
         <v>7</v>
@@ -8535,7 +8671,7 @@
         <v>62</v>
       </c>
       <c r="E45" s="56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F45" s="31" t="s">
         <v>33</v>
@@ -8552,7 +8688,9 @@
         <v>2</v>
       </c>
       <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
+      <c r="K45" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L45" s="31"/>
       <c r="M45" s="31" t="s">
         <v>7</v>
@@ -8582,11 +8720,11 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J46" s="67">
+      <c r="J46" s="70">
         <v>11</v>
       </c>
       <c r="K46" s="27" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L46" s="27"/>
       <c r="M46" s="27" t="s">
@@ -8607,9 +8745,9 @@
       <c r="G47" s="58"/>
       <c r="H47" s="58"/>
       <c r="I47" s="58"/>
-      <c r="J47" s="68"/>
+      <c r="J47" s="71"/>
       <c r="K47" s="27" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L47" s="27"/>
       <c r="M47" s="27" t="s">
@@ -8630,9 +8768,9 @@
       <c r="G48" s="58"/>
       <c r="H48" s="58"/>
       <c r="I48" s="58"/>
-      <c r="J48" s="68"/>
+      <c r="J48" s="71"/>
       <c r="K48" s="27" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L48" s="27"/>
       <c r="M48" s="27" t="s">
@@ -8653,9 +8791,9 @@
       <c r="G49" s="59"/>
       <c r="H49" s="59"/>
       <c r="I49" s="59"/>
-      <c r="J49" s="68"/>
+      <c r="J49" s="71"/>
       <c r="K49" s="27" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L49" s="27"/>
       <c r="M49" s="27" t="s">
@@ -8670,13 +8808,13 @@
         <v>3.9</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>41</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F50" s="25" t="s">
         <v>8</v>
@@ -8689,16 +8827,16 @@
         <v>5</v>
       </c>
       <c r="I50" s="25">
-        <f t="shared" ref="I50:I65" si="2">H50</f>
+        <f t="shared" ref="I50:I68" si="2">H50</f>
         <v>5</v>
       </c>
-      <c r="J50" s="68"/>
+      <c r="J50" s="71"/>
       <c r="K50" s="25" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L50" s="25"/>
       <c r="M50" s="25" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -8709,13 +8847,13 @@
         <v>3.9</v>
       </c>
       <c r="C51" s="25" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>41</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F51" s="25" t="s">
         <v>8</v>
@@ -8731,13 +8869,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J51" s="68"/>
+      <c r="J51" s="71"/>
       <c r="K51" s="25" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L51" s="25"/>
       <c r="M51" s="25" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
@@ -8748,13 +8886,13 @@
         <v>3.9</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D52" s="25" t="s">
         <v>41</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F52" s="25" t="s">
         <v>8</v>
@@ -8770,13 +8908,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J52" s="69"/>
+      <c r="J52" s="72"/>
       <c r="K52" s="25" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L52" s="25"/>
       <c r="M52" s="25" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -8787,13 +8925,13 @@
         <v>3.9</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D53" s="25" t="s">
         <v>41</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F53" s="25" t="s">
         <v>8</v>
@@ -8810,9 +8948,13 @@
         <v>1</v>
       </c>
       <c r="J53" s="47"/>
-      <c r="K53" s="25"/>
+      <c r="K53" s="25" t="s">
+        <v>26</v>
+      </c>
       <c r="L53" s="25"/>
-      <c r="M53" s="25"/>
+      <c r="M53" s="25" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="54" spans="1:13" s="15" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A54" s="31"/>
@@ -8822,7 +8964,7 @@
         <v>62</v>
       </c>
       <c r="E54" s="50" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F54" s="31" t="s">
         <v>33</v>
@@ -8839,9 +8981,13 @@
         <v>2</v>
       </c>
       <c r="J54" s="51"/>
-      <c r="K54" s="31"/>
+      <c r="K54" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
+      <c r="M54" s="31" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="55" spans="1:13" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="31"/>
@@ -8851,7 +8997,7 @@
         <v>62</v>
       </c>
       <c r="E55" s="50" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F55" s="31" t="s">
         <v>33</v>
@@ -8868,9 +9014,13 @@
         <v>2</v>
       </c>
       <c r="J55" s="51"/>
-      <c r="K55" s="31"/>
+      <c r="K55" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
+      <c r="M55" s="31" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="56" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="29" t="s">
@@ -8896,11 +9046,11 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J56" s="74">
+      <c r="J56" s="62">
         <v>27</v>
       </c>
       <c r="K56" s="29" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L56" s="29"/>
       <c r="M56" s="29" t="s">
@@ -8931,9 +9081,9 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J57" s="75"/>
+      <c r="J57" s="63"/>
       <c r="K57" s="29" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L57" s="29"/>
       <c r="M57" s="29" t="s">
@@ -8964,9 +9114,9 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J58" s="75"/>
+      <c r="J58" s="63"/>
       <c r="K58" s="29" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L58" s="29"/>
       <c r="M58" s="29" t="s">
@@ -8978,16 +9128,16 @@
         <v>48</v>
       </c>
       <c r="B59" s="60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D59" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F59" s="32" t="s">
         <v>8</v>
@@ -9003,13 +9153,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J59" s="75"/>
+      <c r="J59" s="63"/>
       <c r="K59" s="32" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L59" s="32"/>
       <c r="M59" s="32" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
@@ -9017,16 +9167,16 @@
         <v>48</v>
       </c>
       <c r="B60" s="60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C60" s="32" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D60" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F60" s="32" t="s">
         <v>34</v>
@@ -9042,13 +9192,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J60" s="75"/>
+      <c r="J60" s="63"/>
       <c r="K60" s="32" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L60" s="32"/>
       <c r="M60" s="32" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
@@ -9056,16 +9206,16 @@
         <v>48</v>
       </c>
       <c r="B61" s="60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D61" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F61" s="32" t="s">
         <v>8</v>
@@ -9081,7 +9231,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J61" s="75"/>
+      <c r="J61" s="63"/>
       <c r="K61" s="32" t="s">
         <v>26</v>
       </c>
@@ -9101,8 +9251,8 @@
       <c r="D62" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E62" s="73" t="s">
-        <v>94</v>
+      <c r="E62" s="61" t="s">
+        <v>87</v>
       </c>
       <c r="F62" s="34"/>
       <c r="G62" s="34"/>
@@ -9114,13 +9264,13 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J62" s="76"/>
+      <c r="J62" s="64"/>
       <c r="K62" s="34" t="s">
         <v>26</v>
       </c>
       <c r="L62" s="34"/>
       <c r="M62" s="34" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -9131,13 +9281,13 @@
         <v>3.11</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D63" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F63" s="32" t="s">
         <v>8</v>
@@ -9153,13 +9303,13 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J63" s="75"/>
+      <c r="J63" s="63"/>
       <c r="K63" s="32" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L63" s="32"/>
       <c r="M63" s="32" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
@@ -9170,13 +9320,13 @@
         <v>3.11</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D64" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F64" s="32" t="s">
         <v>8</v>
@@ -9192,13 +9342,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J64" s="75"/>
+      <c r="J64" s="63"/>
       <c r="K64" s="32" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L64" s="32"/>
       <c r="M64" s="32" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -9209,13 +9359,13 @@
         <v>3.11</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D65" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F65" s="32" t="s">
         <v>8</v>
@@ -9231,74 +9381,122 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J65" s="75"/>
+      <c r="J65" s="63"/>
       <c r="K65" s="32" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L65" s="32"/>
       <c r="M65" s="32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A66" s="31"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" s="15" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="31" t="s">
+        <v>48</v>
+      </c>
       <c r="B66" s="31"/>
       <c r="C66" s="31"/>
       <c r="D66" s="31" t="s">
         <v>62</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="31"/>
-      <c r="I66" s="31"/>
+        <v>103</v>
+      </c>
+      <c r="F66" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H66" s="31" cm="1">
+        <f t="array" ref="H66">_xlfn.SWITCH(G66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I66" s="31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="J66" s="51"/>
-      <c r="K66" s="31"/>
+      <c r="K66" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L66" s="31"/>
-      <c r="M66" s="31"/>
-    </row>
-    <row r="67" spans="1:13" s="15" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="31"/>
+      <c r="M66" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" s="15" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="31" t="s">
+        <v>48</v>
+      </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
       <c r="D67" s="31" t="s">
         <v>62</v>
       </c>
       <c r="E67" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
+        <v>102</v>
+      </c>
+      <c r="F67" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H67" s="31" cm="1">
+        <f t="array" ref="H67">_xlfn.SWITCH(G67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I67" s="31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="J67" s="51"/>
-      <c r="K67" s="31"/>
+      <c r="K67" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-    </row>
-    <row r="68" spans="1:13" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="31"/>
+      <c r="M67" s="31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" s="15" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="31" t="s">
+        <v>48</v>
+      </c>
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
       <c r="D68" s="31" t="s">
         <v>62</v>
       </c>
       <c r="E68" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="31"/>
+        <v>105</v>
+      </c>
+      <c r="F68" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H68" s="31" cm="1">
+        <f t="array" ref="H68">_xlfn.SWITCH(G68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I68" s="31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="J68" s="51"/>
-      <c r="K68" s="31"/>
+      <c r="K68" s="31" t="s">
+        <v>26</v>
+      </c>
       <c r="L68" s="31"/>
-      <c r="M68" s="31"/>
+      <c r="M68" s="31" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="69" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="36" t="s">
         <v>48</v>
       </c>
       <c r="B69" s="36"/>
@@ -9321,11 +9519,11 @@
         <f>H69</f>
         <v>1</v>
       </c>
-      <c r="J69" s="61">
+      <c r="J69" s="65">
         <v>27</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="L69" s="36"/>
       <c r="M69" s="36" t="s">
@@ -9333,20 +9531,20 @@
       </c>
     </row>
     <row r="70" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A70" s="32" t="s">
+      <c r="A70" s="34" t="s">
         <v>48</v>
       </c>
       <c r="B70" s="34">
         <v>3.12</v>
       </c>
       <c r="C70" s="34" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D70" s="34" t="s">
         <v>41</v>
       </c>
       <c r="E70" s="35" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F70" s="34" t="s">
         <v>8</v>
@@ -9362,9 +9560,9 @@
         <f>H70</f>
         <v>8</v>
       </c>
-      <c r="J70" s="62"/>
+      <c r="J70" s="66"/>
       <c r="K70" s="34" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L70" s="34"/>
       <c r="M70" s="34" t="s">
@@ -9372,20 +9570,20 @@
       </c>
     </row>
     <row r="71" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="32" t="s">
+      <c r="A71" s="34" t="s">
         <v>48</v>
       </c>
       <c r="B71" s="34">
         <v>3.12</v>
       </c>
       <c r="C71" s="34" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D71" s="34" t="s">
         <v>41</v>
       </c>
       <c r="E71" s="35" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F71" s="34" t="s">
         <v>8</v>
@@ -9401,9 +9599,9 @@
         <f>H71</f>
         <v>5</v>
       </c>
-      <c r="J71" s="62"/>
+      <c r="J71" s="66"/>
       <c r="K71" s="34" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="L71" s="34"/>
       <c r="M71" s="34" t="s">
@@ -9411,20 +9609,20 @@
       </c>
     </row>
     <row r="72" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="32" t="s">
+      <c r="A72" s="34" t="s">
         <v>48</v>
       </c>
       <c r="B72" s="34">
         <v>3.13</v>
       </c>
       <c r="C72" s="34" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D72" s="34" t="s">
         <v>41</v>
       </c>
       <c r="E72" s="35" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F72" s="34" t="s">
         <v>33</v>
@@ -9440,7 +9638,7 @@
         <f>H72</f>
         <v>8</v>
       </c>
-      <c r="J72" s="62"/>
+      <c r="J72" s="66"/>
       <c r="K72" s="34" t="s">
         <v>26</v>
       </c>
@@ -9449,61 +9647,44 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="32" t="s">
+    <row r="73" spans="1:13" s="15" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B73" s="34"/>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E73" s="35"/>
-      <c r="F73" s="34" t="s">
+      <c r="B73" s="31"/>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="F73" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G73" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H73" s="34" cm="1">
+      <c r="G73" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H73" s="31" cm="1">
         <f t="array" ref="H73">_xlfn.SWITCH(G73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="I73" s="34">
+        <v>1</v>
+      </c>
+      <c r="I73" s="31">
         <f>H73</f>
-        <v>5</v>
-      </c>
-      <c r="J73" s="63"/>
-      <c r="K73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="31"/>
+      <c r="K73" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="L73" s="34"/>
-      <c r="M73" s="34" t="s">
+      <c r="L73" s="31"/>
+      <c r="M73" s="31" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" s="15" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="31"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E74" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="31"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="31"/>
-      <c r="K74" s="31"/>
-      <c r="L74" s="31"/>
-      <c r="M74" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="J69:J73"/>
+    <mergeCell ref="J69:J72"/>
     <mergeCell ref="J35:J42"/>
     <mergeCell ref="J46:J52"/>
     <mergeCell ref="F39:F42"/>

--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0871B4E-B768-4FBF-A9A2-AA0C7F515C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C2B064-0979-4C44-96D2-B8400ADEB069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15684" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="141">
   <si>
     <t>Epic</t>
   </si>
@@ -139,9 +139,6 @@
     <t>Scope</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
     <t>Atish</t>
   </si>
   <si>
@@ -5391,188 +5388,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>RenterBookedE-BikeRaiseIssue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout:
-1. Add heading: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Raise Issue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. Add </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upload an image of the issue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> camera upload
-3. Add subheading: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Describe the Issue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Add a TextField that accepts 500 characters max.
-4. Add </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Raise Issuse + Cancel Booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> secondary button
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Image</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of the issue *required. Until filled, navigation blocked onPress
-- Navigates to ?????????????
-5. Add </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Ignore Issue, Go Back </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>primary button
-- Navigates to ?????????????</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>RenterE-BikeReturn</t>
     </r>
     <r>
@@ -8078,53 +7893,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MANUAL/E2E:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Verify "Raise Issue" screen allows image upload and text description.
-2. Verify "Raise Issue + Cancel Booking" button triggers both cancellation and issue reporting flows.
-3. Verify "Ignore Issue, Go Back" button navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedE-BikeOptions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen, wiith the bottom sheet open.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">1. Verify heading: "Raise Issue"
 2. Verify cameraPicker component renders
 3. Verify </t>
@@ -8525,6 +8293,272 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeRaiseIssue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Add heading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upload an image of the issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> camera upload
+3. Add subheading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Describe the Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Add a TextField that accepts 500 characters max.
+4. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issuse + Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> secondary button
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Image</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the issue *required. Until filled, navigation blocked onPress
+- When filled. navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, the cancelled bike removed from the list of cards
+5. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ignore Issue, Go Back </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">primary button
+- Closes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeRaiseIssue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, navigates back to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, with the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeFeaturestoCheck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet open.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -8544,11 +8578,461 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-1. Verify clicking "Return E-Bike" on the end date navigates directly to Return screen.
-2. Verify clicking "Return E-Bike" before end date triggers the "Premature Return" modal component.
-3. Verify "Premature Return" modal: "Keep Riding" closes modal, "Return Anyway" proceeds.
-4. Verify Star Rating logic: Selecting 4th star auto-fills stars 1, 2, and 3 and 4.</t>
-    </r>
+1. Verify Raise Issue screen allows image upload and text description.
+2. Verify "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Raise Issue + Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" button discards the bike card from the list when navigated back to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedBikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+3. Verify "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ignore Issue, Go Back</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" button navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, wiith the bottom sheet open.</t>
+    </r>
+  </si>
+  <si>
+    <t>RenterE-BikeReturn &amp; RenterE-BikeReturn (PREMATURE)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MANUAL/E2E:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Verify clicking "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" on the end date navigates directly to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeReturn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen.
+2. Verify clicking "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>before</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> end date triggers the "prematureReturn" modal component.
+3. Verify "prematureReturn" modal: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Keep Riding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" closes modal, "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return Anyway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeReturn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen.
+4. Verify Star Rating logic: Selecting 4th star auto-fills stars 1, 2, and 3 and 4. 3rd star fills 1,2,3 and so on.
+5. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button does not trigger any action onPress until image uploaded.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeCurrentBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen:
+1. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return E-Bike button</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> renders with primary styling (button backgroundColor = Colors.primary)
+2. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prematureBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> modal renders onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button, if onPress occurs BEFORE endDate.
+- in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prematureBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> modal, verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Keep Riding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button renders with primary styling (button backgroundColor = Colors.primary) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Return Anyway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button renders with secondary styling (button label color = Colors.white)</t>
+    </r>
+  </si>
+  <si>
+    <t>3.12 - 3.13</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t>1. Verify heading: "Return E-Bike" renders
+2. Verify cameraPicker component renders
+3. Verify "Rate Your Experience" section renders
+4. Verify Leave a Comment section renders
+- Verify a textField that can take 500 characters max renders</t>
   </si>
 </sst>
 </file>
@@ -8662,7 +9146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8765,12 +9249,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -8836,7 +9314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8907,9 +9385,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8937,20 +9412,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8973,12 +9439,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8992,9 +9452,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9049,9 +9506,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9109,6 +9563,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10411,14 +10880,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="51" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="45" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.21875" style="75" customWidth="1"/>
+    <col min="5" max="5" width="80.21875" style="67" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -10434,7 +10903,7 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -10456,12 +10925,12 @@
         <v>18</v>
       </c>
       <c r="I1" s="4">
-        <f>SUM(I3:I42)</f>
-        <v>42</v>
+        <f>SUM(I2:I76)</f>
+        <v>115</v>
       </c>
       <c r="J1" s="4">
-        <f>SUM(J3:J42)</f>
-        <v>16</v>
+        <f>SUM(J2:J76)</f>
+        <v>83</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>5</v>
@@ -10475,22 +10944,22 @@
     </row>
     <row r="2" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="77">
+        <v>35</v>
+      </c>
+      <c r="B2" s="69">
         <v>3.1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>110</v>
+        <v>81</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>108</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>25</v>
@@ -10503,7 +10972,10 @@
         <f>H2</f>
         <v>1</v>
       </c>
-      <c r="J2" s="24"/>
+      <c r="J2" s="88">
+        <f>SUM(I2:I11)</f>
+        <v>18</v>
+      </c>
       <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
@@ -10514,22 +10986,22 @@
     </row>
     <row r="3" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="77">
+        <v>35</v>
+      </c>
+      <c r="B3" s="69">
         <v>3.1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>111</v>
+        <v>81</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>109</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>25</v>
@@ -10542,9 +11014,7 @@
         <f>H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="34">
-        <v>16</v>
-      </c>
+      <c r="J3" s="88"/>
       <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
@@ -10555,22 +11025,22 @@
     </row>
     <row r="4" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="77">
+        <v>35</v>
+      </c>
+      <c r="B4" s="69">
         <v>3.1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>112</v>
+        <v>81</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>110</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>25</v>
@@ -10583,7 +11053,7 @@
         <f t="shared" ref="I4:I35" si="0">H4</f>
         <v>1</v>
       </c>
-      <c r="J4" s="24"/>
+      <c r="J4" s="88"/>
       <c r="K4" s="5" t="s">
         <v>15</v>
       </c>
@@ -10594,22 +11064,22 @@
     </row>
     <row r="5" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="77">
+        <v>35</v>
+      </c>
+      <c r="B5" s="69">
         <v>3.1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>128</v>
+        <v>81</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>126</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>25</v>
@@ -10622,7 +11092,7 @@
         <f>H5</f>
         <v>1</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="88"/>
       <c r="K5" s="5" t="s">
         <v>15</v>
       </c>
@@ -10633,22 +11103,22 @@
     </row>
     <row r="6" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="77">
+        <v>35</v>
+      </c>
+      <c r="B6" s="69">
         <v>3.1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>113</v>
+        <v>81</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>111</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>25</v>
@@ -10661,7 +11131,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J6" s="24"/>
+      <c r="J6" s="88"/>
       <c r="K6" s="5" t="s">
         <v>15</v>
       </c>
@@ -10672,19 +11142,19 @@
     </row>
     <row r="7" spans="1:13" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="78">
+        <v>35</v>
+      </c>
+      <c r="B7" s="70">
         <v>3.1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>45</v>
+        <v>28</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>44</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>8</v>
@@ -10700,7 +11170,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J7" s="24"/>
+      <c r="J7" s="88"/>
       <c r="K7" s="6" t="s">
         <v>15</v>
       </c>
@@ -10711,19 +11181,19 @@
     </row>
     <row r="8" spans="1:13" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="78">
+        <v>35</v>
+      </c>
+      <c r="B8" s="70">
         <v>3.1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>8</v>
@@ -10739,7 +11209,7 @@
         <f>H8</f>
         <v>2</v>
       </c>
-      <c r="J8" s="24"/>
+      <c r="J8" s="88"/>
       <c r="K8" s="6" t="s">
         <v>15</v>
       </c>
@@ -10750,19 +11220,19 @@
     </row>
     <row r="9" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="78">
+        <v>35</v>
+      </c>
+      <c r="B9" s="70">
         <v>3.1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="58" t="s">
-        <v>39</v>
+        <v>28</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>38</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>8</v>
@@ -10778,7 +11248,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J9" s="24"/>
+      <c r="J9" s="88"/>
       <c r="K9" s="6" t="s">
         <v>15</v>
       </c>
@@ -10789,19 +11259,19 @@
     </row>
     <row r="10" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="78">
+        <v>35</v>
+      </c>
+      <c r="B10" s="70">
         <v>3.1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="58" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>8</v>
@@ -10817,7 +11287,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J10" s="35"/>
+      <c r="J10" s="88"/>
       <c r="K10" s="6" t="s">
         <v>15</v>
       </c>
@@ -10828,19 +11298,19 @@
     </row>
     <row r="11" spans="1:13" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="78">
+        <v>35</v>
+      </c>
+      <c r="B11" s="70">
         <v>3.1</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>37</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>8</v>
@@ -10856,7 +11326,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J11" s="24"/>
+      <c r="J11" s="88"/>
       <c r="K11" s="6" t="s">
         <v>15</v>
       </c>
@@ -10867,31 +11337,33 @@
     </row>
     <row r="12" spans="1:13" ht="129" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="79">
+        <v>35</v>
+      </c>
+      <c r="B12" s="71">
         <v>3.2</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="59" t="s">
-        <v>127</v>
+        <v>81</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>125</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7" t="str" cm="1">
+        <v>27</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="7" cm="1">
         <f t="array" ref="H12">_xlfn.SWITCH(G12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7">
         <f>H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="25"/>
+        <v>1</v>
+      </c>
+      <c r="J12" s="24"/>
       <c r="K12" s="7" t="s">
         <v>15</v>
       </c>
@@ -10902,31 +11374,33 @@
     </row>
     <row r="13" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="79">
+        <v>35</v>
+      </c>
+      <c r="B13" s="71">
         <v>3.2</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="59" t="s">
-        <v>114</v>
+        <v>81</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>112</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7" t="str" cm="1">
+        <v>27</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="7" cm="1">
         <f t="array" ref="H13">_xlfn.SWITCH(G13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="I13" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="36"/>
+        <v>1</v>
+      </c>
+      <c r="J13" s="33"/>
       <c r="K13" s="7" t="s">
         <v>15</v>
       </c>
@@ -10937,19 +11411,19 @@
     </row>
     <row r="14" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="72">
+        <v>3.2</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="53" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="80">
-        <v>3.2</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>37</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>8</v>
@@ -10965,7 +11439,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J14" s="37"/>
+      <c r="J14" s="34"/>
       <c r="K14" s="8" t="s">
         <v>15</v>
       </c>
@@ -10976,19 +11450,19 @@
     </row>
     <row r="15" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="80">
+        <v>35</v>
+      </c>
+      <c r="B15" s="72">
         <v>3.2</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="60" t="s">
-        <v>115</v>
+        <v>28</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>113</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
@@ -11004,7 +11478,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="24"/>
       <c r="K15" s="8" t="s">
         <v>15</v>
       </c>
@@ -11015,19 +11489,19 @@
     </row>
     <row r="16" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="80">
+        <v>35</v>
+      </c>
+      <c r="B16" s="72">
         <v>3.2</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="53" t="s">
         <v>41</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="60" t="s">
-        <v>42</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>8</v>
@@ -11043,7 +11517,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J16" s="32"/>
+      <c r="J16" s="31"/>
       <c r="K16" s="8" t="s">
         <v>15</v>
       </c>
@@ -11053,35 +11527,43 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="48"/>
-      <c r="B17" s="81"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="61" t="s">
+      <c r="A17" s="42"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="E17" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
+      <c r="G17" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="42" cm="1">
+        <f t="array" ref="H17">_xlfn.SWITCH(G17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I17" s="42">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J17" s="43"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
     </row>
     <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
-      <c r="B18" s="82"/>
+      <c r="B18" s="74"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="62" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>51</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>22</v>
@@ -11097,7 +11579,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J18" s="33"/>
+      <c r="J18" s="32"/>
       <c r="K18" s="17" t="s">
         <v>15</v>
       </c>
@@ -11108,13 +11590,13 @@
     </row>
     <row r="19" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
-      <c r="B19" s="82"/>
+      <c r="B19" s="74"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="62" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="E19" s="55" t="s">
+        <v>52</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>22</v>
@@ -11130,7 +11612,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J19" s="33"/>
+      <c r="J19" s="32"/>
       <c r="K19" s="17" t="s">
         <v>15</v>
       </c>
@@ -11141,22 +11623,22 @@
     </row>
     <row r="20" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="83">
+        <v>35</v>
+      </c>
+      <c r="B20" s="75">
         <v>3.3</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="63" t="s">
-        <v>118</v>
+        <v>81</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>116</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>19</v>
@@ -11169,7 +11651,7 @@
         <f>H20</f>
         <v>2</v>
       </c>
-      <c r="J20" s="28"/>
+      <c r="J20" s="27"/>
       <c r="K20" s="10" t="s">
         <v>15</v>
       </c>
@@ -11180,19 +11662,19 @@
     </row>
     <row r="21" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="83">
+        <v>35</v>
+      </c>
+      <c r="B21" s="75">
         <v>3.3</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="63" t="s">
-        <v>117</v>
+        <v>81</v>
+      </c>
+      <c r="E21" s="56" t="s">
+        <v>115</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>8</v>
@@ -11208,7 +11690,7 @@
         <f>H21</f>
         <v>1</v>
       </c>
-      <c r="J21" s="27"/>
+      <c r="J21" s="26"/>
       <c r="K21" s="10" t="s">
         <v>15</v>
       </c>
@@ -11219,22 +11701,22 @@
     </row>
     <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="83">
+        <v>35</v>
+      </c>
+      <c r="B22" s="75">
         <v>3.4</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="63" t="s">
-        <v>119</v>
+        <v>81</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>117</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>25</v>
@@ -11247,7 +11729,7 @@
         <f>H22</f>
         <v>1</v>
       </c>
-      <c r="J22" s="28"/>
+      <c r="J22" s="27"/>
       <c r="K22" s="10" t="s">
         <v>15</v>
       </c>
@@ -11258,22 +11740,22 @@
     </row>
     <row r="23" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="83">
+        <v>35</v>
+      </c>
+      <c r="B23" s="75">
         <v>3.4</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="63" t="s">
-        <v>116</v>
+        <v>81</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>114</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>25</v>
@@ -11286,7 +11768,7 @@
         <f>H23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="28"/>
+      <c r="J23" s="27"/>
       <c r="K23" s="10" t="s">
         <v>15</v>
       </c>
@@ -11297,30 +11779,35 @@
     </row>
     <row r="24" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="84">
+        <v>35</v>
+      </c>
+      <c r="B24" s="76">
         <v>3.3</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="64" t="s">
-        <v>47</v>
+        <v>28</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>46</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11" t="str" cm="1">
+      <c r="G24" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="11" cm="1">
         <f t="array" ref="H24">_xlfn.SWITCH(G24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="26"/>
+        <v>1</v>
+      </c>
+      <c r="I24" s="11">
+        <f t="shared" ref="I24:I76" si="1">H24</f>
+        <v>1</v>
+      </c>
+      <c r="J24" s="25"/>
       <c r="K24" s="11" t="s">
         <v>15</v>
       </c>
@@ -11331,30 +11818,35 @@
     </row>
     <row r="25" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="84">
+        <v>35</v>
+      </c>
+      <c r="B25" s="76">
         <v>3.4</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="64" t="s">
-        <v>48</v>
+        <v>28</v>
+      </c>
+      <c r="E25" s="57" t="s">
+        <v>47</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11" t="str" cm="1">
+      <c r="G25" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="11" cm="1">
         <f t="array" ref="H25">_xlfn.SWITCH(G25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="26"/>
+        <v>1</v>
+      </c>
+      <c r="I25" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J25" s="25"/>
       <c r="K25" s="11" t="s">
         <v>15</v>
       </c>
@@ -11364,42 +11856,58 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>83</v>
+      <c r="A26" s="42"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="54" t="s">
+        <v>82</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
+      <c r="G26" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="42" cm="1">
+        <f t="array" ref="H26">_xlfn.SWITCH(G26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I26" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
-      <c r="B27" s="82"/>
+      <c r="B27" s="74"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="55" t="s">
         <v>49</v>
-      </c>
-      <c r="E27" s="62" t="s">
-        <v>50</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
+      <c r="G27" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="17" cm="1">
+        <f t="array" ref="H27">_xlfn.SWITCH(G27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I27" s="17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="J27" s="17"/>
       <c r="K27" s="17" t="s">
         <v>15</v>
@@ -11411,20 +11919,28 @@
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
-      <c r="B28" s="82"/>
+      <c r="B28" s="74"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="62" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="E28" s="55" t="s">
+        <v>50</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
+      <c r="G28" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="17" cm="1">
+        <f t="array" ref="H28">_xlfn.SWITCH(G28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I28" s="17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="J28" s="17"/>
       <c r="K28" s="17" t="s">
         <v>15</v>
@@ -11436,62 +11952,70 @@
     </row>
     <row r="29" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="85">
+        <v>35</v>
+      </c>
+      <c r="B29" s="77">
         <v>3.6</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E29" s="65" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="52"/>
+        <v>81</v>
+      </c>
+      <c r="E29" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="41" cm="1">
+        <f t="array" ref="H29">_xlfn.SWITCH(G29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I29" s="41">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J29" s="46"/>
       <c r="K29" s="12"/>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
     </row>
     <row r="30" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="85">
+        <v>35</v>
+      </c>
+      <c r="B30" s="77">
         <v>3.5</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="65" t="s">
-        <v>121</v>
+        <v>81</v>
+      </c>
+      <c r="E30" s="58" t="s">
+        <v>119</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="52" cm="1">
+        <v>27</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="12" cm="1">
         <f t="array" ref="H30">_xlfn.SWITCH(G30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I30" s="52">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J30" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="I30" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J30" s="46"/>
       <c r="K30" s="12" t="s">
         <v>15</v>
       </c>
@@ -11502,25 +12026,33 @@
     </row>
     <row r="31" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="85">
+        <v>35</v>
+      </c>
+      <c r="B31" s="77">
         <v>3.5</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="65" t="s">
-        <v>125</v>
-      </c>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
+        <v>81</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="12" cm="1">
+        <f t="array" ref="H31">_xlfn.SWITCH(G31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I31" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J31" s="46"/>
       <c r="K31" s="12" t="s">
         <v>15</v>
       </c>
@@ -11531,25 +12063,33 @@
     </row>
     <row r="32" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="85">
+        <v>35</v>
+      </c>
+      <c r="B32" s="77">
         <v>3.6</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E32" s="65" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
+        <v>81</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="12" cm="1">
+        <f t="array" ref="H32">_xlfn.SWITCH(G32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I32" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J32" s="46"/>
       <c r="K32" s="12" t="s">
         <v>15</v>
       </c>
@@ -11560,25 +12100,33 @@
     </row>
     <row r="33" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="85">
+        <v>35</v>
+      </c>
+      <c r="B33" s="77">
         <v>3.7</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="65" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
+        <v>81</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" s="12" cm="1">
+        <f t="array" ref="H33">_xlfn.SWITCH(G33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I33" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J33" s="46"/>
       <c r="K33" s="12" t="s">
         <v>15</v>
       </c>
@@ -11589,60 +12137,68 @@
     </row>
     <row r="34" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="85">
+        <v>35</v>
+      </c>
+      <c r="B34" s="77">
         <v>3.8</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="45"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="52"/>
+        <v>81</v>
+      </c>
+      <c r="E34" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="41"/>
+      <c r="G34" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="12" cm="1">
+        <f t="array" ref="H34">_xlfn.SWITCH(G34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I34" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J34" s="46"/>
       <c r="K34" s="12"/>
       <c r="L34" s="12"/>
       <c r="M34" s="12"/>
     </row>
     <row r="35" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="86">
+        <v>35</v>
+      </c>
+      <c r="B35" s="78">
         <v>3.5</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G35" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="53" cm="1">
+      <c r="G35" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="13" cm="1">
         <f t="array" ref="H35">_xlfn.SWITCH(G35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="I35" s="53">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="J35" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="I35" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J35" s="46"/>
       <c r="K35" s="13" t="s">
         <v>15</v>
       </c>
@@ -11653,25 +12209,33 @@
     </row>
     <row r="36" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="86">
+        <v>35</v>
+      </c>
+      <c r="B36" s="78">
         <v>3.5</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="52"/>
+        <v>28</v>
+      </c>
+      <c r="E36" s="59" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" s="13" cm="1">
+        <f t="array" ref="H36">_xlfn.SWITCH(G36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I36" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J36" s="46"/>
       <c r="K36" s="13" t="s">
         <v>15</v>
       </c>
@@ -11682,25 +12246,33 @@
     </row>
     <row r="37" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="86">
+        <v>35</v>
+      </c>
+      <c r="B37" s="78">
         <v>3.6</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="52"/>
+        <v>28</v>
+      </c>
+      <c r="E37" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="13" cm="1">
+        <f t="array" ref="H37">_xlfn.SWITCH(G37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I37" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J37" s="46"/>
       <c r="K37" s="13" t="s">
         <v>15</v>
       </c>
@@ -11711,25 +12283,33 @@
     </row>
     <row r="38" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="86">
+        <v>35</v>
+      </c>
+      <c r="B38" s="78">
         <v>3.7</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="52"/>
+        <v>28</v>
+      </c>
+      <c r="E38" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="13" cm="1">
+        <f t="array" ref="H38">_xlfn.SWITCH(G38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I38" s="13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J38" s="46"/>
       <c r="K38" s="13" t="s">
         <v>15</v>
       </c>
@@ -11740,23 +12320,31 @@
     </row>
     <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
-      <c r="B39" s="86">
+      <c r="B39" s="78">
         <v>3.8</v>
       </c>
       <c r="C39" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" s="67" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="29"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="30" cm="1">
+        <f t="array" ref="H39">_xlfn.SWITCH(G39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I39" s="30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J39" s="28"/>
       <c r="K39" s="13" t="s">
         <v>15</v>
       </c>
@@ -11766,35 +12354,43 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
-      <c r="B40" s="81"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="48"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="48"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" s="44" cm="1">
+        <f t="array" ref="H40">_xlfn.SWITCH(G40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I40" s="44">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="44"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
     </row>
     <row r="41" spans="1:13" s="9" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="74"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="69" t="s">
-        <v>78</v>
+        <v>48</v>
+      </c>
+      <c r="E41" s="62" t="s">
+        <v>77</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>22</v>
@@ -11807,7 +12403,7 @@
         <v>2</v>
       </c>
       <c r="I41" s="13">
-        <f t="shared" ref="I41:I44" si="1">H41</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J41" s="17"/>
@@ -11821,15 +12417,15 @@
     </row>
     <row r="42" spans="1:13" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="74"/>
       <c r="C42" s="17"/>
       <c r="D42" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="69" t="s">
-        <v>56</v>
+        <v>48</v>
+      </c>
+      <c r="E42" s="62" t="s">
+        <v>55</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>22</v>
@@ -11856,25 +12452,33 @@
     </row>
     <row r="43" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43" s="87">
+        <v>35</v>
+      </c>
+      <c r="B43" s="79">
         <v>3.9</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
+        <v>81</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" s="29" cm="1">
+        <f t="array" ref="H43">_xlfn.SWITCH(G43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I43" s="29">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J43" s="35"/>
       <c r="K43" s="15" t="s">
         <v>15</v>
       </c>
@@ -11885,35 +12489,35 @@
     </row>
     <row r="44" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A44" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="87">
+        <v>35</v>
+      </c>
+      <c r="B44" s="79">
         <v>3.9</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="F44" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="38" cm="1">
+        <v>81</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" s="15" cm="1">
         <f t="array" ref="H44">_xlfn.SWITCH(G44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I44" s="38">
+        <v>1</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J44" s="38">
+        <v>1</v>
+      </c>
+      <c r="J44" s="87">
         <v>11</v>
       </c>
       <c r="K44" s="15" t="s">
@@ -11926,25 +12530,33 @@
     </row>
     <row r="45" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="87">
+        <v>35</v>
+      </c>
+      <c r="B45" s="79">
         <v>3.9</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E45" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="39"/>
+        <v>81</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" s="15" cm="1">
+        <f t="array" ref="H45">_xlfn.SWITCH(G45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J45" s="87"/>
       <c r="K45" s="15" t="s">
         <v>15</v>
       </c>
@@ -11955,25 +12567,33 @@
     </row>
     <row r="46" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A46" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" s="87">
+        <v>35</v>
+      </c>
+      <c r="B46" s="79">
         <v>3.9</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E46" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
+        <v>81</v>
+      </c>
+      <c r="E46" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" s="15" cm="1">
+        <f t="array" ref="H46">_xlfn.SWITCH(G46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J46" s="87"/>
       <c r="K46" s="15" t="s">
         <v>15</v>
       </c>
@@ -11984,54 +12604,54 @@
     </row>
     <row r="47" spans="1:13" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47" s="88">
+        <v>35</v>
+      </c>
+      <c r="B47" s="80">
         <v>3.9</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E47" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="F47" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="H47" s="14" cm="1">
+      <c r="H47" s="86" cm="1">
         <f t="array" ref="H47">_xlfn.SWITCH(G47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="I47" s="14">
-        <f t="shared" ref="I47:I69" si="2">H47</f>
+      <c r="I47" s="86">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J47" s="39"/>
+      <c r="J47" s="35"/>
       <c r="K47" s="15"/>
       <c r="L47" s="15"/>
       <c r="M47" s="15"/>
     </row>
     <row r="48" spans="1:13" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48" s="88">
+        <v>35</v>
+      </c>
+      <c r="B48" s="80">
         <v>3.9</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E48" s="55" t="s">
-        <v>89</v>
+        <v>28</v>
+      </c>
+      <c r="E48" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>8</v>
@@ -12044,10 +12664,10 @@
         <v>5</v>
       </c>
       <c r="I48" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J48" s="39"/>
+      <c r="J48" s="35"/>
       <c r="K48" s="14" t="s">
         <v>15</v>
       </c>
@@ -12058,19 +12678,19 @@
     </row>
     <row r="49" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49" s="88">
+        <v>35</v>
+      </c>
+      <c r="B49" s="80">
         <v>3.9</v>
       </c>
       <c r="C49" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="48" t="s">
         <v>60</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="55" t="s">
-        <v>61</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>8</v>
@@ -12083,10 +12703,10 @@
         <v>2</v>
       </c>
       <c r="I49" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J49" s="40"/>
+      <c r="J49" s="36"/>
       <c r="K49" s="14" t="s">
         <v>15</v>
       </c>
@@ -12097,19 +12717,19 @@
     </row>
     <row r="50" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="88">
+        <v>35</v>
+      </c>
+      <c r="B50" s="80">
         <v>3.9</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" s="55" t="s">
-        <v>62</v>
+        <v>28</v>
+      </c>
+      <c r="E50" s="48" t="s">
+        <v>61</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>8</v>
@@ -12122,10 +12742,10 @@
         <v>1</v>
       </c>
       <c r="I50" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J50" s="30"/>
+      <c r="J50" s="29"/>
       <c r="K50" s="14" t="s">
         <v>15</v>
       </c>
@@ -12135,33 +12755,41 @@
       </c>
     </row>
     <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="48"/>
-      <c r="B51" s="81"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E51" s="68" t="s">
-        <v>108</v>
-      </c>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="49"/>
-      <c r="K51" s="48"/>
-      <c r="L51" s="48"/>
-      <c r="M51" s="48"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="73"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H51" s="42" cm="1">
+        <f t="array" ref="H51">_xlfn.SWITCH(G51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I51" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J51" s="43"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42"/>
+      <c r="M51" s="42"/>
     </row>
     <row r="52" spans="1:13" s="9" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
-      <c r="B52" s="82"/>
+      <c r="B52" s="74"/>
       <c r="C52" s="17"/>
       <c r="D52" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E52" s="62" t="s">
-        <v>63</v>
+        <v>48</v>
+      </c>
+      <c r="E52" s="55" t="s">
+        <v>62</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>22</v>
@@ -12174,10 +12802,10 @@
         <v>2</v>
       </c>
       <c r="I52" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J52" s="33"/>
+      <c r="J52" s="32"/>
       <c r="K52" s="17" t="s">
         <v>15</v>
       </c>
@@ -12188,13 +12816,13 @@
     </row>
     <row r="53" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
-      <c r="B53" s="82"/>
+      <c r="B53" s="74"/>
       <c r="C53" s="17"/>
       <c r="D53" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="62" t="s">
-        <v>64</v>
+        <v>48</v>
+      </c>
+      <c r="E53" s="55" t="s">
+        <v>63</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>22</v>
@@ -12207,10 +12835,10 @@
         <v>2</v>
       </c>
       <c r="I53" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J53" s="33"/>
+      <c r="J53" s="32"/>
       <c r="K53" s="17" t="s">
         <v>15</v>
       </c>
@@ -12221,22 +12849,22 @@
     </row>
     <row r="54" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B54" s="89" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B54" s="81" t="s">
+        <v>64</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="F54" s="16" t="s">
         <v>27</v>
-      </c>
-      <c r="E54" s="70" t="s">
-        <v>134</v>
-      </c>
-      <c r="F54" s="16" t="s">
-        <v>28</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>25</v>
@@ -12246,10 +12874,10 @@
         <v>1</v>
       </c>
       <c r="I54" s="16">
-        <f>H54</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J54" s="43"/>
+      <c r="J54" s="39"/>
       <c r="K54" s="16" t="s">
         <v>15</v>
       </c>
@@ -12260,72 +12888,88 @@
     </row>
     <row r="55" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="89" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B55" s="81" t="s">
+        <v>64</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E55" s="70" t="s">
-        <v>133</v>
+        <v>81</v>
+      </c>
+      <c r="E55" s="63" t="s">
+        <v>130</v>
       </c>
       <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="43"/>
+      <c r="G55" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H55" s="16" cm="1">
+        <f t="array" ref="H55">_xlfn.SWITCH(G55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I55" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J55" s="39"/>
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
     </row>
     <row r="56" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A56" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" s="89" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B56" s="81" t="s">
+        <v>64</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="70" t="s">
-        <v>132</v>
+        <v>81</v>
+      </c>
+      <c r="E56" s="63" t="s">
+        <v>129</v>
       </c>
       <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="43"/>
+      <c r="G56" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" s="16" cm="1">
+        <f t="array" ref="H56">_xlfn.SWITCH(G56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I56" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J56" s="39"/>
       <c r="K56" s="16"/>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
     </row>
     <row r="57" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B57" s="89" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B57" s="81" t="s">
+        <v>64</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" s="16" t="s">
         <v>27</v>
-      </c>
-      <c r="E57" s="70" t="s">
-        <v>131</v>
-      </c>
-      <c r="F57" s="16" t="s">
-        <v>28</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>25</v>
@@ -12335,10 +12979,10 @@
         <v>1</v>
       </c>
       <c r="I57" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J57" s="42">
+      <c r="J57" s="38">
         <v>27</v>
       </c>
       <c r="K57" s="16" t="s">
@@ -12349,70 +12993,76 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="89"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="70"/>
-      <c r="F58" s="16" t="s">
+    <row r="58" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H58" s="16" cm="1">
+      <c r="E58" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="18" cm="1">
         <f t="array" ref="H58">_xlfn.SWITCH(G58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="I58" s="16">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="J58" s="43"/>
-      <c r="K58" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" s="18">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J58" s="39"/>
+      <c r="K58" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16" t="s">
+      <c r="L58" s="18"/>
+      <c r="M58" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A59" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B59" s="41" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B59" s="37" t="s">
+        <v>64</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E59" s="71" t="s">
-        <v>88</v>
+        <v>28</v>
+      </c>
+      <c r="E59" s="64" t="s">
+        <v>100</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H59" s="18" cm="1">
         <f t="array" ref="H59">_xlfn.SWITCH(G59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="18">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="J59" s="43"/>
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J59" s="39"/>
       <c r="K59" s="18" t="s">
         <v>15</v>
       </c>
@@ -12421,37 +13071,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="41" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B60" s="37" t="s">
+        <v>64</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E60" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" s="64" t="s">
         <v>101</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H60" s="18" cm="1">
         <f t="array" ref="H60">_xlfn.SWITCH(G60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="18">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="J60" s="43"/>
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J60" s="39"/>
       <c r="K60" s="18" t="s">
         <v>15</v>
       </c>
@@ -12460,37 +13110,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="41" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B61" s="37" t="s">
+        <v>64</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>67</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E61" s="72" t="s">
-        <v>102</v>
+        <v>28</v>
+      </c>
+      <c r="E61" s="64" t="s">
+        <v>133</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H61" s="18" cm="1">
         <f t="array" ref="H61">_xlfn.SWITCH(G61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I61" s="18">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="J61" s="43"/>
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J61" s="39"/>
       <c r="K61" s="18" t="s">
         <v>15</v>
       </c>
@@ -12499,21 +13149,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="144" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B62" s="41" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="B62" s="37">
+        <v>3.11</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>68</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E62" s="72" t="s">
-        <v>105</v>
+        <v>28</v>
+      </c>
+      <c r="E62" s="64" t="s">
+        <v>89</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>8</v>
@@ -12526,10 +13176,10 @@
         <v>1</v>
       </c>
       <c r="I62" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J62" s="43"/>
+      <c r="J62" s="39"/>
       <c r="K62" s="18" t="s">
         <v>15</v>
       </c>
@@ -12538,37 +13188,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B63" s="41">
+        <v>35</v>
+      </c>
+      <c r="B63" s="37">
         <v>3.11</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E63" s="71" t="s">
-        <v>90</v>
+        <v>28</v>
+      </c>
+      <c r="E63" s="64" t="s">
+        <v>72</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H63" s="18" cm="1">
         <f t="array" ref="H63">_xlfn.SWITCH(G63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I63" s="18">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="J63" s="43"/>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J63" s="39"/>
       <c r="K63" s="18" t="s">
         <v>15</v>
       </c>
@@ -12577,37 +13227,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B64" s="41">
+        <v>35</v>
+      </c>
+      <c r="B64" s="37">
         <v>3.11</v>
       </c>
       <c r="C64" s="18" t="s">
         <v>69</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E64" s="71" t="s">
-        <v>73</v>
+        <v>28</v>
+      </c>
+      <c r="E64" s="64" t="s">
+        <v>103</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H64" s="18" cm="1">
         <f t="array" ref="H64">_xlfn.SWITCH(G64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I64" s="18">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="J64" s="43"/>
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J64" s="39"/>
       <c r="K64" s="18" t="s">
         <v>15</v>
       </c>
@@ -12616,37 +13266,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B65" s="41">
+        <v>35</v>
+      </c>
+      <c r="B65" s="37">
         <v>3.11</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>70</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65" s="71" t="s">
-        <v>104</v>
+        <v>28</v>
+      </c>
+      <c r="E65" s="64" t="s">
+        <v>65</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>8</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H65" s="18" cm="1">
         <f t="array" ref="H65">_xlfn.SWITCH(G65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I65" s="18">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="J65" s="43"/>
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J65" s="39"/>
       <c r="K65" s="18" t="s">
         <v>15</v>
       </c>
@@ -12655,56 +13305,52 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B66" s="41">
-        <v>3.11</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E66" s="71" t="s">
-        <v>66</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="G66" s="18" t="s">
+    <row r="66" spans="1:13" s="9" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="74"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H66" s="18" cm="1">
+      <c r="H66" s="17" cm="1">
         <f t="array" ref="H66">_xlfn.SWITCH(G66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I66" s="18">
-        <f t="shared" si="2"/>
+      <c r="I66" s="17">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J66" s="43"/>
-      <c r="K66" s="18" t="s">
+      <c r="J66" s="32"/>
+      <c r="K66" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18" t="s">
+      <c r="L66" s="17"/>
+      <c r="M66" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:13" s="9" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" s="9" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B67" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="B67" s="74"/>
       <c r="C67" s="17"/>
       <c r="D67" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E67" s="62" t="s">
-        <v>77</v>
+        <v>48</v>
+      </c>
+      <c r="E67" s="55" t="s">
+        <v>75</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>22</v>
@@ -12717,10 +13363,10 @@
         <v>1</v>
       </c>
       <c r="I67" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J67" s="33"/>
+      <c r="J67" s="32"/>
       <c r="K67" s="17" t="s">
         <v>15</v>
       </c>
@@ -12729,17 +13375,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:13" s="9" customFormat="1" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B68" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="B68" s="74"/>
       <c r="C68" s="17"/>
       <c r="D68" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E68" s="62" t="s">
-        <v>76</v>
+        <v>48</v>
+      </c>
+      <c r="E68" s="55" t="s">
+        <v>78</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>22</v>
@@ -12752,10 +13398,10 @@
         <v>1</v>
       </c>
       <c r="I68" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J68" s="33"/>
+      <c r="J68" s="32"/>
       <c r="K68" s="17" t="s">
         <v>15</v>
       </c>
@@ -12764,56 +13410,62 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B69" s="82"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E69" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G69" s="17" t="s">
+    <row r="69" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E69" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H69" s="17" cm="1">
+      <c r="H69" s="20" cm="1">
         <f t="array" ref="H69">_xlfn.SWITCH(G69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I69" s="17">
-        <f t="shared" si="2"/>
+      <c r="I69" s="20">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J69" s="33"/>
-      <c r="K69" s="17" t="s">
+      <c r="J69" s="84">
+        <v>27</v>
+      </c>
+      <c r="K69" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L69" s="17"/>
-      <c r="M69" s="17" t="s">
+      <c r="L69" s="20"/>
+      <c r="M69" s="20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B70" s="90"/>
-      <c r="C70" s="20"/>
+    <row r="70" spans="1:13" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="20"/>
+      <c r="B70" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>135</v>
+      </c>
       <c r="D70" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E70" s="73" t="s">
-        <v>136</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>28</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="E70" s="65" t="s">
+        <v>137</v>
+      </c>
+      <c r="F70" s="20"/>
       <c r="G70" s="20" t="s">
         <v>25</v>
       </c>
@@ -12822,90 +13474,76 @@
         <v>1</v>
       </c>
       <c r="I70" s="20">
-        <f>H70</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J70" s="46">
-        <v>27</v>
-      </c>
-      <c r="K70" s="20" t="s">
-        <v>15</v>
-      </c>
+      <c r="J70" s="85"/>
+      <c r="K70" s="20"/>
       <c r="L70" s="20"/>
-      <c r="M70" s="20" t="s">
-        <v>7</v>
-      </c>
+      <c r="M70" s="20"/>
     </row>
-    <row r="71" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A71" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B71" s="91">
+    <row r="71" spans="1:13" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="20"/>
+      <c r="B71" s="82" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" s="20" cm="1">
+        <f t="array" ref="H71">_xlfn.SWITCH(G71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I71" s="20">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J71" s="85"/>
+      <c r="K71" s="20"/>
+      <c r="L71" s="20"/>
+      <c r="M71" s="20"/>
+    </row>
+    <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A72" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="83">
         <v>3.12</v>
       </c>
-      <c r="C71" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E71" s="74" t="s">
-        <v>75</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" s="19" cm="1">
-        <f t="array" ref="H71">_xlfn.SWITCH(G71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="I71" s="19">
-        <f>H71</f>
-        <v>8</v>
-      </c>
-      <c r="J71" s="47"/>
-      <c r="K71" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A72" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B72" s="91">
-        <v>3.12</v>
-      </c>
       <c r="C72" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E72" s="74" t="s">
-        <v>106</v>
+        <v>28</v>
+      </c>
+      <c r="E72" s="66" t="s">
+        <v>74</v>
       </c>
       <c r="F72" s="19" t="s">
         <v>8</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H72" s="19" cm="1">
         <f t="array" ref="H72">_xlfn.SWITCH(G72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I72" s="19">
-        <f>H72</f>
-        <v>5</v>
-      </c>
-      <c r="J72" s="47"/>
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J72" s="85"/>
       <c r="K72" s="19" t="s">
         <v>15</v>
       </c>
@@ -12914,37 +13552,37 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A73" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B73" s="91">
-        <v>3.13</v>
+        <v>35</v>
+      </c>
+      <c r="B73" s="83">
+        <v>3.12</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E73" s="74" t="s">
-        <v>103</v>
+        <v>28</v>
+      </c>
+      <c r="E73" s="66" t="s">
+        <v>104</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H73" s="19" cm="1">
         <f t="array" ref="H73">_xlfn.SWITCH(G73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I73" s="19">
-        <f>H73</f>
-        <v>8</v>
-      </c>
-      <c r="J73" s="47"/>
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J73" s="85"/>
       <c r="K73" s="19" t="s">
         <v>15</v>
       </c>
@@ -12953,67 +13591,114 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B74" s="81"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="E74" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="F74" s="48" t="s">
+    <row r="74" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" s="83">
+        <v>3.13</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="F74" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
-      <c r="J74" s="49"/>
-      <c r="K74" s="48"/>
-      <c r="L74" s="48"/>
-      <c r="M74" s="48"/>
+      <c r="G74" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H74" s="19" cm="1">
+        <f t="array" ref="H74">_xlfn.SWITCH(G74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I74" s="19">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="J74" s="85"/>
+      <c r="K74" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L74" s="19"/>
+      <c r="M74" s="19" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="75" spans="1:13" s="9" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B75" s="82"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E75" s="62" t="s">
+    <row r="75" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" s="73"/>
+      <c r="C75" s="42"/>
+      <c r="D75" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E75" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="G75" s="17" t="s">
+      <c r="G75" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="H75" s="17" cm="1">
+      <c r="H75" s="42" cm="1">
         <f t="array" ref="H75">_xlfn.SWITCH(G75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I75" s="17">
-        <f>H75</f>
+      <c r="I75" s="42">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J75" s="17"/>
-      <c r="K75" s="17" t="s">
+      <c r="J75" s="43"/>
+      <c r="K75" s="42"/>
+      <c r="L75" s="42"/>
+      <c r="M75" s="42"/>
+    </row>
+    <row r="76" spans="1:13" s="9" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A76" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" s="74"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H76" s="17" cm="1">
+        <f t="array" ref="H76">_xlfn.SWITCH(G76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I76" s="17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="L75" s="17"/>
-      <c r="M75" s="17" t="s">
+      <c r="L76" s="17"/>
+      <c r="M76" s="17" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J70:J73"/>
+    <mergeCell ref="J2:J11"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13034,16 +13719,16 @@
   <sheetData>
     <row r="1" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
@@ -13208,7 +13893,7 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="W15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -13262,7 +13947,7 @@
   <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="51" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="45" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="33" style="1" customWidth="1"/>
@@ -13277,38 +13962,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C2B064-0979-4C44-96D2-B8400ADEB069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D98EAF-D7B4-47CE-BE0B-0D55A792638C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="141">
   <si>
     <t>Epic</t>
   </si>
@@ -9314,7 +9314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9385,53 +9385,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9442,17 +9403,11 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9565,19 +9520,73 @@
     <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10884,10 +10893,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.21875" style="67" customWidth="1"/>
+    <col min="5" max="5" width="80.21875" style="52" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -10903,7 +10912,7 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -10930,7 +10939,7 @@
       </c>
       <c r="J1" s="4">
         <f>SUM(J2:J76)</f>
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>5</v>
@@ -10946,7 +10955,7 @@
       <c r="A2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="69">
+      <c r="B2" s="54">
         <v>3.1</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -10955,7 +10964,7 @@
       <c r="D2" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="34" t="s">
         <v>108</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -10972,7 +10981,7 @@
         <f>H2</f>
         <v>1</v>
       </c>
-      <c r="J2" s="88">
+      <c r="J2" s="70">
         <f>SUM(I2:I11)</f>
         <v>18</v>
       </c>
@@ -10988,7 +10997,7 @@
       <c r="A3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="69">
+      <c r="B3" s="54">
         <v>3.1</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -10997,7 +11006,7 @@
       <c r="D3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="35" t="s">
         <v>109</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -11014,7 +11023,7 @@
         <f>H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="88"/>
+      <c r="J3" s="70"/>
       <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
@@ -11027,7 +11036,7 @@
       <c r="A4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="69">
+      <c r="B4" s="54">
         <v>3.1</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -11036,7 +11045,7 @@
       <c r="D4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="35" t="s">
         <v>110</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -11050,10 +11059,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" ref="I4:I35" si="0">H4</f>
+        <f t="shared" ref="I4:I19" si="0">H4</f>
         <v>1</v>
       </c>
-      <c r="J4" s="88"/>
+      <c r="J4" s="70"/>
       <c r="K4" s="5" t="s">
         <v>15</v>
       </c>
@@ -11066,7 +11075,7 @@
       <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="69">
+      <c r="B5" s="54">
         <v>3.1</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -11075,7 +11084,7 @@
       <c r="D5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="35" t="s">
         <v>126</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -11092,7 +11101,7 @@
         <f>H5</f>
         <v>1</v>
       </c>
-      <c r="J5" s="88"/>
+      <c r="J5" s="70"/>
       <c r="K5" s="5" t="s">
         <v>15</v>
       </c>
@@ -11105,7 +11114,7 @@
       <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="69">
+      <c r="B6" s="54">
         <v>3.1</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -11114,7 +11123,7 @@
       <c r="D6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="34" t="s">
         <v>111</v>
       </c>
       <c r="F6" s="5" t="s">
@@ -11131,7 +11140,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J6" s="88"/>
+      <c r="J6" s="70"/>
       <c r="K6" s="5" t="s">
         <v>15</v>
       </c>
@@ -11144,7 +11153,7 @@
       <c r="A7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="70">
+      <c r="B7" s="55">
         <v>3.1</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -11153,7 +11162,7 @@
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="36" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -11170,7 +11179,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J7" s="88"/>
+      <c r="J7" s="70"/>
       <c r="K7" s="6" t="s">
         <v>15</v>
       </c>
@@ -11183,7 +11192,7 @@
       <c r="A8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="70">
+      <c r="B8" s="55">
         <v>3.1</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -11192,7 +11201,7 @@
       <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="36" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -11209,7 +11218,7 @@
         <f>H8</f>
         <v>2</v>
       </c>
-      <c r="J8" s="88"/>
+      <c r="J8" s="70"/>
       <c r="K8" s="6" t="s">
         <v>15</v>
       </c>
@@ -11222,7 +11231,7 @@
       <c r="A9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="70">
+      <c r="B9" s="55">
         <v>3.1</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -11231,7 +11240,7 @@
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="36" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -11248,7 +11257,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J9" s="88"/>
+      <c r="J9" s="70"/>
       <c r="K9" s="6" t="s">
         <v>15</v>
       </c>
@@ -11261,7 +11270,7 @@
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="55">
         <v>3.1</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -11270,7 +11279,7 @@
       <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="36" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -11287,7 +11296,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J10" s="88"/>
+      <c r="J10" s="70"/>
       <c r="K10" s="6" t="s">
         <v>15</v>
       </c>
@@ -11300,7 +11309,7 @@
       <c r="A11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="70">
+      <c r="B11" s="55">
         <v>3.1</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -11309,7 +11318,7 @@
       <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="36" t="s">
         <v>37</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -11326,7 +11335,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J11" s="88"/>
+      <c r="J11" s="70"/>
       <c r="K11" s="6" t="s">
         <v>15</v>
       </c>
@@ -11339,14 +11348,14 @@
       <c r="A12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="71">
+      <c r="B12" s="56">
         <v>3.2</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="37" t="s">
         <v>125</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -11363,7 +11372,10 @@
         <f>H12</f>
         <v>1</v>
       </c>
-      <c r="J12" s="24"/>
+      <c r="J12" s="71">
+        <f>SUM(I12:I16)</f>
+        <v>5</v>
+      </c>
       <c r="K12" s="7" t="s">
         <v>15</v>
       </c>
@@ -11376,14 +11388,14 @@
       <c r="A13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="71">
+      <c r="B13" s="56">
         <v>3.2</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="37" t="s">
         <v>112</v>
       </c>
       <c r="F13" s="7" t="s">
@@ -11400,7 +11412,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J13" s="33"/>
+      <c r="J13" s="72"/>
       <c r="K13" s="7" t="s">
         <v>15</v>
       </c>
@@ -11413,7 +11425,7 @@
       <c r="A14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="72">
+      <c r="B14" s="57">
         <v>3.2</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -11422,7 +11434,7 @@
       <c r="D14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E14" s="38" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="8" t="s">
@@ -11439,7 +11451,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="72"/>
       <c r="K14" s="8" t="s">
         <v>15</v>
       </c>
@@ -11452,7 +11464,7 @@
       <c r="A15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="72">
+      <c r="B15" s="57">
         <v>3.2</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -11461,7 +11473,7 @@
       <c r="D15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="38" t="s">
         <v>113</v>
       </c>
       <c r="F15" s="8" t="s">
@@ -11478,7 +11490,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J15" s="24"/>
+      <c r="J15" s="72"/>
       <c r="K15" s="8" t="s">
         <v>15</v>
       </c>
@@ -11491,7 +11503,7 @@
       <c r="A16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="57">
         <v>3.2</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -11500,7 +11512,7 @@
       <c r="D16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" s="38" t="s">
         <v>41</v>
       </c>
       <c r="F16" s="8" t="s">
@@ -11517,7 +11529,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J16" s="31"/>
+      <c r="J16" s="73"/>
       <c r="K16" s="8" t="s">
         <v>15</v>
       </c>
@@ -11527,42 +11539,47 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="54" t="s">
+      <c r="E17" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="42" cm="1">
+      <c r="H17" s="29" cm="1">
         <f t="array" ref="H17">_xlfn.SWITCH(G17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="29">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J17" s="43"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
+      <c r="J17" s="76">
+        <f>SUM(I17:I19)</f>
+        <v>4</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
     </row>
     <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
-      <c r="B18" s="74"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="40" t="s">
         <v>51</v>
       </c>
       <c r="F18" s="17" t="s">
@@ -11579,7 +11596,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J18" s="32"/>
+      <c r="J18" s="76"/>
       <c r="K18" s="17" t="s">
         <v>15</v>
       </c>
@@ -11590,12 +11607,12 @@
     </row>
     <row r="19" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
-      <c r="B19" s="74"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="55" t="s">
+      <c r="E19" s="40" t="s">
         <v>52</v>
       </c>
       <c r="F19" s="17" t="s">
@@ -11612,7 +11629,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J19" s="32"/>
+      <c r="J19" s="76"/>
       <c r="K19" s="17" t="s">
         <v>15</v>
       </c>
@@ -11625,7 +11642,7 @@
       <c r="A20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="75">
+      <c r="B20" s="60">
         <v>3.3</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -11634,7 +11651,7 @@
       <c r="D20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="41" t="s">
         <v>116</v>
       </c>
       <c r="F20" s="10" t="s">
@@ -11651,7 +11668,10 @@
         <f>H20</f>
         <v>2</v>
       </c>
-      <c r="J20" s="27"/>
+      <c r="J20" s="78">
+        <f>SUM(I20:I25)</f>
+        <v>7</v>
+      </c>
       <c r="K20" s="10" t="s">
         <v>15</v>
       </c>
@@ -11664,7 +11684,7 @@
       <c r="A21" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="75">
+      <c r="B21" s="60">
         <v>3.3</v>
       </c>
       <c r="C21" s="10" t="s">
@@ -11673,7 +11693,7 @@
       <c r="D21" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="41" t="s">
         <v>115</v>
       </c>
       <c r="F21" s="10" t="s">
@@ -11690,7 +11710,7 @@
         <f>H21</f>
         <v>1</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="77"/>
       <c r="K21" s="10" t="s">
         <v>15</v>
       </c>
@@ -11703,7 +11723,7 @@
       <c r="A22" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="75">
+      <c r="B22" s="60">
         <v>3.4</v>
       </c>
       <c r="C22" s="10" t="s">
@@ -11712,7 +11732,7 @@
       <c r="D22" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="E22" s="41" t="s">
         <v>117</v>
       </c>
       <c r="F22" s="10" t="s">
@@ -11729,7 +11749,7 @@
         <f>H22</f>
         <v>1</v>
       </c>
-      <c r="J22" s="27"/>
+      <c r="J22" s="77"/>
       <c r="K22" s="10" t="s">
         <v>15</v>
       </c>
@@ -11742,7 +11762,7 @@
       <c r="A23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="75">
+      <c r="B23" s="60">
         <v>3.4</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -11751,7 +11771,7 @@
       <c r="D23" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="41" t="s">
         <v>114</v>
       </c>
       <c r="F23" s="10" t="s">
@@ -11768,7 +11788,7 @@
         <f>H23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="27"/>
+      <c r="J23" s="77"/>
       <c r="K23" s="10" t="s">
         <v>15</v>
       </c>
@@ -11781,7 +11801,7 @@
       <c r="A24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="76">
+      <c r="B24" s="61">
         <v>3.3</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -11790,7 +11810,7 @@
       <c r="D24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="42" t="s">
         <v>46</v>
       </c>
       <c r="F24" s="11" t="s">
@@ -11807,7 +11827,7 @@
         <f t="shared" ref="I24:I76" si="1">H24</f>
         <v>1</v>
       </c>
-      <c r="J24" s="25"/>
+      <c r="J24" s="77"/>
       <c r="K24" s="11" t="s">
         <v>15</v>
       </c>
@@ -11820,7 +11840,7 @@
       <c r="A25" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="76">
+      <c r="B25" s="61">
         <v>3.4</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -11829,7 +11849,7 @@
       <c r="D25" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="42" t="s">
         <v>47</v>
       </c>
       <c r="F25" s="11" t="s">
@@ -11846,7 +11866,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J25" s="25"/>
+      <c r="J25" s="79"/>
       <c r="K25" s="11" t="s">
         <v>15</v>
       </c>
@@ -11856,42 +11876,47 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="42"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="54" t="s">
+      <c r="E26" s="39" t="s">
         <v>82</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="42" t="s">
+      <c r="G26" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="H26" s="42" cm="1">
+      <c r="H26" s="29" cm="1">
         <f t="array" ref="H26">_xlfn.SWITCH(G26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I26" s="42">
+      <c r="I26" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
+      <c r="J26" s="75">
+        <f>SUM(I26:I28)</f>
+        <v>3</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
     </row>
     <row r="27" spans="1:13" s="9" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
-      <c r="B27" s="74"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="40" t="s">
         <v>49</v>
       </c>
       <c r="F27" s="17" t="s">
@@ -11908,7 +11933,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J27" s="17"/>
+      <c r="J27" s="74"/>
       <c r="K27" s="17" t="s">
         <v>15</v>
       </c>
@@ -11919,12 +11944,12 @@
     </row>
     <row r="28" spans="1:13" s="9" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
-      <c r="B28" s="74"/>
+      <c r="B28" s="59"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="55" t="s">
+      <c r="E28" s="40" t="s">
         <v>50</v>
       </c>
       <c r="F28" s="17" t="s">
@@ -11941,7 +11966,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J28" s="17"/>
+      <c r="J28" s="80"/>
       <c r="K28" s="17" t="s">
         <v>15</v>
       </c>
@@ -11954,7 +11979,7 @@
       <c r="A29" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="77">
+      <c r="B29" s="62">
         <v>3.6</v>
       </c>
       <c r="C29" s="12" t="s">
@@ -11963,25 +11988,30 @@
       <c r="D29" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="58" t="s">
+      <c r="E29" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="F29" s="40" t="s">
+      <c r="F29" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="41" cm="1">
+      <c r="H29" s="28" cm="1">
         <f t="array" ref="H29">_xlfn.SWITCH(G29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I29" s="41">
+      <c r="I29" s="28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J29" s="46"/>
-      <c r="K29" s="12"/>
+      <c r="J29" s="81">
+        <f>SUM(I29:I39)</f>
+        <v>11</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
     </row>
@@ -11989,7 +12019,7 @@
       <c r="A30" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="77">
+      <c r="B30" s="62">
         <v>3.5</v>
       </c>
       <c r="C30" s="12" t="s">
@@ -11998,7 +12028,7 @@
       <c r="D30" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="58" t="s">
+      <c r="E30" s="43" t="s">
         <v>119</v>
       </c>
       <c r="F30" s="12" t="s">
@@ -12015,7 +12045,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J30" s="46"/>
+      <c r="J30" s="82"/>
       <c r="K30" s="12" t="s">
         <v>15</v>
       </c>
@@ -12028,7 +12058,7 @@
       <c r="A31" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="77">
+      <c r="B31" s="62">
         <v>3.5</v>
       </c>
       <c r="C31" s="12" t="s">
@@ -12037,7 +12067,7 @@
       <c r="D31" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="58" t="s">
+      <c r="E31" s="43" t="s">
         <v>123</v>
       </c>
       <c r="F31" s="12"/>
@@ -12052,7 +12082,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J31" s="46"/>
+      <c r="J31" s="82"/>
       <c r="K31" s="12" t="s">
         <v>15</v>
       </c>
@@ -12065,7 +12095,7 @@
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="77">
+      <c r="B32" s="62">
         <v>3.6</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -12074,7 +12104,7 @@
       <c r="D32" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="58" t="s">
+      <c r="E32" s="43" t="s">
         <v>122</v>
       </c>
       <c r="F32" s="12"/>
@@ -12089,7 +12119,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J32" s="46"/>
+      <c r="J32" s="82"/>
       <c r="K32" s="12" t="s">
         <v>15</v>
       </c>
@@ -12102,7 +12132,7 @@
       <c r="A33" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="77">
+      <c r="B33" s="62">
         <v>3.7</v>
       </c>
       <c r="C33" s="12" t="s">
@@ -12111,7 +12141,7 @@
       <c r="D33" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="58" t="s">
+      <c r="E33" s="43" t="s">
         <v>121</v>
       </c>
       <c r="F33" s="12"/>
@@ -12126,7 +12156,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J33" s="46"/>
+      <c r="J33" s="82"/>
       <c r="K33" s="12" t="s">
         <v>15</v>
       </c>
@@ -12139,7 +12169,7 @@
       <c r="A34" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="77">
+      <c r="B34" s="62">
         <v>3.8</v>
       </c>
       <c r="C34" s="12" t="s">
@@ -12148,10 +12178,10 @@
       <c r="D34" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="F34" s="41"/>
+      <c r="F34" s="28"/>
       <c r="G34" s="12" t="s">
         <v>25</v>
       </c>
@@ -12163,8 +12193,10 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J34" s="46"/>
-      <c r="K34" s="12"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="L34" s="12"/>
       <c r="M34" s="12"/>
     </row>
@@ -12172,7 +12204,7 @@
       <c r="A35" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="78">
+      <c r="B35" s="63">
         <v>3.5</v>
       </c>
       <c r="C35" s="13" t="s">
@@ -12181,7 +12213,7 @@
       <c r="D35" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="59" t="s">
+      <c r="E35" s="44" t="s">
         <v>83</v>
       </c>
       <c r="F35" s="13" t="s">
@@ -12198,7 +12230,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J35" s="46"/>
+      <c r="J35" s="82"/>
       <c r="K35" s="13" t="s">
         <v>15</v>
       </c>
@@ -12211,7 +12243,7 @@
       <c r="A36" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="78">
+      <c r="B36" s="63">
         <v>3.5</v>
       </c>
       <c r="C36" s="13" t="s">
@@ -12220,7 +12252,7 @@
       <c r="D36" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="59" t="s">
+      <c r="E36" s="44" t="s">
         <v>85</v>
       </c>
       <c r="F36" s="13"/>
@@ -12235,7 +12267,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J36" s="46"/>
+      <c r="J36" s="82"/>
       <c r="K36" s="13" t="s">
         <v>15</v>
       </c>
@@ -12248,7 +12280,7 @@
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="78">
+      <c r="B37" s="63">
         <v>3.6</v>
       </c>
       <c r="C37" s="13" t="s">
@@ -12257,7 +12289,7 @@
       <c r="D37" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="59" t="s">
+      <c r="E37" s="44" t="s">
         <v>53</v>
       </c>
       <c r="F37" s="13"/>
@@ -12272,7 +12304,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J37" s="46"/>
+      <c r="J37" s="82"/>
       <c r="K37" s="13" t="s">
         <v>15</v>
       </c>
@@ -12285,7 +12317,7 @@
       <c r="A38" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="78">
+      <c r="B38" s="63">
         <v>3.7</v>
       </c>
       <c r="C38" s="13" t="s">
@@ -12294,7 +12326,7 @@
       <c r="D38" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E38" s="60" t="s">
+      <c r="E38" s="45" t="s">
         <v>54</v>
       </c>
       <c r="F38" s="13"/>
@@ -12309,7 +12341,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J38" s="46"/>
+      <c r="J38" s="82"/>
       <c r="K38" s="13" t="s">
         <v>15</v>
       </c>
@@ -12320,7 +12352,7 @@
     </row>
     <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
-      <c r="B39" s="78">
+      <c r="B39" s="63">
         <v>3.8</v>
       </c>
       <c r="C39" s="13" t="s">
@@ -12329,22 +12361,22 @@
       <c r="D39" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E39" s="60" t="s">
+      <c r="E39" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="F39" s="30"/>
+      <c r="F39" s="25"/>
       <c r="G39" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="30" cm="1">
+      <c r="H39" s="25" cm="1">
         <f t="array" ref="H39">_xlfn.SWITCH(G39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="25">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J39" s="28"/>
+      <c r="J39" s="83"/>
       <c r="K39" s="13" t="s">
         <v>15</v>
       </c>
@@ -12354,42 +12386,47 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="42"/>
-      <c r="B40" s="73"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42" t="s">
+      <c r="A40" s="29"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="61" t="s">
+      <c r="E40" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44" t="s">
+      <c r="F40" s="30"/>
+      <c r="G40" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="H40" s="44" cm="1">
+      <c r="H40" s="30" cm="1">
         <f t="array" ref="H40">_xlfn.SWITCH(G40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J40" s="44"/>
-      <c r="K40" s="42"/>
-      <c r="L40" s="42"/>
-      <c r="M40" s="42"/>
+      <c r="J40" s="75">
+        <f>SUM(I40:I42)</f>
+        <v>5</v>
+      </c>
+      <c r="K40" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
     </row>
     <row r="41" spans="1:13" s="9" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="74"/>
+      <c r="B41" s="59"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="47" t="s">
         <v>77</v>
       </c>
       <c r="F41" s="17" t="s">
@@ -12406,7 +12443,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J41" s="17"/>
+      <c r="J41" s="74"/>
       <c r="K41" s="17" t="s">
         <v>15</v>
       </c>
@@ -12419,12 +12456,12 @@
       <c r="A42" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="74"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="17"/>
       <c r="D42" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="62" t="s">
+      <c r="E42" s="47" t="s">
         <v>55</v>
       </c>
       <c r="F42" s="17" t="s">
@@ -12441,7 +12478,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J42" s="17"/>
+      <c r="J42" s="80"/>
       <c r="K42" s="17" t="s">
         <v>15</v>
       </c>
@@ -12454,7 +12491,7 @@
       <c r="A43" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="79">
+      <c r="B43" s="64">
         <v>3.9</v>
       </c>
       <c r="C43" s="15" t="s">
@@ -12463,22 +12500,25 @@
       <c r="D43" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="47" t="s">
+      <c r="E43" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29" t="s">
+      <c r="F43" s="24"/>
+      <c r="G43" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H43" s="29" cm="1">
+      <c r="H43" s="24" cm="1">
         <f t="array" ref="H43">_xlfn.SWITCH(G43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I43" s="29">
+      <c r="I43" s="24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J43" s="35"/>
+      <c r="J43" s="84">
+        <f>SUM(I43:I50)</f>
+        <v>14</v>
+      </c>
       <c r="K43" s="15" t="s">
         <v>15</v>
       </c>
@@ -12491,7 +12531,7 @@
       <c r="A44" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="79">
+      <c r="B44" s="64">
         <v>3.9</v>
       </c>
       <c r="C44" s="15" t="s">
@@ -12500,7 +12540,7 @@
       <c r="D44" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E44" s="47" t="s">
+      <c r="E44" s="32" t="s">
         <v>132</v>
       </c>
       <c r="F44" s="15" t="s">
@@ -12517,9 +12557,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J44" s="87">
-        <v>11</v>
-      </c>
+      <c r="J44" s="85"/>
       <c r="K44" s="15" t="s">
         <v>15</v>
       </c>
@@ -12532,7 +12570,7 @@
       <c r="A45" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B45" s="79">
+      <c r="B45" s="64">
         <v>3.9</v>
       </c>
       <c r="C45" s="15" t="s">
@@ -12541,7 +12579,7 @@
       <c r="D45" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E45" s="47" t="s">
+      <c r="E45" s="32" t="s">
         <v>128</v>
       </c>
       <c r="F45" s="15"/>
@@ -12556,7 +12594,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J45" s="87"/>
+      <c r="J45" s="85"/>
       <c r="K45" s="15" t="s">
         <v>15</v>
       </c>
@@ -12569,7 +12607,7 @@
       <c r="A46" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B46" s="79">
+      <c r="B46" s="64">
         <v>3.9</v>
       </c>
       <c r="C46" s="15" t="s">
@@ -12578,7 +12616,7 @@
       <c r="D46" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E46" s="47" t="s">
+      <c r="E46" s="32" t="s">
         <v>124</v>
       </c>
       <c r="F46" s="15"/>
@@ -12593,7 +12631,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J46" s="87"/>
+      <c r="J46" s="85"/>
       <c r="K46" s="15" t="s">
         <v>15</v>
       </c>
@@ -12606,7 +12644,7 @@
       <c r="A47" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B47" s="80">
+      <c r="B47" s="65">
         <v>3.9</v>
       </c>
       <c r="C47" s="14" t="s">
@@ -12615,25 +12653,27 @@
       <c r="D47" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E47" s="48" t="s">
+      <c r="E47" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="86" t="s">
+      <c r="F47" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="86" t="s">
+      <c r="G47" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="H47" s="86" cm="1">
+      <c r="H47" s="69" cm="1">
         <f t="array" ref="H47">_xlfn.SWITCH(G47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="I47" s="86">
+      <c r="I47" s="69">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J47" s="35"/>
-      <c r="K47" s="15"/>
+      <c r="J47" s="85"/>
+      <c r="K47" s="15" t="s">
+        <v>15</v>
+      </c>
       <c r="L47" s="15"/>
       <c r="M47" s="15"/>
     </row>
@@ -12641,7 +12681,7 @@
       <c r="A48" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="80">
+      <c r="B48" s="65">
         <v>3.9</v>
       </c>
       <c r="C48" s="14" t="s">
@@ -12650,7 +12690,7 @@
       <c r="D48" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E48" s="48" t="s">
+      <c r="E48" s="33" t="s">
         <v>88</v>
       </c>
       <c r="F48" s="14" t="s">
@@ -12667,7 +12707,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J48" s="35"/>
+      <c r="J48" s="85"/>
       <c r="K48" s="14" t="s">
         <v>15</v>
       </c>
@@ -12680,7 +12720,7 @@
       <c r="A49" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="80">
+      <c r="B49" s="65">
         <v>3.9</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -12689,7 +12729,7 @@
       <c r="D49" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E49" s="48" t="s">
+      <c r="E49" s="33" t="s">
         <v>60</v>
       </c>
       <c r="F49" s="14" t="s">
@@ -12706,7 +12746,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J49" s="36"/>
+      <c r="J49" s="85"/>
       <c r="K49" s="14" t="s">
         <v>15</v>
       </c>
@@ -12719,7 +12759,7 @@
       <c r="A50" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B50" s="80">
+      <c r="B50" s="65">
         <v>3.9</v>
       </c>
       <c r="C50" s="14" t="s">
@@ -12728,7 +12768,7 @@
       <c r="D50" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="33" t="s">
         <v>61</v>
       </c>
       <c r="F50" s="14" t="s">
@@ -12745,7 +12785,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J50" s="29"/>
+      <c r="J50" s="85"/>
       <c r="K50" s="14" t="s">
         <v>15</v>
       </c>
@@ -12755,40 +12795,45 @@
       </c>
     </row>
     <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="42"/>
-      <c r="B51" s="73"/>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42" t="s">
+      <c r="A51" s="29"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E51" s="61" t="s">
+      <c r="E51" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42" t="s">
+      <c r="F51" s="29"/>
+      <c r="G51" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="H51" s="42" cm="1">
+      <c r="H51" s="29" cm="1">
         <f t="array" ref="H51">_xlfn.SWITCH(G51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I51" s="42">
+      <c r="I51" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J51" s="43"/>
-      <c r="K51" s="42"/>
-      <c r="L51" s="42"/>
-      <c r="M51" s="42"/>
+      <c r="J51" s="76">
+        <f>SUM(I51:I53)</f>
+        <v>5</v>
+      </c>
+      <c r="K51" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
     </row>
     <row r="52" spans="1:13" s="9" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
-      <c r="B52" s="74"/>
+      <c r="B52" s="59"/>
       <c r="C52" s="17"/>
       <c r="D52" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E52" s="55" t="s">
+      <c r="E52" s="40" t="s">
         <v>62</v>
       </c>
       <c r="F52" s="17" t="s">
@@ -12805,7 +12850,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J52" s="32"/>
+      <c r="J52" s="76"/>
       <c r="K52" s="17" t="s">
         <v>15</v>
       </c>
@@ -12816,12 +12861,12 @@
     </row>
     <row r="53" spans="1:13" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
-      <c r="B53" s="74"/>
+      <c r="B53" s="59"/>
       <c r="C53" s="17"/>
       <c r="D53" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E53" s="55" t="s">
+      <c r="E53" s="40" t="s">
         <v>63</v>
       </c>
       <c r="F53" s="17" t="s">
@@ -12838,7 +12883,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J53" s="32"/>
+      <c r="J53" s="76"/>
       <c r="K53" s="17" t="s">
         <v>15</v>
       </c>
@@ -12851,7 +12896,7 @@
       <c r="A54" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B54" s="81" t="s">
+      <c r="B54" s="66" t="s">
         <v>64</v>
       </c>
       <c r="C54" s="16" t="s">
@@ -12860,7 +12905,7 @@
       <c r="D54" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E54" s="63" t="s">
+      <c r="E54" s="48" t="s">
         <v>131</v>
       </c>
       <c r="F54" s="16" t="s">
@@ -12877,7 +12922,10 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J54" s="39"/>
+      <c r="J54" s="86">
+        <f>SUM(I54:I65)</f>
+        <v>21</v>
+      </c>
       <c r="K54" s="16" t="s">
         <v>15</v>
       </c>
@@ -12890,7 +12938,7 @@
       <c r="A55" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="81" t="s">
+      <c r="B55" s="66" t="s">
         <v>64</v>
       </c>
       <c r="C55" s="16" t="s">
@@ -12899,7 +12947,7 @@
       <c r="D55" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E55" s="63" t="s">
+      <c r="E55" s="48" t="s">
         <v>130</v>
       </c>
       <c r="F55" s="16"/>
@@ -12914,8 +12962,10 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J55" s="39"/>
-      <c r="K55" s="16"/>
+      <c r="J55" s="87"/>
+      <c r="K55" s="16" t="s">
+        <v>15</v>
+      </c>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
     </row>
@@ -12923,7 +12973,7 @@
       <c r="A56" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="81" t="s">
+      <c r="B56" s="66" t="s">
         <v>64</v>
       </c>
       <c r="C56" s="16" t="s">
@@ -12932,7 +12982,7 @@
       <c r="D56" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="63" t="s">
+      <c r="E56" s="48" t="s">
         <v>129</v>
       </c>
       <c r="F56" s="16"/>
@@ -12947,8 +12997,10 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J56" s="39"/>
-      <c r="K56" s="16"/>
+      <c r="J56" s="87"/>
+      <c r="K56" s="16" t="s">
+        <v>15</v>
+      </c>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
     </row>
@@ -12956,7 +13008,7 @@
       <c r="A57" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="81" t="s">
+      <c r="B57" s="66" t="s">
         <v>64</v>
       </c>
       <c r="C57" s="16" t="s">
@@ -12965,7 +13017,7 @@
       <c r="D57" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="E57" s="63" t="s">
+      <c r="E57" s="48" t="s">
         <v>134</v>
       </c>
       <c r="F57" s="16" t="s">
@@ -12982,9 +13034,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J57" s="38">
-        <v>27</v>
-      </c>
+      <c r="J57" s="87"/>
       <c r="K57" s="16" t="s">
         <v>15</v>
       </c>
@@ -12997,7 +13047,7 @@
       <c r="A58" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B58" s="37" t="s">
+      <c r="B58" s="26" t="s">
         <v>64</v>
       </c>
       <c r="C58" s="18" t="s">
@@ -13006,7 +13056,7 @@
       <c r="D58" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E58" s="64" t="s">
+      <c r="E58" s="49" t="s">
         <v>87</v>
       </c>
       <c r="F58" s="18" t="s">
@@ -13023,7 +13073,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J58" s="39"/>
+      <c r="J58" s="87"/>
       <c r="K58" s="18" t="s">
         <v>15</v>
       </c>
@@ -13036,7 +13086,7 @@
       <c r="A59" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B59" s="37" t="s">
+      <c r="B59" s="26" t="s">
         <v>64</v>
       </c>
       <c r="C59" s="18" t="s">
@@ -13045,7 +13095,7 @@
       <c r="D59" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E59" s="64" t="s">
+      <c r="E59" s="49" t="s">
         <v>100</v>
       </c>
       <c r="F59" s="18" t="s">
@@ -13062,7 +13112,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J59" s="39"/>
+      <c r="J59" s="87"/>
       <c r="K59" s="18" t="s">
         <v>15</v>
       </c>
@@ -13075,7 +13125,7 @@
       <c r="A60" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B60" s="37" t="s">
+      <c r="B60" s="26" t="s">
         <v>64</v>
       </c>
       <c r="C60" s="18" t="s">
@@ -13084,7 +13134,7 @@
       <c r="D60" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E60" s="64" t="s">
+      <c r="E60" s="49" t="s">
         <v>101</v>
       </c>
       <c r="F60" s="18" t="s">
@@ -13101,7 +13151,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J60" s="39"/>
+      <c r="J60" s="87"/>
       <c r="K60" s="18" t="s">
         <v>15</v>
       </c>
@@ -13114,7 +13164,7 @@
       <c r="A61" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B61" s="37" t="s">
+      <c r="B61" s="26" t="s">
         <v>64</v>
       </c>
       <c r="C61" s="18" t="s">
@@ -13123,7 +13173,7 @@
       <c r="D61" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E61" s="64" t="s">
+      <c r="E61" s="49" t="s">
         <v>133</v>
       </c>
       <c r="F61" s="18" t="s">
@@ -13140,7 +13190,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J61" s="39"/>
+      <c r="J61" s="87"/>
       <c r="K61" s="18" t="s">
         <v>15</v>
       </c>
@@ -13153,7 +13203,7 @@
       <c r="A62" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B62" s="37">
+      <c r="B62" s="26">
         <v>3.11</v>
       </c>
       <c r="C62" s="18" t="s">
@@ -13162,7 +13212,7 @@
       <c r="D62" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E62" s="64" t="s">
+      <c r="E62" s="49" t="s">
         <v>89</v>
       </c>
       <c r="F62" s="18" t="s">
@@ -13179,7 +13229,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J62" s="39"/>
+      <c r="J62" s="87"/>
       <c r="K62" s="18" t="s">
         <v>15</v>
       </c>
@@ -13192,7 +13242,7 @@
       <c r="A63" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B63" s="37">
+      <c r="B63" s="26">
         <v>3.11</v>
       </c>
       <c r="C63" s="18" t="s">
@@ -13201,7 +13251,7 @@
       <c r="D63" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E63" s="64" t="s">
+      <c r="E63" s="49" t="s">
         <v>72</v>
       </c>
       <c r="F63" s="18" t="s">
@@ -13218,7 +13268,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J63" s="39"/>
+      <c r="J63" s="87"/>
       <c r="K63" s="18" t="s">
         <v>15</v>
       </c>
@@ -13231,7 +13281,7 @@
       <c r="A64" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B64" s="37">
+      <c r="B64" s="26">
         <v>3.11</v>
       </c>
       <c r="C64" s="18" t="s">
@@ -13240,7 +13290,7 @@
       <c r="D64" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E64" s="64" t="s">
+      <c r="E64" s="49" t="s">
         <v>103</v>
       </c>
       <c r="F64" s="18" t="s">
@@ -13257,7 +13307,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J64" s="39"/>
+      <c r="J64" s="87"/>
       <c r="K64" s="18" t="s">
         <v>15</v>
       </c>
@@ -13270,7 +13320,7 @@
       <c r="A65" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B65" s="37">
+      <c r="B65" s="26">
         <v>3.11</v>
       </c>
       <c r="C65" s="18" t="s">
@@ -13279,7 +13329,7 @@
       <c r="D65" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E65" s="64" t="s">
+      <c r="E65" s="49" t="s">
         <v>65</v>
       </c>
       <c r="F65" s="18" t="s">
@@ -13296,7 +13346,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J65" s="39"/>
+      <c r="J65" s="87"/>
       <c r="K65" s="18" t="s">
         <v>15</v>
       </c>
@@ -13309,12 +13359,12 @@
       <c r="A66" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B66" s="74"/>
+      <c r="B66" s="59"/>
       <c r="C66" s="17"/>
       <c r="D66" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E66" s="55" t="s">
+      <c r="E66" s="40" t="s">
         <v>76</v>
       </c>
       <c r="F66" s="17" t="s">
@@ -13331,7 +13381,10 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J66" s="32"/>
+      <c r="J66" s="88">
+        <f>SUM(I66:I68)</f>
+        <v>3</v>
+      </c>
       <c r="K66" s="17" t="s">
         <v>15</v>
       </c>
@@ -13344,12 +13397,12 @@
       <c r="A67" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B67" s="74"/>
+      <c r="B67" s="59"/>
       <c r="C67" s="17"/>
       <c r="D67" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E67" s="55" t="s">
+      <c r="E67" s="40" t="s">
         <v>75</v>
       </c>
       <c r="F67" s="17" t="s">
@@ -13366,7 +13419,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J67" s="32"/>
+      <c r="J67" s="88"/>
       <c r="K67" s="17" t="s">
         <v>15</v>
       </c>
@@ -13379,12 +13432,12 @@
       <c r="A68" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B68" s="74"/>
+      <c r="B68" s="59"/>
       <c r="C68" s="17"/>
       <c r="D68" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E68" s="55" t="s">
+      <c r="E68" s="40" t="s">
         <v>78</v>
       </c>
       <c r="F68" s="17" t="s">
@@ -13401,7 +13454,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J68" s="32"/>
+      <c r="J68" s="89"/>
       <c r="K68" s="17" t="s">
         <v>15</v>
       </c>
@@ -13414,7 +13467,7 @@
       <c r="A69" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="82" t="s">
+      <c r="B69" s="67" t="s">
         <v>138</v>
       </c>
       <c r="C69" s="20" t="s">
@@ -13423,7 +13476,7 @@
       <c r="D69" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E69" s="65" t="s">
+      <c r="E69" s="50" t="s">
         <v>136</v>
       </c>
       <c r="F69" s="20" t="s">
@@ -13440,8 +13493,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J69" s="84">
-        <v>27</v>
+      <c r="J69" s="90">
+        <f>SUM(I69:I74)</f>
+        <v>17</v>
       </c>
       <c r="K69" s="20" t="s">
         <v>15</v>
@@ -13453,7 +13507,7 @@
     </row>
     <row r="70" spans="1:13" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20"/>
-      <c r="B70" s="82" t="s">
+      <c r="B70" s="67" t="s">
         <v>138</v>
       </c>
       <c r="C70" s="20" t="s">
@@ -13462,7 +13516,7 @@
       <c r="D70" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E70" s="65" t="s">
+      <c r="E70" s="50" t="s">
         <v>137</v>
       </c>
       <c r="F70" s="20"/>
@@ -13477,14 +13531,16 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J70" s="85"/>
-      <c r="K70" s="20"/>
+      <c r="J70" s="91"/>
+      <c r="K70" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="L70" s="20"/>
       <c r="M70" s="20"/>
     </row>
     <row r="71" spans="1:13" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20"/>
-      <c r="B71" s="82" t="s">
+      <c r="B71" s="67" t="s">
         <v>139</v>
       </c>
       <c r="C71" s="20" t="s">
@@ -13493,7 +13549,7 @@
       <c r="D71" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E71" s="65" t="s">
+      <c r="E71" s="50" t="s">
         <v>140</v>
       </c>
       <c r="F71" s="20"/>
@@ -13508,8 +13564,10 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J71" s="85"/>
-      <c r="K71" s="20"/>
+      <c r="J71" s="91"/>
+      <c r="K71" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="L71" s="20"/>
       <c r="M71" s="20"/>
     </row>
@@ -13517,7 +13575,7 @@
       <c r="A72" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B72" s="83">
+      <c r="B72" s="68">
         <v>3.12</v>
       </c>
       <c r="C72" s="19" t="s">
@@ -13526,7 +13584,7 @@
       <c r="D72" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E72" s="66" t="s">
+      <c r="E72" s="51" t="s">
         <v>74</v>
       </c>
       <c r="F72" s="19" t="s">
@@ -13543,7 +13601,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J72" s="85"/>
+      <c r="J72" s="91"/>
       <c r="K72" s="19" t="s">
         <v>15</v>
       </c>
@@ -13556,7 +13614,7 @@
       <c r="A73" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B73" s="83">
+      <c r="B73" s="68">
         <v>3.12</v>
       </c>
       <c r="C73" s="19" t="s">
@@ -13565,7 +13623,7 @@
       <c r="D73" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E73" s="66" t="s">
+      <c r="E73" s="51" t="s">
         <v>104</v>
       </c>
       <c r="F73" s="19" t="s">
@@ -13582,7 +13640,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J73" s="85"/>
+      <c r="J73" s="91"/>
       <c r="K73" s="19" t="s">
         <v>15</v>
       </c>
@@ -13595,7 +13653,7 @@
       <c r="A74" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B74" s="83">
+      <c r="B74" s="68">
         <v>3.13</v>
       </c>
       <c r="C74" s="19" t="s">
@@ -13604,7 +13662,7 @@
       <c r="D74" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E74" s="66" t="s">
+      <c r="E74" s="51" t="s">
         <v>102</v>
       </c>
       <c r="F74" s="19" t="s">
@@ -13621,7 +13679,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="J74" s="85"/>
+      <c r="J74" s="91"/>
       <c r="K74" s="19" t="s">
         <v>15</v>
       </c>
@@ -13631,46 +13689,51 @@
       </c>
     </row>
     <row r="75" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="42" t="s">
+      <c r="A75" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B75" s="73"/>
-      <c r="C75" s="42"/>
-      <c r="D75" s="42" t="s">
+      <c r="B75" s="58"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E75" s="54" t="s">
+      <c r="E75" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="F75" s="42" t="s">
+      <c r="F75" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="G75" s="42" t="s">
+      <c r="G75" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="H75" s="42" cm="1">
+      <c r="H75" s="29" cm="1">
         <f t="array" ref="H75">_xlfn.SWITCH(G75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="I75" s="42">
+      <c r="I75" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J75" s="43"/>
-      <c r="K75" s="42"/>
-      <c r="L75" s="42"/>
-      <c r="M75" s="42"/>
+      <c r="J75" s="74">
+        <f>SUM(I75:I76)</f>
+        <v>2</v>
+      </c>
+      <c r="K75" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L75" s="29"/>
+      <c r="M75" s="29"/>
     </row>
     <row r="76" spans="1:13" s="9" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A76" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B76" s="74"/>
+      <c r="B76" s="59"/>
       <c r="C76" s="17"/>
       <c r="D76" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E76" s="55" t="s">
+      <c r="E76" s="40" t="s">
         <v>105</v>
       </c>
       <c r="F76" s="17" t="s">
@@ -13687,7 +13750,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J76" s="17"/>
+      <c r="J76" s="80"/>
       <c r="K76" s="17" t="s">
         <v>15</v>
       </c>
@@ -13697,8 +13760,20 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="13">
+    <mergeCell ref="J66:J68"/>
+    <mergeCell ref="J69:J74"/>
+    <mergeCell ref="J75:J76"/>
+    <mergeCell ref="J29:J39"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="J43:J50"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="J54:J65"/>
     <mergeCell ref="J2:J11"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="J20:J25"/>
+    <mergeCell ref="J26:J28"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13947,7 +14022,7 @@
   <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="33" style="1" customWidth="1"/>
@@ -13962,7 +14037,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">

--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D98EAF-D7B4-47CE-BE0B-0D55A792638C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FAFF00-EE16-4E41-A5AB-8F754482FCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
@@ -1886,192 +1886,6 @@
   </si>
   <si>
     <r>
-      <t>Create</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> GET /api/bikes/search</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Endpoint
-1. Input (Query Params): </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>startDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>endDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>minPrice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>maxPrice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>category</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (e-bike type), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (lat/long or cityId).
-2. Logic:
-- Filter bikes by availability (exclude bikes booked during startDate to endDate).
-- Filter by price range and category.
-- Sorting: Implement strict SQL sorting: ORDER BY price ASC.
-3. Output: List of Bike objects (thumbnail, name, price, rating).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GET /api/bikes/{id} Endpoint</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Logic: Fetch full details for a specific bike.
-2. Output: Detailed JSON including specifications, full image URLs, and nested owner summary object.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Render e-bikes filtered by the date entered in list of clickable cards with E-bike </t>
     </r>
     <r>
@@ -9033,6 +8847,343 @@
 3. Verify "Rate Your Experience" section renders
 4. Verify Leave a Comment section renders
 - Verify a textField that can take 500 characters max renders</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /api/bikes/search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Input (Query Params): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>startDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>endDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>minPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>maxPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e-bike type), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (lat/long or cityId).
+2. Logic:
+- Filter bikes by availability (exclude bikes booked during startDate to endDate).
+- Filter by price range and category.
+- Sorting: Implement strict SQL sorting: ORDER BY price ASC (Ensure "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cheapest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" appears first).
+3. Output: List of Bike objects (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thumbnail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isVerified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /api/bikes/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+1. Logic: Fetch full details for a specific bike.
+2. Output: Detailed JSON including:
+- Specifications (range, speed, etc.)
+- Full image URLs
+- Verification Status (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isVerified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: boolean)
+- Nested owner summary object.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -9523,34 +9674,19 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9565,10 +9701,16 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9577,16 +9719,25 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9689,37 +9840,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>156</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>156</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>156</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>156</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>156</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>148</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>148</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>148</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>148</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>148</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>148</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9764,34 +9915,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>156</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>140.4</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>124.8</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>109.2</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>93.6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>78</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>62.400000000000006</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46.8</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>31.200000000000003</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.599999999999994</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -10962,10 +11113,10 @@
         <v>33</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>27</v>
@@ -10981,7 +11132,7 @@
         <f>H2</f>
         <v>1</v>
       </c>
-      <c r="J2" s="70">
+      <c r="J2" s="85">
         <f>SUM(I2:I11)</f>
         <v>18</v>
       </c>
@@ -11004,10 +11155,10 @@
         <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>27</v>
@@ -11023,7 +11174,7 @@
         <f>H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="70"/>
+      <c r="J3" s="85"/>
       <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
@@ -11043,10 +11194,10 @@
         <v>33</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>27</v>
@@ -11062,7 +11213,7 @@
         <f t="shared" ref="I4:I19" si="0">H4</f>
         <v>1</v>
       </c>
-      <c r="J4" s="70"/>
+      <c r="J4" s="85"/>
       <c r="K4" s="5" t="s">
         <v>15</v>
       </c>
@@ -11082,10 +11233,10 @@
         <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>27</v>
@@ -11101,7 +11252,7 @@
         <f>H5</f>
         <v>1</v>
       </c>
-      <c r="J5" s="70"/>
+      <c r="J5" s="85"/>
       <c r="K5" s="5" t="s">
         <v>15</v>
       </c>
@@ -11121,10 +11272,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>27</v>
@@ -11140,7 +11291,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J6" s="70"/>
+      <c r="J6" s="85"/>
       <c r="K6" s="5" t="s">
         <v>15</v>
       </c>
@@ -11179,7 +11330,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J7" s="70"/>
+      <c r="J7" s="85"/>
       <c r="K7" s="6" t="s">
         <v>15</v>
       </c>
@@ -11218,7 +11369,7 @@
         <f>H8</f>
         <v>2</v>
       </c>
-      <c r="J8" s="70"/>
+      <c r="J8" s="85"/>
       <c r="K8" s="6" t="s">
         <v>15</v>
       </c>
@@ -11257,7 +11408,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J9" s="70"/>
+      <c r="J9" s="85"/>
       <c r="K9" s="6" t="s">
         <v>15</v>
       </c>
@@ -11296,7 +11447,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J10" s="70"/>
+      <c r="J10" s="85"/>
       <c r="K10" s="6" t="s">
         <v>15</v>
       </c>
@@ -11335,7 +11486,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J11" s="70"/>
+      <c r="J11" s="85"/>
       <c r="K11" s="6" t="s">
         <v>15</v>
       </c>
@@ -11353,10 +11504,10 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
@@ -11372,7 +11523,7 @@
         <f>H12</f>
         <v>1</v>
       </c>
-      <c r="J12" s="71">
+      <c r="J12" s="86">
         <f>SUM(I12:I16)</f>
         <v>5</v>
       </c>
@@ -11393,10 +11544,10 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>27</v>
@@ -11412,7 +11563,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J13" s="72"/>
+      <c r="J13" s="87"/>
       <c r="K13" s="7" t="s">
         <v>15</v>
       </c>
@@ -11451,7 +11602,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J14" s="72"/>
+      <c r="J14" s="87"/>
       <c r="K14" s="8" t="s">
         <v>15</v>
       </c>
@@ -11474,7 +11625,7 @@
         <v>28</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
@@ -11490,7 +11641,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J15" s="72"/>
+      <c r="J15" s="87"/>
       <c r="K15" s="8" t="s">
         <v>15</v>
       </c>
@@ -11529,7 +11680,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J16" s="73"/>
+      <c r="J16" s="88"/>
       <c r="K16" s="8" t="s">
         <v>15</v>
       </c>
@@ -11543,10 +11694,10 @@
       <c r="B17" s="58"/>
       <c r="C17" s="29"/>
       <c r="D17" s="29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F17" s="29" t="s">
         <v>22</v>
@@ -11562,7 +11713,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J17" s="76">
+      <c r="J17" s="82">
         <f>SUM(I17:I19)</f>
         <v>4</v>
       </c>
@@ -11572,7 +11723,7 @@
       <c r="L17" s="29"/>
       <c r="M17" s="29"/>
     </row>
-    <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
       <c r="B18" s="59"/>
       <c r="C18" s="17"/>
@@ -11580,7 +11731,7 @@
         <v>48</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>22</v>
@@ -11596,7 +11747,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J18" s="76"/>
+      <c r="J18" s="82"/>
       <c r="K18" s="17" t="s">
         <v>15</v>
       </c>
@@ -11605,7 +11756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
       <c r="B19" s="59"/>
       <c r="C19" s="17"/>
@@ -11613,7 +11764,7 @@
         <v>48</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>22</v>
@@ -11629,7 +11780,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J19" s="76"/>
+      <c r="J19" s="82"/>
       <c r="K19" s="17" t="s">
         <v>15</v>
       </c>
@@ -11649,10 +11800,10 @@
         <v>42</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>27</v>
@@ -11668,7 +11819,7 @@
         <f>H20</f>
         <v>2</v>
       </c>
-      <c r="J20" s="78">
+      <c r="J20" s="89">
         <f>SUM(I20:I25)</f>
         <v>7</v>
       </c>
@@ -11691,10 +11842,10 @@
         <v>42</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>8</v>
@@ -11710,7 +11861,7 @@
         <f>H21</f>
         <v>1</v>
       </c>
-      <c r="J21" s="77"/>
+      <c r="J21" s="90"/>
       <c r="K21" s="10" t="s">
         <v>15</v>
       </c>
@@ -11730,10 +11881,10 @@
         <v>43</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>27</v>
@@ -11749,7 +11900,7 @@
         <f>H22</f>
         <v>1</v>
       </c>
-      <c r="J22" s="77"/>
+      <c r="J22" s="90"/>
       <c r="K22" s="10" t="s">
         <v>15</v>
       </c>
@@ -11769,10 +11920,10 @@
         <v>43</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>27</v>
@@ -11788,7 +11939,7 @@
         <f>H23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="77"/>
+      <c r="J23" s="90"/>
       <c r="K23" s="10" t="s">
         <v>15</v>
       </c>
@@ -11827,7 +11978,7 @@
         <f t="shared" ref="I24:I76" si="1">H24</f>
         <v>1</v>
       </c>
-      <c r="J24" s="77"/>
+      <c r="J24" s="90"/>
       <c r="K24" s="11" t="s">
         <v>15</v>
       </c>
@@ -11866,7 +12017,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J25" s="79"/>
+      <c r="J25" s="91"/>
       <c r="K25" s="11" t="s">
         <v>15</v>
       </c>
@@ -11880,10 +12031,10 @@
       <c r="B26" s="58"/>
       <c r="C26" s="29"/>
       <c r="D26" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="39" t="s">
         <v>80</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>82</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>22</v>
@@ -11899,7 +12050,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J26" s="75">
+      <c r="J26" s="79">
         <f>SUM(I26:I28)</f>
         <v>3</v>
       </c>
@@ -11966,7 +12117,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J28" s="80"/>
+      <c r="J28" s="75"/>
       <c r="K28" s="17" t="s">
         <v>15</v>
       </c>
@@ -11983,13 +12134,13 @@
         <v>3.6</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F29" s="27" t="s">
         <v>27</v>
@@ -12005,7 +12156,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J29" s="81">
+      <c r="J29" s="76">
         <f>SUM(I29:I39)</f>
         <v>11</v>
       </c>
@@ -12023,13 +12174,13 @@
         <v>3.5</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>27</v>
@@ -12045,7 +12196,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J30" s="82"/>
+      <c r="J30" s="77"/>
       <c r="K30" s="12" t="s">
         <v>15</v>
       </c>
@@ -12062,13 +12213,13 @@
         <v>3.5</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12" t="s">
@@ -12082,7 +12233,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J31" s="82"/>
+      <c r="J31" s="77"/>
       <c r="K31" s="12" t="s">
         <v>15</v>
       </c>
@@ -12099,13 +12250,13 @@
         <v>3.6</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12" t="s">
@@ -12119,7 +12270,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J32" s="82"/>
+      <c r="J32" s="77"/>
       <c r="K32" s="12" t="s">
         <v>15</v>
       </c>
@@ -12136,13 +12287,13 @@
         <v>3.7</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E33" s="43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12" t="s">
@@ -12156,7 +12307,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J33" s="82"/>
+      <c r="J33" s="77"/>
       <c r="K33" s="12" t="s">
         <v>15</v>
       </c>
@@ -12173,13 +12324,13 @@
         <v>3.8</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E34" s="43" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F34" s="28"/>
       <c r="G34" s="12" t="s">
@@ -12193,7 +12344,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J34" s="82"/>
+      <c r="J34" s="77"/>
       <c r="K34" s="12" t="s">
         <v>15</v>
       </c>
@@ -12208,13 +12359,13 @@
         <v>3.5</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>8</v>
@@ -12230,7 +12381,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J35" s="82"/>
+      <c r="J35" s="77"/>
       <c r="K35" s="13" t="s">
         <v>15</v>
       </c>
@@ -12247,13 +12398,13 @@
         <v>3.5</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13" t="s">
@@ -12267,7 +12418,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J36" s="82"/>
+      <c r="J36" s="77"/>
       <c r="K36" s="13" t="s">
         <v>15</v>
       </c>
@@ -12284,13 +12435,13 @@
         <v>3.6</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13" t="s">
@@ -12304,7 +12455,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J37" s="82"/>
+      <c r="J37" s="77"/>
       <c r="K37" s="13" t="s">
         <v>15</v>
       </c>
@@ -12321,13 +12472,13 @@
         <v>3.7</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="13" t="s">
@@ -12341,7 +12492,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J38" s="82"/>
+      <c r="J38" s="77"/>
       <c r="K38" s="13" t="s">
         <v>15</v>
       </c>
@@ -12356,13 +12507,13 @@
         <v>3.8</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F39" s="25"/>
       <c r="G39" s="13" t="s">
@@ -12376,7 +12527,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J39" s="83"/>
+      <c r="J39" s="78"/>
       <c r="K39" s="13" t="s">
         <v>15</v>
       </c>
@@ -12390,10 +12541,10 @@
       <c r="B40" s="58"/>
       <c r="C40" s="29"/>
       <c r="D40" s="29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E40" s="46" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F40" s="30"/>
       <c r="G40" s="30" t="s">
@@ -12407,7 +12558,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J40" s="75">
+      <c r="J40" s="79">
         <f>SUM(I40:I42)</f>
         <v>5</v>
       </c>
@@ -12427,7 +12578,7 @@
         <v>48</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>22</v>
@@ -12462,7 +12613,7 @@
         <v>48</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>22</v>
@@ -12478,7 +12629,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J42" s="80"/>
+      <c r="J42" s="75"/>
       <c r="K42" s="17" t="s">
         <v>15</v>
       </c>
@@ -12495,13 +12646,13 @@
         <v>3.9</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F43" s="24"/>
       <c r="G43" s="24" t="s">
@@ -12515,7 +12666,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J43" s="84">
+      <c r="J43" s="80">
         <f>SUM(I43:I50)</f>
         <v>14</v>
       </c>
@@ -12535,13 +12686,13 @@
         <v>3.9</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>27</v>
@@ -12557,7 +12708,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J44" s="85"/>
+      <c r="J44" s="81"/>
       <c r="K44" s="15" t="s">
         <v>15</v>
       </c>
@@ -12574,13 +12725,13 @@
         <v>3.9</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15" t="s">
@@ -12594,7 +12745,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J45" s="85"/>
+      <c r="J45" s="81"/>
       <c r="K45" s="15" t="s">
         <v>15</v>
       </c>
@@ -12611,13 +12762,13 @@
         <v>3.9</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15" t="s">
@@ -12631,7 +12782,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J46" s="85"/>
+      <c r="J46" s="81"/>
       <c r="K46" s="15" t="s">
         <v>15</v>
       </c>
@@ -12648,13 +12799,13 @@
         <v>3.9</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F47" s="69" t="s">
         <v>8</v>
@@ -12670,7 +12821,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J47" s="85"/>
+      <c r="J47" s="81"/>
       <c r="K47" s="15" t="s">
         <v>15</v>
       </c>
@@ -12685,13 +12836,13 @@
         <v>3.9</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>8</v>
@@ -12707,7 +12858,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J48" s="85"/>
+      <c r="J48" s="81"/>
       <c r="K48" s="14" t="s">
         <v>15</v>
       </c>
@@ -12724,13 +12875,13 @@
         <v>3.9</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>8</v>
@@ -12746,7 +12897,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J49" s="85"/>
+      <c r="J49" s="81"/>
       <c r="K49" s="14" t="s">
         <v>15</v>
       </c>
@@ -12763,13 +12914,13 @@
         <v>3.9</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>8</v>
@@ -12785,7 +12936,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J50" s="85"/>
+      <c r="J50" s="81"/>
       <c r="K50" s="14" t="s">
         <v>15</v>
       </c>
@@ -12799,10 +12950,10 @@
       <c r="B51" s="58"/>
       <c r="C51" s="29"/>
       <c r="D51" s="29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F51" s="29"/>
       <c r="G51" s="29" t="s">
@@ -12816,7 +12967,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J51" s="76">
+      <c r="J51" s="82">
         <f>SUM(I51:I53)</f>
         <v>5</v>
       </c>
@@ -12834,7 +12985,7 @@
         <v>48</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>22</v>
@@ -12850,7 +13001,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J52" s="76"/>
+      <c r="J52" s="82"/>
       <c r="K52" s="17" t="s">
         <v>15</v>
       </c>
@@ -12867,7 +13018,7 @@
         <v>48</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>22</v>
@@ -12883,7 +13034,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J53" s="76"/>
+      <c r="J53" s="82"/>
       <c r="K53" s="17" t="s">
         <v>15</v>
       </c>
@@ -12897,16 +13048,16 @@
         <v>35</v>
       </c>
       <c r="B54" s="66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>27</v>
@@ -12922,7 +13073,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J54" s="86">
+      <c r="J54" s="83">
         <f>SUM(I54:I65)</f>
         <v>21</v>
       </c>
@@ -12939,16 +13090,16 @@
         <v>35</v>
       </c>
       <c r="B55" s="66" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="16" t="s">
-        <v>66</v>
-      </c>
       <c r="D55" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F55" s="16"/>
       <c r="G55" s="16" t="s">
@@ -12962,7 +13113,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J55" s="87"/>
+      <c r="J55" s="84"/>
       <c r="K55" s="16" t="s">
         <v>15</v>
       </c>
@@ -12974,16 +13125,16 @@
         <v>35</v>
       </c>
       <c r="B56" s="66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E56" s="48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F56" s="16"/>
       <c r="G56" s="16" t="s">
@@ -12997,7 +13148,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J56" s="87"/>
+      <c r="J56" s="84"/>
       <c r="K56" s="16" t="s">
         <v>15</v>
       </c>
@@ -13009,16 +13160,16 @@
         <v>35</v>
       </c>
       <c r="B57" s="66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E57" s="48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F57" s="16" t="s">
         <v>27</v>
@@ -13034,7 +13185,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J57" s="87"/>
+      <c r="J57" s="84"/>
       <c r="K57" s="16" t="s">
         <v>15</v>
       </c>
@@ -13048,16 +13199,16 @@
         <v>35</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="49" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>8</v>
@@ -13073,7 +13224,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J58" s="87"/>
+      <c r="J58" s="84"/>
       <c r="K58" s="18" t="s">
         <v>15</v>
       </c>
@@ -13087,16 +13238,16 @@
         <v>35</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>8</v>
@@ -13112,7 +13263,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J59" s="87"/>
+      <c r="J59" s="84"/>
       <c r="K59" s="18" t="s">
         <v>15</v>
       </c>
@@ -13126,16 +13277,16 @@
         <v>35</v>
       </c>
       <c r="B60" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>66</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="49" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>23</v>
@@ -13151,7 +13302,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J60" s="87"/>
+      <c r="J60" s="84"/>
       <c r="K60" s="18" t="s">
         <v>15</v>
       </c>
@@ -13165,16 +13316,16 @@
         <v>35</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="49" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>8</v>
@@ -13190,7 +13341,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J61" s="87"/>
+      <c r="J61" s="84"/>
       <c r="K61" s="18" t="s">
         <v>15</v>
       </c>
@@ -13207,13 +13358,13 @@
         <v>3.11</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>8</v>
@@ -13229,7 +13380,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J62" s="87"/>
+      <c r="J62" s="84"/>
       <c r="K62" s="18" t="s">
         <v>15</v>
       </c>
@@ -13246,13 +13397,13 @@
         <v>3.11</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>8</v>
@@ -13268,7 +13419,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J63" s="87"/>
+      <c r="J63" s="84"/>
       <c r="K63" s="18" t="s">
         <v>15</v>
       </c>
@@ -13285,13 +13436,13 @@
         <v>3.11</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D64" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>8</v>
@@ -13307,7 +13458,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J64" s="87"/>
+      <c r="J64" s="84"/>
       <c r="K64" s="18" t="s">
         <v>15</v>
       </c>
@@ -13324,13 +13475,13 @@
         <v>3.11</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D65" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>8</v>
@@ -13346,7 +13497,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J65" s="87"/>
+      <c r="J65" s="84"/>
       <c r="K65" s="18" t="s">
         <v>15</v>
       </c>
@@ -13365,7 +13516,7 @@
         <v>48</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>22</v>
@@ -13381,7 +13532,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J66" s="88">
+      <c r="J66" s="70">
         <f>SUM(I66:I68)</f>
         <v>3</v>
       </c>
@@ -13403,7 +13554,7 @@
         <v>48</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>22</v>
@@ -13419,7 +13570,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J67" s="88"/>
+      <c r="J67" s="70"/>
       <c r="K67" s="17" t="s">
         <v>15</v>
       </c>
@@ -13438,7 +13589,7 @@
         <v>48</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>22</v>
@@ -13454,7 +13605,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J68" s="89"/>
+      <c r="J68" s="71"/>
       <c r="K68" s="17" t="s">
         <v>15</v>
       </c>
@@ -13468,16 +13619,16 @@
         <v>35</v>
       </c>
       <c r="B69" s="67" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F69" s="20" t="s">
         <v>27</v>
@@ -13493,7 +13644,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J69" s="90">
+      <c r="J69" s="72">
         <f>SUM(I69:I74)</f>
         <v>17</v>
       </c>
@@ -13508,16 +13659,16 @@
     <row r="70" spans="1:13" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20"/>
       <c r="B70" s="67" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C70" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="50" t="s">
         <v>135</v>
-      </c>
-      <c r="D70" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E70" s="50" t="s">
-        <v>137</v>
       </c>
       <c r="F70" s="20"/>
       <c r="G70" s="20" t="s">
@@ -13531,7 +13682,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J70" s="91"/>
+      <c r="J70" s="73"/>
       <c r="K70" s="20" t="s">
         <v>15</v>
       </c>
@@ -13541,16 +13692,16 @@
     <row r="71" spans="1:13" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20"/>
       <c r="B71" s="67" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F71" s="20"/>
       <c r="G71" s="20" t="s">
@@ -13564,7 +13715,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J71" s="91"/>
+      <c r="J71" s="73"/>
       <c r="K71" s="20" t="s">
         <v>15</v>
       </c>
@@ -13579,13 +13730,13 @@
         <v>3.12</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F72" s="19" t="s">
         <v>8</v>
@@ -13601,7 +13752,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J72" s="91"/>
+      <c r="J72" s="73"/>
       <c r="K72" s="19" t="s">
         <v>15</v>
       </c>
@@ -13618,13 +13769,13 @@
         <v>3.12</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F73" s="19" t="s">
         <v>8</v>
@@ -13640,7 +13791,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J73" s="91"/>
+      <c r="J73" s="73"/>
       <c r="K73" s="19" t="s">
         <v>15</v>
       </c>
@@ -13657,13 +13808,13 @@
         <v>3.13</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F74" s="19" t="s">
         <v>22</v>
@@ -13679,7 +13830,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="J74" s="91"/>
+      <c r="J74" s="73"/>
       <c r="K74" s="19" t="s">
         <v>15</v>
       </c>
@@ -13695,10 +13846,10 @@
       <c r="B75" s="58"/>
       <c r="C75" s="29"/>
       <c r="D75" s="29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E75" s="39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F75" s="29" t="s">
         <v>22</v>
@@ -13734,7 +13885,7 @@
         <v>48</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>22</v>
@@ -13750,7 +13901,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J76" s="80"/>
+      <c r="J76" s="75"/>
       <c r="K76" s="17" t="s">
         <v>15</v>
       </c>
@@ -13761,6 +13912,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="J2:J11"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="J20:J25"/>
+    <mergeCell ref="J26:J28"/>
     <mergeCell ref="J66:J68"/>
     <mergeCell ref="J69:J74"/>
     <mergeCell ref="J75:J76"/>
@@ -13769,11 +13925,6 @@
     <mergeCell ref="J43:J50"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="J54:J65"/>
-    <mergeCell ref="J2:J11"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="J20:J25"/>
-    <mergeCell ref="J26:J28"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13811,10 +13962,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="22">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="C2" s="1">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -13824,13 +13975,11 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="23">
-        <f>156-SUM(D$3:D3)</f>
-        <v>156</v>
-      </c>
-      <c r="C3" s="2">
-        <f>156-A3*15.6</f>
-        <v>140.4</v>
+      <c r="B3" s="22">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1">
+        <v>115</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -13840,13 +13989,11 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="23">
-        <f>156-SUM(D$3:D4)</f>
-        <v>156</v>
-      </c>
-      <c r="C4" s="2">
-        <f t="shared" ref="C4:C12" si="0">156-A4*15.6</f>
-        <v>124.8</v>
+      <c r="B4" s="22">
+        <v>115</v>
+      </c>
+      <c r="C4" s="1">
+        <v>115</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -13857,13 +14004,11 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="23">
-        <f>156-SUM(D$3:D5)</f>
-        <v>156</v>
-      </c>
-      <c r="C5" s="2">
-        <f t="shared" si="0"/>
-        <v>109.2</v>
+      <c r="B5" s="22">
+        <v>115</v>
+      </c>
+      <c r="C5" s="1">
+        <v>115</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -13873,13 +14018,11 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="23">
-        <f>156-SUM(D$3:D6)</f>
-        <v>156</v>
+      <c r="B6" s="22">
+        <v>115</v>
       </c>
       <c r="C6" s="2">
-        <f t="shared" si="0"/>
-        <v>93.6</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -13889,86 +14032,89 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="23">
-        <f>156-SUM(D$3:D7)</f>
-        <v>148</v>
+      <c r="B7" s="22">
+        <v>115</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" si="0"/>
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="23">
-        <f>156-SUM(D$3:D8)</f>
-        <v>148</v>
+      <c r="B8" s="22">
+        <v>115</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" si="0"/>
-        <v>62.400000000000006</v>
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="23">
-        <f>156-SUM(D$3:D9)</f>
-        <v>148</v>
+      <c r="B9" s="22">
+        <v>115</v>
       </c>
       <c r="C9" s="2">
-        <f t="shared" si="0"/>
-        <v>46.8</v>
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="23">
-        <f>156-SUM(D$3:D10)</f>
-        <v>148</v>
+      <c r="B10" s="22">
+        <v>115</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" si="0"/>
-        <v>31.200000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="23">
-        <f>156-SUM(D$3:D11)</f>
-        <v>148</v>
+      <c r="B11" s="22">
+        <v>115</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="0"/>
-        <v>15.599999999999994</v>
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="23">
-        <f>156-SUM(D$3:D12)</f>
-        <v>148</v>
+      <c r="B12" s="22">
+        <v>115</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="W15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -14041,34 +14187,34 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/02SprintPlanJanuary2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FAFF00-EE16-4E41-A5AB-8F754482FCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4B515B-C723-4C3E-A743-2FB2540E355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
@@ -258,578 +258,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Design the cards for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Similar E-Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> list of cards
-2. Make the cards clickable
-3. Render </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-bike name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Circular</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">thumbnail </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">of the E-Bike, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>rating</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date Range</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-bike type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the cards</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBooking-BikeDetails</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen component/layout:
-2. Render an empty card for highlighting the cheapest e-bike
-3.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-bike type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pickup location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> placeholders under big card
-4. Style </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book This E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button as primary
-5. Add Subheading: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Similar E-Bikes </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>under the button</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Render the cheapest E-Bike's 
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>enlarged image</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as the card's background image (occupying 100% of the card)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>rating</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> with (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>no. of ratings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) in the lowest sub-section of the card with 85% opacity.
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-bike type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of the cheapest e-bike under the card
-3.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Wire </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Book This E-Bike </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">button to the highlighted bike
-</t>
-    </r>
-  </si>
-  <si>
     <t>RenterE-BikeBookingConfirmation</t>
   </si>
   <si>
@@ -1882,158 +1310,6 @@
       </rPr>
       <t xml:space="preserve"> Endpoint:
 1. Logic: Fetch the current active insurance policy text/HTML from a CMS or config file (allows updating policy without app store releases).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Render e-bikes filtered by the date entered in list of clickable cards with E-bike </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Circular thumbnail</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of the E-Bike, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>rating</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date Range</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, E-bike </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the cards</t>
     </r>
   </si>
   <si>
@@ -3987,301 +3263,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> hyperlink is hidden away.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedE-BikeOptions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout:
-1. Render the booked E-Bike's 
-- enlarged image as the card's background image (occupying 100% of the card)
-- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, E-bike </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date range</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of booking (From-To) of the cheapest e-bike under the card
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Owner's Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> clickable hyperlink
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Insurance Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> clickable hyperlink
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel Booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> clickable hyperlink
-6. Fetch the booking start date and hide away </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel Booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> option as soon as the date arrives
-- Render a checkbox, followed by "I confirm all </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>e-bike features</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> are working fine" text with hyperlink
-- Render </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Accept E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> primary button
-7. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterBookedE-BikeCancellationOption</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen onPress of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel Booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink</t>
     </r>
   </si>
   <si>
@@ -6106,243 +5087,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingConfirmation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen component/layout:
-1. Render the selected E-Bike's 
-- enlarged image as the card's background image (occupying 100% of the card)
-- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-bike type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date range of booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (From-To) of the cheapest e-bike under the card
-3.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Owner's Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">clickable hyperlink
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Insurance Requirements</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section with 2-3 lines of the document, ending with </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Learn More</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink
-5. A checkbox with "Purchase mandatory </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Insurance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" (Insurance is hyperlink)
-6. A primary button </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -6921,600 +5665,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>" button navigates back without changes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>card</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> component renders with variant = highlightBikeCard
-2. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-Bike Type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup Location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>From: (startDate) - To: (endDate)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> renders
-3. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Owner's Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink renders
-5. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Insurance Requirements </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">section label renders
-- Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Learn more</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink renders
-6. Verify Checkbox component renders
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>insurance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink renders
-7. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button renders with primary styling (button backgroundColor = Colors.primary)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>card</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> component renders with variant = highlightBikeCard
-2. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-Bike Type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup Location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>From: (startDate) - To: (endDate)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> renders
-3. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Book This E-Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button renders with primary style ((button backgroundColor = Colors.primary)
-4. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Similar E-Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> subheading renders
-5. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>listCards</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> component renders
-- Verify scrollability (Manual)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>card</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> component renders with variant = highlightBikeCard
-2. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Price</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E-Bike Type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pickup Location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>From: (startDate) - To: (endDate)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> renders
-3. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Owner's Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink renders
-4. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Insurance Details</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">hyperlink renders
-5. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel Booking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink renders</t>
     </r>
   </si>
   <si>
@@ -9183,6 +7333,2066 @@
       </rPr>
       <t>: boolean)
 - Nested owner summary object.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBooking-BikeDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen component/layout:
+2. Render an empty card for highlighting the cheapest e-bike
+3.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-bike type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> datePicker under big card
+4. Style </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book This E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button as primary
+5. Add Subheading: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Similar E-Bikes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>under the button</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Render the cheapest E-Bike's 
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>enlarged image</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as the card's background image (occupying 100% of the card)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no. of ratings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) in the lowest sub-section of the card with 85% opacity.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-bike type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the cheapest e-bike under the card
+3.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Wire </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Book This E-Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button to the highlighted bike
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Design the cards for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Similar E-Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> list of cards
+2. Make the cards clickable
+3. Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-bike name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Circular</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">thumbnail </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">of the E-Bike, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date Range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-bike type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the cards</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>card</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> component renders with variant = highlightBikeCard
+2. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-Bike Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup Location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From: (startDate) - To: (endDate)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> renders
+3. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink renders
+5. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Insurance Requirements </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">section label renders
+- Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Learn more</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink renders
+6. Verify Checkbox component renders
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>insurance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink renders
+7. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button renders with primary styling (button backgroundColor = Colors.primary)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingConfirmation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen component/layout:
+1. Render the selected E-Bike's 
+- enlarged image as the card's background image (occupying 100% of the card)
+- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-bike type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date range of booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (From-To) of the cheapest e-bike under the card
+3.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">clickable hyperlink
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Requirements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> section with 2-3 lines of the document, ending with </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Learn More</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink
+5. A checkbox with "Purchase mandatory </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" (Insurance is hyperlink)
+6. A primary button </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Render e-bikes filtered by the date entered in list of clickable cards with E-bike </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Circular thumbnail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the E-Bike, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date Range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, E-bike </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the cards</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>card</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> component renders with variant = highlightBikeCard
+2. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-Bike Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup Location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From: (startDate) - To: (endDate)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> renders
+3. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink renders
+4. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Details</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">hyperlink renders
+5. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink renders</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeOptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout:
+1. Render the booked E-Bike's 
+- enlarged image as the card's background image (occupying 100% of the card)
+- name, rating with (no. of ratings) in the lowest sub-section of the card with 85% opacity.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, E-bike </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of booking (From-To) of the cheapest e-bike under the card
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>View Owner's Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Insurance Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> clickable hyperlink
+6. Fetch the booking start date and hide away </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option as soon as the date arrives
+- Render a checkbox, followed by "I confirm all </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e-bike features</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are working fine" text with hyperlink
+- Render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accept E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button
+7. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterBookedE-BikeCancellationOption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen onPress of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel Booking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>card</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> component renders with variant = highlightBikeCard
+2. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Price</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E-Bike Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verifiedBadge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(if isVerified==true), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pickup Location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>From: (startDate) - To: (endDate)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> renders
+3. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Book This E-Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button renders with primary style ((button backgroundColor = Colors.primary)
+4. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Similar E-Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> subheading renders
+5. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>listCards</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> component renders
+- Verify scrollability (Manual)</t>
     </r>
   </si>
 </sst>
@@ -9674,6 +9884,39 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9686,12 +9929,6 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9701,43 +9938,16 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11113,10 +11323,10 @@
         <v>33</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>27</v>
@@ -11132,7 +11342,7 @@
         <f>H2</f>
         <v>1</v>
       </c>
-      <c r="J2" s="85">
+      <c r="J2" s="70">
         <f>SUM(I2:I11)</f>
         <v>18</v>
       </c>
@@ -11155,10 +11365,10 @@
         <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>27</v>
@@ -11174,7 +11384,7 @@
         <f>H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="85"/>
+      <c r="J3" s="70"/>
       <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
@@ -11194,10 +11404,10 @@
         <v>33</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>27</v>
@@ -11213,7 +11423,7 @@
         <f t="shared" ref="I4:I19" si="0">H4</f>
         <v>1</v>
       </c>
-      <c r="J4" s="85"/>
+      <c r="J4" s="70"/>
       <c r="K4" s="5" t="s">
         <v>15</v>
       </c>
@@ -11222,7 +11432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
@@ -11233,10 +11443,10 @@
         <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>27</v>
@@ -11252,7 +11462,7 @@
         <f>H5</f>
         <v>1</v>
       </c>
-      <c r="J5" s="85"/>
+      <c r="J5" s="70"/>
       <c r="K5" s="5" t="s">
         <v>15</v>
       </c>
@@ -11272,10 +11482,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>27</v>
@@ -11291,7 +11501,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J6" s="85"/>
+      <c r="J6" s="70"/>
       <c r="K6" s="5" t="s">
         <v>15</v>
       </c>
@@ -11314,7 +11524,7 @@
         <v>28</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>8</v>
@@ -11330,7 +11540,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J7" s="85"/>
+      <c r="J7" s="70"/>
       <c r="K7" s="6" t="s">
         <v>15</v>
       </c>
@@ -11353,7 +11563,7 @@
         <v>28</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>8</v>
@@ -11369,7 +11579,7 @@
         <f>H8</f>
         <v>2</v>
       </c>
-      <c r="J8" s="85"/>
+      <c r="J8" s="70"/>
       <c r="K8" s="6" t="s">
         <v>15</v>
       </c>
@@ -11378,7 +11588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>35</v>
       </c>
@@ -11392,7 +11602,7 @@
         <v>28</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>8</v>
@@ -11408,7 +11618,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J9" s="85"/>
+      <c r="J9" s="70"/>
       <c r="K9" s="6" t="s">
         <v>15</v>
       </c>
@@ -11417,7 +11627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
@@ -11431,7 +11641,7 @@
         <v>28</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>8</v>
@@ -11447,7 +11657,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J10" s="85"/>
+      <c r="J10" s="70"/>
       <c r="K10" s="6" t="s">
         <v>15</v>
       </c>
@@ -11470,7 +11680,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>8</v>
@@ -11486,7 +11696,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J11" s="85"/>
+      <c r="J11" s="70"/>
       <c r="K11" s="6" t="s">
         <v>15</v>
       </c>
@@ -11504,10 +11714,10 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>27</v>
@@ -11523,7 +11733,7 @@
         <f>H12</f>
         <v>1</v>
       </c>
-      <c r="J12" s="86">
+      <c r="J12" s="71">
         <f>SUM(I12:I16)</f>
         <v>5</v>
       </c>
@@ -11544,10 +11754,10 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>27</v>
@@ -11563,7 +11773,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J13" s="87"/>
+      <c r="J13" s="72"/>
       <c r="K13" s="7" t="s">
         <v>15</v>
       </c>
@@ -11580,7 +11790,7 @@
         <v>3.2</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>28</v>
@@ -11602,7 +11812,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J14" s="87"/>
+      <c r="J14" s="72"/>
       <c r="K14" s="8" t="s">
         <v>15</v>
       </c>
@@ -11619,13 +11829,13 @@
         <v>3.2</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
@@ -11641,7 +11851,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J15" s="87"/>
+      <c r="J15" s="72"/>
       <c r="K15" s="8" t="s">
         <v>15</v>
       </c>
@@ -11658,13 +11868,13 @@
         <v>3.2</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>8</v>
@@ -11680,7 +11890,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J16" s="88"/>
+      <c r="J16" s="73"/>
       <c r="K16" s="8" t="s">
         <v>15</v>
       </c>
@@ -11694,10 +11904,10 @@
       <c r="B17" s="58"/>
       <c r="C17" s="29"/>
       <c r="D17" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" s="29" t="s">
         <v>22</v>
@@ -11713,7 +11923,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J17" s="82">
+      <c r="J17" s="74">
         <f>SUM(I17:I19)</f>
         <v>4</v>
       </c>
@@ -11728,10 +11938,10 @@
       <c r="B18" s="59"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>22</v>
@@ -11747,7 +11957,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="J18" s="82"/>
+      <c r="J18" s="74"/>
       <c r="K18" s="17" t="s">
         <v>15</v>
       </c>
@@ -11761,10 +11971,10 @@
       <c r="B19" s="59"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>22</v>
@@ -11780,7 +11990,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J19" s="82"/>
+      <c r="J19" s="74"/>
       <c r="K19" s="17" t="s">
         <v>15</v>
       </c>
@@ -11797,13 +12007,13 @@
         <v>3.3</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>27</v>
@@ -11819,7 +12029,7 @@
         <f>H20</f>
         <v>2</v>
       </c>
-      <c r="J20" s="89">
+      <c r="J20" s="75">
         <f>SUM(I20:I25)</f>
         <v>7</v>
       </c>
@@ -11839,13 +12049,13 @@
         <v>3.3</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>8</v>
@@ -11861,7 +12071,7 @@
         <f>H21</f>
         <v>1</v>
       </c>
-      <c r="J21" s="90"/>
+      <c r="J21" s="76"/>
       <c r="K21" s="10" t="s">
         <v>15</v>
       </c>
@@ -11878,13 +12088,13 @@
         <v>3.4</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>27</v>
@@ -11900,7 +12110,7 @@
         <f>H22</f>
         <v>1</v>
       </c>
-      <c r="J22" s="90"/>
+      <c r="J22" s="76"/>
       <c r="K22" s="10" t="s">
         <v>15</v>
       </c>
@@ -11917,13 +12127,13 @@
         <v>3.4</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>27</v>
@@ -11939,7 +12149,7 @@
         <f>H23</f>
         <v>1</v>
       </c>
-      <c r="J23" s="90"/>
+      <c r="J23" s="76"/>
       <c r="K23" s="10" t="s">
         <v>15</v>
       </c>
@@ -11956,13 +12166,13 @@
         <v>3.3</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>8</v>
@@ -11978,7 +12188,7 @@
         <f t="shared" ref="I24:I76" si="1">H24</f>
         <v>1</v>
       </c>
-      <c r="J24" s="90"/>
+      <c r="J24" s="76"/>
       <c r="K24" s="11" t="s">
         <v>15</v>
       </c>
@@ -11995,13 +12205,13 @@
         <v>3.4</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>8</v>
@@ -12017,7 +12227,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J25" s="91"/>
+      <c r="J25" s="77"/>
       <c r="K25" s="11" t="s">
         <v>15</v>
       </c>
@@ -12031,10 +12241,10 @@
       <c r="B26" s="58"/>
       <c r="C26" s="29"/>
       <c r="D26" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>22</v>
@@ -12050,7 +12260,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J26" s="79">
+      <c r="J26" s="78">
         <f>SUM(I26:I28)</f>
         <v>3</v>
       </c>
@@ -12065,10 +12275,10 @@
       <c r="B27" s="59"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>22</v>
@@ -12084,7 +12294,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J27" s="74"/>
+      <c r="J27" s="79"/>
       <c r="K27" s="17" t="s">
         <v>15</v>
       </c>
@@ -12098,10 +12308,10 @@
       <c r="B28" s="59"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>22</v>
@@ -12117,7 +12327,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J28" s="75"/>
+      <c r="J28" s="80"/>
       <c r="K28" s="17" t="s">
         <v>15</v>
       </c>
@@ -12134,13 +12344,13 @@
         <v>3.6</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F29" s="27" t="s">
         <v>27</v>
@@ -12156,7 +12366,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J29" s="76">
+      <c r="J29" s="85">
         <f>SUM(I29:I39)</f>
         <v>11</v>
       </c>
@@ -12174,13 +12384,13 @@
         <v>3.5</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>27</v>
@@ -12196,7 +12406,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J30" s="77"/>
+      <c r="J30" s="86"/>
       <c r="K30" s="12" t="s">
         <v>15</v>
       </c>
@@ -12213,13 +12423,13 @@
         <v>3.5</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12" t="s">
@@ -12233,7 +12443,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J31" s="77"/>
+      <c r="J31" s="86"/>
       <c r="K31" s="12" t="s">
         <v>15</v>
       </c>
@@ -12250,13 +12460,13 @@
         <v>3.6</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12" t="s">
@@ -12270,7 +12480,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J32" s="77"/>
+      <c r="J32" s="86"/>
       <c r="K32" s="12" t="s">
         <v>15</v>
       </c>
@@ -12287,13 +12497,13 @@
         <v>3.7</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E33" s="43" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12" t="s">
@@ -12307,7 +12517,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J33" s="77"/>
+      <c r="J33" s="86"/>
       <c r="K33" s="12" t="s">
         <v>15</v>
       </c>
@@ -12324,13 +12534,13 @@
         <v>3.8</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E34" s="43" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F34" s="28"/>
       <c r="G34" s="12" t="s">
@@ -12344,7 +12554,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J34" s="77"/>
+      <c r="J34" s="86"/>
       <c r="K34" s="12" t="s">
         <v>15</v>
       </c>
@@ -12359,13 +12569,13 @@
         <v>3.5</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>8</v>
@@ -12381,7 +12591,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J35" s="77"/>
+      <c r="J35" s="86"/>
       <c r="K35" s="13" t="s">
         <v>15</v>
       </c>
@@ -12398,13 +12608,13 @@
         <v>3.5</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13" t="s">
@@ -12418,7 +12628,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J36" s="77"/>
+      <c r="J36" s="86"/>
       <c r="K36" s="13" t="s">
         <v>15</v>
       </c>
@@ -12435,13 +12645,13 @@
         <v>3.6</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13" t="s">
@@ -12455,7 +12665,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J37" s="77"/>
+      <c r="J37" s="86"/>
       <c r="K37" s="13" t="s">
         <v>15</v>
       </c>
@@ -12472,13 +12682,13 @@
         <v>3.7</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F38" s="13"/>
       <c r="G38" s="13" t="s">
@@ -12492,7 +12702,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J38" s="77"/>
+      <c r="J38" s="86"/>
       <c r="K38" s="13" t="s">
         <v>15</v>
       </c>
@@ -12507,13 +12717,13 @@
         <v>3.8</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="45" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F39" s="25"/>
       <c r="G39" s="13" t="s">
@@ -12527,7 +12737,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J39" s="78"/>
+      <c r="J39" s="87"/>
       <c r="K39" s="13" t="s">
         <v>15</v>
       </c>
@@ -12541,10 +12751,10 @@
       <c r="B40" s="58"/>
       <c r="C40" s="29"/>
       <c r="D40" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="46" t="s">
         <v>78</v>
-      </c>
-      <c r="E40" s="46" t="s">
-        <v>82</v>
       </c>
       <c r="F40" s="30"/>
       <c r="G40" s="30" t="s">
@@ -12558,7 +12768,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J40" s="79">
+      <c r="J40" s="78">
         <f>SUM(I40:I42)</f>
         <v>5</v>
       </c>
@@ -12575,10 +12785,10 @@
       <c r="B41" s="59"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>22</v>
@@ -12594,7 +12804,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J41" s="74"/>
+      <c r="J41" s="79"/>
       <c r="K41" s="17" t="s">
         <v>15</v>
       </c>
@@ -12610,10 +12820,10 @@
       <c r="B42" s="59"/>
       <c r="C42" s="17"/>
       <c r="D42" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>22</v>
@@ -12629,7 +12839,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J42" s="75"/>
+      <c r="J42" s="80"/>
       <c r="K42" s="17" t="s">
         <v>15</v>
       </c>
@@ -12638,7 +12848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>35</v>
       </c>
@@ -12646,13 +12856,13 @@
         <v>3.9</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F43" s="24"/>
       <c r="G43" s="24" t="s">
@@ -12666,7 +12876,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J43" s="80">
+      <c r="J43" s="88">
         <f>SUM(I43:I50)</f>
         <v>14</v>
       </c>
@@ -12686,13 +12896,13 @@
         <v>3.9</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>27</v>
@@ -12708,7 +12918,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J44" s="81"/>
+      <c r="J44" s="89"/>
       <c r="K44" s="15" t="s">
         <v>15</v>
       </c>
@@ -12725,13 +12935,13 @@
         <v>3.9</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15" t="s">
@@ -12745,7 +12955,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J45" s="81"/>
+      <c r="J45" s="89"/>
       <c r="K45" s="15" t="s">
         <v>15</v>
       </c>
@@ -12762,13 +12972,13 @@
         <v>3.9</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F46" s="15"/>
       <c r="G46" s="15" t="s">
@@ -12782,7 +12992,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J46" s="81"/>
+      <c r="J46" s="89"/>
       <c r="K46" s="15" t="s">
         <v>15</v>
       </c>
@@ -12799,13 +13009,13 @@
         <v>3.9</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F47" s="69" t="s">
         <v>8</v>
@@ -12821,7 +13031,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J47" s="81"/>
+      <c r="J47" s="89"/>
       <c r="K47" s="15" t="s">
         <v>15</v>
       </c>
@@ -12836,13 +13046,13 @@
         <v>3.9</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>8</v>
@@ -12858,7 +13068,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J48" s="81"/>
+      <c r="J48" s="89"/>
       <c r="K48" s="14" t="s">
         <v>15</v>
       </c>
@@ -12875,13 +13085,13 @@
         <v>3.9</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>8</v>
@@ -12897,7 +13107,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J49" s="81"/>
+      <c r="J49" s="89"/>
       <c r="K49" s="14" t="s">
         <v>15</v>
       </c>
@@ -12914,13 +13124,13 @@
         <v>3.9</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>8</v>
@@ -12936,7 +13146,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J50" s="81"/>
+      <c r="J50" s="89"/>
       <c r="K50" s="14" t="s">
         <v>15</v>
       </c>
@@ -12950,10 +13160,10 @@
       <c r="B51" s="58"/>
       <c r="C51" s="29"/>
       <c r="D51" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F51" s="29"/>
       <c r="G51" s="29" t="s">
@@ -12967,7 +13177,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J51" s="82">
+      <c r="J51" s="74">
         <f>SUM(I51:I53)</f>
         <v>5</v>
       </c>
@@ -12982,10 +13192,10 @@
       <c r="B52" s="59"/>
       <c r="C52" s="17"/>
       <c r="D52" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>22</v>
@@ -13001,7 +13211,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J52" s="82"/>
+      <c r="J52" s="74"/>
       <c r="K52" s="17" t="s">
         <v>15</v>
       </c>
@@ -13015,10 +13225,10 @@
       <c r="B53" s="59"/>
       <c r="C53" s="17"/>
       <c r="D53" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>22</v>
@@ -13034,7 +13244,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J53" s="82"/>
+      <c r="J53" s="74"/>
       <c r="K53" s="17" t="s">
         <v>15</v>
       </c>
@@ -13048,16 +13258,16 @@
         <v>35</v>
       </c>
       <c r="B54" s="66" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>27</v>
@@ -13073,7 +13283,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J54" s="83">
+      <c r="J54" s="90">
         <f>SUM(I54:I65)</f>
         <v>21</v>
       </c>
@@ -13090,16 +13300,16 @@
         <v>35</v>
       </c>
       <c r="B55" s="66" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F55" s="16"/>
       <c r="G55" s="16" t="s">
@@ -13113,7 +13323,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J55" s="84"/>
+      <c r="J55" s="91"/>
       <c r="K55" s="16" t="s">
         <v>15</v>
       </c>
@@ -13125,16 +13335,16 @@
         <v>35</v>
       </c>
       <c r="B56" s="66" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E56" s="48" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="F56" s="16"/>
       <c r="G56" s="16" t="s">
@@ -13148,7 +13358,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J56" s="84"/>
+      <c r="J56" s="91"/>
       <c r="K56" s="16" t="s">
         <v>15</v>
       </c>
@@ -13160,16 +13370,16 @@
         <v>35</v>
       </c>
       <c r="B57" s="66" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E57" s="48" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="F57" s="16" t="s">
         <v>27</v>
@@ -13185,7 +13395,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J57" s="84"/>
+      <c r="J57" s="91"/>
       <c r="K57" s="16" t="s">
         <v>15</v>
       </c>
@@ -13199,16 +13409,16 @@
         <v>35</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="49" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>8</v>
@@ -13224,7 +13434,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J58" s="84"/>
+      <c r="J58" s="91"/>
       <c r="K58" s="18" t="s">
         <v>15</v>
       </c>
@@ -13238,16 +13448,16 @@
         <v>35</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="49" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>8</v>
@@ -13263,7 +13473,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J59" s="84"/>
+      <c r="J59" s="91"/>
       <c r="K59" s="18" t="s">
         <v>15</v>
       </c>
@@ -13277,16 +13487,16 @@
         <v>35</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="49" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>23</v>
@@ -13302,7 +13512,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J60" s="84"/>
+      <c r="J60" s="91"/>
       <c r="K60" s="18" t="s">
         <v>15</v>
       </c>
@@ -13316,16 +13526,16 @@
         <v>35</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="49" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>8</v>
@@ -13341,7 +13551,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J61" s="84"/>
+      <c r="J61" s="91"/>
       <c r="K61" s="18" t="s">
         <v>15</v>
       </c>
@@ -13358,13 +13568,13 @@
         <v>3.11</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="49" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>8</v>
@@ -13380,7 +13590,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J62" s="84"/>
+      <c r="J62" s="91"/>
       <c r="K62" s="18" t="s">
         <v>15</v>
       </c>
@@ -13397,13 +13607,13 @@
         <v>3.11</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="49" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>8</v>
@@ -13419,7 +13629,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J63" s="84"/>
+      <c r="J63" s="91"/>
       <c r="K63" s="18" t="s">
         <v>15</v>
       </c>
@@ -13436,13 +13646,13 @@
         <v>3.11</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D64" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="49" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>8</v>
@@ -13458,7 +13668,7 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J64" s="84"/>
+      <c r="J64" s="91"/>
       <c r="K64" s="18" t="s">
         <v>15</v>
       </c>
@@ -13475,13 +13685,13 @@
         <v>3.11</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D65" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="49" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>8</v>
@@ -13497,7 +13707,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J65" s="84"/>
+      <c r="J65" s="91"/>
       <c r="K65" s="18" t="s">
         <v>15</v>
       </c>
@@ -13513,10 +13723,10 @@
       <c r="B66" s="59"/>
       <c r="C66" s="17"/>
       <c r="D66" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>22</v>
@@ -13532,7 +13742,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J66" s="70">
+      <c r="J66" s="81">
         <f>SUM(I66:I68)</f>
         <v>3</v>
       </c>
@@ -13551,10 +13761,10 @@
       <c r="B67" s="59"/>
       <c r="C67" s="17"/>
       <c r="D67" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>22</v>
@@ -13570,7 +13780,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J67" s="70"/>
+      <c r="J67" s="81"/>
       <c r="K67" s="17" t="s">
         <v>15</v>
       </c>
@@ -13586,10 +13796,10 @@
       <c r="B68" s="59"/>
       <c r="C68" s="17"/>
       <c r="D68" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>22</v>
@@ -13605,7 +13815,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J68" s="71"/>
+      <c r="J68" s="82"/>
       <c r="K68" s="17" t="s">
         <v>15</v>
       </c>
@@ -13619,16 +13829,16 @@
         <v>35</v>
       </c>
       <c r="B69" s="67" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E69" s="50" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F69" s="20" t="s">
         <v>27</v>
@@ -13644,7 +13854,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J69" s="72">
+      <c r="J69" s="83">
         <f>SUM(I69:I74)</f>
         <v>17</v>
       </c>
@@ -13659,16 +13869,16 @@
     <row r="70" spans="1:13" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20"/>
       <c r="B70" s="67" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E70" s="50" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F70" s="20"/>
       <c r="G70" s="20" t="s">
@@ -13682,7 +13892,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J70" s="73"/>
+      <c r="J70" s="84"/>
       <c r="K70" s="20" t="s">
         <v>15</v>
       </c>
@@ -13692,16 +13902,16 @@
     <row r="71" spans="1:13" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20"/>
       <c r="B71" s="67" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E71" s="50" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="F71" s="20"/>
       <c r="G71" s="20" t="s">
@@ -13715,7 +13925,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J71" s="73"/>
+      <c r="J71" s="84"/>
       <c r="K71" s="20" t="s">
         <v>15</v>
       </c>
@@ -13730,13 +13940,13 @@
         <v>3.12</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F72" s="19" t="s">
         <v>8</v>
@@ -13752,7 +13962,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J72" s="73"/>
+      <c r="J72" s="84"/>
       <c r="K72" s="19" t="s">
         <v>15</v>
       </c>
@@ -13769,13 +13979,13 @@
         <v>3.12</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F73" s="19" t="s">
         <v>8</v>
@@ -13791,7 +14001,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="J73" s="73"/>
+      <c r="J73" s="84"/>
       <c r="K73" s="19" t="s">
         <v>15</v>
       </c>
@@ -13808,13 +14018,13 @@
         <v>3.13</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="51" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F74" s="19" t="s">
         <v>22</v>
@@ -13830,7 +14040,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="J74" s="73"/>
+      <c r="J74" s="84"/>
       <c r="K74" s="19" t="s">
         <v>15</v>
       </c>
@@ -13846,10 +14056,10 @@
       <c r="B75" s="58"/>
       <c r="C75" s="29"/>
       <c r="D75" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E75" s="39" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F75" s="29" t="s">
         <v>22</v>
@@ -13865,7 +14075,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J75" s="74">
+      <c r="J75" s="79">
         <f>SUM(I75:I76)</f>
         <v>2</v>
       </c>
@@ -13882,10 +14092,10 @@
       <c r="B76" s="59"/>
       <c r="C76" s="17"/>
       <c r="D76" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>22</v>
@@ -13901,7 +14111,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J76" s="75"/>
+      <c r="J76" s="80"/>
       <c r="K76" s="17" t="s">
         <v>15</v>
       </c>
@@ -13912,11 +14122,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="J2:J11"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="J20:J25"/>
-    <mergeCell ref="J26:J28"/>
     <mergeCell ref="J66:J68"/>
     <mergeCell ref="J69:J74"/>
     <mergeCell ref="J75:J76"/>
@@ -13925,6 +14130,11 @@
     <mergeCell ref="J43:J50"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="J54:J65"/>
+    <mergeCell ref="J2:J11"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="J17:J19"/>
+    <mergeCell ref="J20:J25"/>
+    <mergeCell ref="J26:J28"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14114,7 +14324,7 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="W15" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -14187,34 +14397,34 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
